--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -567,13 +567,17 @@
         <v>60</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -663,13 +663,17 @@
         <v>60</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:10</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -617,13 +617,17 @@
         <v>30</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-01 22:13</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -570,14 +570,10 @@
         <v>60</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-09-01 21:10</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -713,13 +713,17 @@
         <v>40</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-02 02:03</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -570,10 +570,14 @@
         <v>60</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:56</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18661,13 +18661,17 @@
         <v>40</v>
       </c>
       <c r="I396" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:59</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18711,13 +18711,17 @@
         <v>30</v>
       </c>
       <c r="I397" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-09-02 11:53</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18714,14 +18714,10 @@
         <v>30</v>
       </c>
       <c r="J397" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>2026-09-02 11:53</t>
-        </is>
-      </c>
+      <c r="L397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22042,7 +22042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22066,6 +22066,11 @@
           <t>MetaSemanal</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SenhaHash</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22085,6 +22090,11 @@
       </c>
       <c r="D2" t="n">
         <v>14</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>03ac674216f3e15c761ee1a5e255f067953623c8b388b4459e13f978d7c846f4</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18714,10 +18714,14 @@
         <v>30</v>
       </c>
       <c r="J397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:00</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18714,14 +18714,10 @@
         <v>30</v>
       </c>
       <c r="J397" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:00</t>
-        </is>
-      </c>
+      <c r="L397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18714,10 +18714,14 @@
         <v>30</v>
       </c>
       <c r="J397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:10</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18664,14 +18664,10 @@
         <v>40</v>
       </c>
       <c r="J396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>2026-09-02 09:59</t>
-        </is>
-      </c>
+      <c r="L396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18664,10 +18664,14 @@
         <v>40</v>
       </c>
       <c r="J396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:36</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18664,14 +18664,10 @@
         <v>40</v>
       </c>
       <c r="J396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:36</t>
-        </is>
-      </c>
+      <c r="L396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22069,13 +22069,17 @@
         <v>40</v>
       </c>
       <c r="I470" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J470" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr"/>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:24</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22119,13 +22119,17 @@
         <v>30</v>
       </c>
       <c r="I471" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J471" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K471" t="inlineStr"/>
-      <c r="L471" t="inlineStr"/>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:24</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22169,13 +22169,17 @@
         <v>40</v>
       </c>
       <c r="I472" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J472" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:25</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22072,14 +22072,10 @@
         <v>40</v>
       </c>
       <c r="J470" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:24</t>
-        </is>
-      </c>
+      <c r="L470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22118,14 +22118,10 @@
         <v>30</v>
       </c>
       <c r="J471" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K471" t="inlineStr"/>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:24</t>
-        </is>
-      </c>
+      <c r="L471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22164,14 +22164,10 @@
         <v>40</v>
       </c>
       <c r="J472" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t>2026-09-02 14:25</t>
-        </is>
-      </c>
+      <c r="L472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -34002,7 +34002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34031,6 +34031,11 @@
           <t>SenhaHash</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>IsAdmin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34056,6 +34061,9 @@
           <t>03ac674216f3e15c761ee1a5e255f067953623c8b388b4459e13f978d7c846f4</t>
         </is>
       </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34080,6 +34088,9 @@
         <is>
           <t>9af15b336e6a9619928537df30b2e6a2376569fcf9d7e773eccede65606529a0</t>
         </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18710,14 +18710,10 @@
         <v>30</v>
       </c>
       <c r="J397" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:10</t>
-        </is>
-      </c>
+      <c r="L397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18664,10 +18664,14 @@
         <v>40</v>
       </c>
       <c r="J396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:15</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L469"/>
+  <dimension ref="A1:L651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22030,6 +22030,8378 @@
       </c>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>545</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>40</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J470" t="b">
+        <v>0</v>
+      </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>546</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>40</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="b">
+        <v>0</v>
+      </c>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>547</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>40</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+      <c r="J472" t="b">
+        <v>0</v>
+      </c>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>548</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H473" t="n">
+        <v>60</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+      <c r="J473" t="b">
+        <v>0</v>
+      </c>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>549</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H474" t="n">
+        <v>120</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" t="b">
+        <v>0</v>
+      </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>550</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H475" t="n">
+        <v>40</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0</v>
+      </c>
+      <c r="J475" t="b">
+        <v>0</v>
+      </c>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>551</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H476" t="n">
+        <v>40</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" t="b">
+        <v>0</v>
+      </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>552</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H477" t="n">
+        <v>40</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0</v>
+      </c>
+      <c r="J477" t="b">
+        <v>0</v>
+      </c>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>553</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>40</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0</v>
+      </c>
+      <c r="J478" t="b">
+        <v>0</v>
+      </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>554</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H479" t="n">
+        <v>40</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+      <c r="J479" t="b">
+        <v>0</v>
+      </c>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>555</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H480" t="n">
+        <v>60</v>
+      </c>
+      <c r="I480" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" t="b">
+        <v>0</v>
+      </c>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>556</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H481" t="n">
+        <v>120</v>
+      </c>
+      <c r="I481" t="n">
+        <v>0</v>
+      </c>
+      <c r="J481" t="b">
+        <v>0</v>
+      </c>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>557</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>40</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" t="b">
+        <v>0</v>
+      </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>558</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>40</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0</v>
+      </c>
+      <c r="J483" t="b">
+        <v>0</v>
+      </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>559</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>40</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+      <c r="J484" t="b">
+        <v>0</v>
+      </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>560</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H485" t="n">
+        <v>40</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0</v>
+      </c>
+      <c r="J485" t="b">
+        <v>0</v>
+      </c>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>561</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>40</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0</v>
+      </c>
+      <c r="J486" t="b">
+        <v>0</v>
+      </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>562</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>60</v>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="b">
+        <v>0</v>
+      </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>563</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>120</v>
+      </c>
+      <c r="I488" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" t="b">
+        <v>0</v>
+      </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>564</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H489" t="n">
+        <v>40</v>
+      </c>
+      <c r="I489" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" t="b">
+        <v>0</v>
+      </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>565</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H490" t="n">
+        <v>40</v>
+      </c>
+      <c r="I490" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" t="b">
+        <v>0</v>
+      </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>566</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>40</v>
+      </c>
+      <c r="I491" t="n">
+        <v>0</v>
+      </c>
+      <c r="J491" t="b">
+        <v>0</v>
+      </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>567</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H492" t="n">
+        <v>40</v>
+      </c>
+      <c r="I492" t="n">
+        <v>0</v>
+      </c>
+      <c r="J492" t="b">
+        <v>0</v>
+      </c>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>568</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H493" t="n">
+        <v>40</v>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="b">
+        <v>0</v>
+      </c>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>569</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H494" t="n">
+        <v>60</v>
+      </c>
+      <c r="I494" t="n">
+        <v>0</v>
+      </c>
+      <c r="J494" t="b">
+        <v>0</v>
+      </c>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>570</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H495" t="n">
+        <v>120</v>
+      </c>
+      <c r="I495" t="n">
+        <v>0</v>
+      </c>
+      <c r="J495" t="b">
+        <v>0</v>
+      </c>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>571</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H496" t="n">
+        <v>40</v>
+      </c>
+      <c r="I496" t="n">
+        <v>0</v>
+      </c>
+      <c r="J496" t="b">
+        <v>0</v>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>572</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H497" t="n">
+        <v>40</v>
+      </c>
+      <c r="I497" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" t="b">
+        <v>0</v>
+      </c>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>573</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H498" t="n">
+        <v>40</v>
+      </c>
+      <c r="I498" t="n">
+        <v>0</v>
+      </c>
+      <c r="J498" t="b">
+        <v>0</v>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>574</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H499" t="n">
+        <v>40</v>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" t="b">
+        <v>0</v>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>575</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H500" t="n">
+        <v>40</v>
+      </c>
+      <c r="I500" t="n">
+        <v>0</v>
+      </c>
+      <c r="J500" t="b">
+        <v>0</v>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>576</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H501" t="n">
+        <v>60</v>
+      </c>
+      <c r="I501" t="n">
+        <v>0</v>
+      </c>
+      <c r="J501" t="b">
+        <v>0</v>
+      </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>577</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H502" t="n">
+        <v>120</v>
+      </c>
+      <c r="I502" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" t="b">
+        <v>0</v>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>578</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H503" t="n">
+        <v>40</v>
+      </c>
+      <c r="I503" t="n">
+        <v>0</v>
+      </c>
+      <c r="J503" t="b">
+        <v>0</v>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>579</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H504" t="n">
+        <v>40</v>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" t="b">
+        <v>0</v>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>580</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H505" t="n">
+        <v>40</v>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="b">
+        <v>0</v>
+      </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>581</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H506" t="n">
+        <v>40</v>
+      </c>
+      <c r="I506" t="n">
+        <v>0</v>
+      </c>
+      <c r="J506" t="b">
+        <v>0</v>
+      </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>582</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H507" t="n">
+        <v>40</v>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="b">
+        <v>0</v>
+      </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>583</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H508" t="n">
+        <v>60</v>
+      </c>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" t="b">
+        <v>0</v>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>584</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>120</v>
+      </c>
+      <c r="I509" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" t="b">
+        <v>0</v>
+      </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>585</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>40</v>
+      </c>
+      <c r="I510" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" t="b">
+        <v>0</v>
+      </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>586</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>40</v>
+      </c>
+      <c r="I511" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" t="b">
+        <v>0</v>
+      </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>587</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>40</v>
+      </c>
+      <c r="I512" t="n">
+        <v>0</v>
+      </c>
+      <c r="J512" t="b">
+        <v>0</v>
+      </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>588</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>40</v>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" t="b">
+        <v>0</v>
+      </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>589</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H514" t="n">
+        <v>40</v>
+      </c>
+      <c r="I514" t="n">
+        <v>0</v>
+      </c>
+      <c r="J514" t="b">
+        <v>0</v>
+      </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>590</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H515" t="n">
+        <v>60</v>
+      </c>
+      <c r="I515" t="n">
+        <v>0</v>
+      </c>
+      <c r="J515" t="b">
+        <v>0</v>
+      </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>591</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>120</v>
+      </c>
+      <c r="I516" t="n">
+        <v>0</v>
+      </c>
+      <c r="J516" t="b">
+        <v>0</v>
+      </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>592</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>40</v>
+      </c>
+      <c r="I517" t="n">
+        <v>0</v>
+      </c>
+      <c r="J517" t="b">
+        <v>0</v>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>593</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>40</v>
+      </c>
+      <c r="I518" t="n">
+        <v>0</v>
+      </c>
+      <c r="J518" t="b">
+        <v>0</v>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>594</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>40</v>
+      </c>
+      <c r="I519" t="n">
+        <v>0</v>
+      </c>
+      <c r="J519" t="b">
+        <v>0</v>
+      </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>595</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H520" t="n">
+        <v>40</v>
+      </c>
+      <c r="I520" t="n">
+        <v>0</v>
+      </c>
+      <c r="J520" t="b">
+        <v>0</v>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>596</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>40</v>
+      </c>
+      <c r="I521" t="n">
+        <v>0</v>
+      </c>
+      <c r="J521" t="b">
+        <v>0</v>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>597</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>60</v>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="b">
+        <v>0</v>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>598</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>120</v>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" t="b">
+        <v>0</v>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>599</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>40</v>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" t="b">
+        <v>0</v>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>600</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>40</v>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="b">
+        <v>0</v>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>601</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>40</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" t="b">
+        <v>0</v>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>602</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>40</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="b">
+        <v>0</v>
+      </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>603</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>40</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" t="b">
+        <v>0</v>
+      </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>604</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>60</v>
+      </c>
+      <c r="I529" t="n">
+        <v>0</v>
+      </c>
+      <c r="J529" t="b">
+        <v>0</v>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>605</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>120</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" t="b">
+        <v>0</v>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>606</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>40</v>
+      </c>
+      <c r="I531" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" t="b">
+        <v>0</v>
+      </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>607</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>40</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" t="b">
+        <v>0</v>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>608</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>40</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J533" t="b">
+        <v>0</v>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>609</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>40</v>
+      </c>
+      <c r="I534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J534" t="b">
+        <v>0</v>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>610</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>40</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" t="b">
+        <v>0</v>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>611</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>60</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" t="b">
+        <v>0</v>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>612</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>120</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" t="b">
+        <v>0</v>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>613</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>40</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0</v>
+      </c>
+      <c r="J538" t="b">
+        <v>0</v>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>614</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>40</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0</v>
+      </c>
+      <c r="J539" t="b">
+        <v>0</v>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>615</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>40</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0</v>
+      </c>
+      <c r="J540" t="b">
+        <v>0</v>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>616</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>40</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="b">
+        <v>0</v>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>617</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>40</v>
+      </c>
+      <c r="I542" t="n">
+        <v>0</v>
+      </c>
+      <c r="J542" t="b">
+        <v>0</v>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>618</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>60</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0</v>
+      </c>
+      <c r="J543" t="b">
+        <v>0</v>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>619</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>120</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" t="b">
+        <v>0</v>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>620</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>40</v>
+      </c>
+      <c r="I545" t="n">
+        <v>0</v>
+      </c>
+      <c r="J545" t="b">
+        <v>0</v>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>621</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>40</v>
+      </c>
+      <c r="I546" t="n">
+        <v>0</v>
+      </c>
+      <c r="J546" t="b">
+        <v>0</v>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>622</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>40</v>
+      </c>
+      <c r="I547" t="n">
+        <v>0</v>
+      </c>
+      <c r="J547" t="b">
+        <v>0</v>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>623</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>40</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" t="b">
+        <v>0</v>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>624</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>40</v>
+      </c>
+      <c r="I549" t="n">
+        <v>0</v>
+      </c>
+      <c r="J549" t="b">
+        <v>0</v>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>625</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>60</v>
+      </c>
+      <c r="I550" t="n">
+        <v>0</v>
+      </c>
+      <c r="J550" t="b">
+        <v>0</v>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>626</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>120</v>
+      </c>
+      <c r="I551" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" t="b">
+        <v>0</v>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>627</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>40</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0</v>
+      </c>
+      <c r="J552" t="b">
+        <v>0</v>
+      </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>628</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>40</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0</v>
+      </c>
+      <c r="J553" t="b">
+        <v>0</v>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>629</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>40</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0</v>
+      </c>
+      <c r="J554" t="b">
+        <v>0</v>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>630</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>40</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0</v>
+      </c>
+      <c r="J555" t="b">
+        <v>0</v>
+      </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>631</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>40</v>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" t="b">
+        <v>0</v>
+      </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>632</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>60</v>
+      </c>
+      <c r="I557" t="n">
+        <v>0</v>
+      </c>
+      <c r="J557" t="b">
+        <v>0</v>
+      </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>633</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>120</v>
+      </c>
+      <c r="I558" t="n">
+        <v>0</v>
+      </c>
+      <c r="J558" t="b">
+        <v>0</v>
+      </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>634</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>40</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="b">
+        <v>0</v>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>635</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>40</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0</v>
+      </c>
+      <c r="J560" t="b">
+        <v>0</v>
+      </c>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>636</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>40</v>
+      </c>
+      <c r="I561" t="n">
+        <v>0</v>
+      </c>
+      <c r="J561" t="b">
+        <v>0</v>
+      </c>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>637</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>40</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0</v>
+      </c>
+      <c r="J562" t="b">
+        <v>0</v>
+      </c>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>638</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>40</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" t="b">
+        <v>0</v>
+      </c>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>639</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>60</v>
+      </c>
+      <c r="I564" t="n">
+        <v>0</v>
+      </c>
+      <c r="J564" t="b">
+        <v>0</v>
+      </c>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>640</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>120</v>
+      </c>
+      <c r="I565" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" t="b">
+        <v>0</v>
+      </c>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>641</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>40</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" t="b">
+        <v>0</v>
+      </c>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>642</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>40</v>
+      </c>
+      <c r="I567" t="n">
+        <v>0</v>
+      </c>
+      <c r="J567" t="b">
+        <v>0</v>
+      </c>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>643</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>40</v>
+      </c>
+      <c r="I568" t="n">
+        <v>0</v>
+      </c>
+      <c r="J568" t="b">
+        <v>0</v>
+      </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>644</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>40</v>
+      </c>
+      <c r="I569" t="n">
+        <v>0</v>
+      </c>
+      <c r="J569" t="b">
+        <v>0</v>
+      </c>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>645</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>40</v>
+      </c>
+      <c r="I570" t="n">
+        <v>0</v>
+      </c>
+      <c r="J570" t="b">
+        <v>0</v>
+      </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>646</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>60</v>
+      </c>
+      <c r="I571" t="n">
+        <v>0</v>
+      </c>
+      <c r="J571" t="b">
+        <v>0</v>
+      </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>647</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>120</v>
+      </c>
+      <c r="I572" t="n">
+        <v>0</v>
+      </c>
+      <c r="J572" t="b">
+        <v>0</v>
+      </c>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>648</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>40</v>
+      </c>
+      <c r="I573" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" t="b">
+        <v>0</v>
+      </c>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>649</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>40</v>
+      </c>
+      <c r="I574" t="n">
+        <v>0</v>
+      </c>
+      <c r="J574" t="b">
+        <v>0</v>
+      </c>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>650</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>40</v>
+      </c>
+      <c r="I575" t="n">
+        <v>0</v>
+      </c>
+      <c r="J575" t="b">
+        <v>0</v>
+      </c>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>651</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>40</v>
+      </c>
+      <c r="I576" t="n">
+        <v>0</v>
+      </c>
+      <c r="J576" t="b">
+        <v>0</v>
+      </c>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>652</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>40</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" t="b">
+        <v>0</v>
+      </c>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>653</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>60</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" t="b">
+        <v>0</v>
+      </c>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>654</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H579" t="n">
+        <v>120</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J579" t="b">
+        <v>0</v>
+      </c>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>655</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H580" t="n">
+        <v>40</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0</v>
+      </c>
+      <c r="J580" t="b">
+        <v>0</v>
+      </c>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>656</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H581" t="n">
+        <v>40</v>
+      </c>
+      <c r="I581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" t="b">
+        <v>0</v>
+      </c>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>657</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H582" t="n">
+        <v>40</v>
+      </c>
+      <c r="I582" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" t="b">
+        <v>0</v>
+      </c>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>658</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H583" t="n">
+        <v>40</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0</v>
+      </c>
+      <c r="J583" t="b">
+        <v>0</v>
+      </c>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>659</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H584" t="n">
+        <v>40</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" t="b">
+        <v>0</v>
+      </c>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>660</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H585" t="n">
+        <v>60</v>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" t="b">
+        <v>0</v>
+      </c>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>661</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H586" t="n">
+        <v>120</v>
+      </c>
+      <c r="I586" t="n">
+        <v>0</v>
+      </c>
+      <c r="J586" t="b">
+        <v>0</v>
+      </c>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>662</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H587" t="n">
+        <v>40</v>
+      </c>
+      <c r="I587" t="n">
+        <v>0</v>
+      </c>
+      <c r="J587" t="b">
+        <v>0</v>
+      </c>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>663</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H588" t="n">
+        <v>40</v>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J588" t="b">
+        <v>0</v>
+      </c>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>664</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H589" t="n">
+        <v>40</v>
+      </c>
+      <c r="I589" t="n">
+        <v>0</v>
+      </c>
+      <c r="J589" t="b">
+        <v>0</v>
+      </c>
+      <c r="K589" t="inlineStr"/>
+      <c r="L589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>665</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H590" t="n">
+        <v>40</v>
+      </c>
+      <c r="I590" t="n">
+        <v>0</v>
+      </c>
+      <c r="J590" t="b">
+        <v>0</v>
+      </c>
+      <c r="K590" t="inlineStr"/>
+      <c r="L590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>666</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H591" t="n">
+        <v>40</v>
+      </c>
+      <c r="I591" t="n">
+        <v>0</v>
+      </c>
+      <c r="J591" t="b">
+        <v>0</v>
+      </c>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>667</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H592" t="n">
+        <v>60</v>
+      </c>
+      <c r="I592" t="n">
+        <v>0</v>
+      </c>
+      <c r="J592" t="b">
+        <v>0</v>
+      </c>
+      <c r="K592" t="inlineStr"/>
+      <c r="L592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>668</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H593" t="n">
+        <v>120</v>
+      </c>
+      <c r="I593" t="n">
+        <v>0</v>
+      </c>
+      <c r="J593" t="b">
+        <v>0</v>
+      </c>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>669</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H594" t="n">
+        <v>40</v>
+      </c>
+      <c r="I594" t="n">
+        <v>0</v>
+      </c>
+      <c r="J594" t="b">
+        <v>0</v>
+      </c>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>670</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H595" t="n">
+        <v>40</v>
+      </c>
+      <c r="I595" t="n">
+        <v>0</v>
+      </c>
+      <c r="J595" t="b">
+        <v>0</v>
+      </c>
+      <c r="K595" t="inlineStr"/>
+      <c r="L595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>671</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H596" t="n">
+        <v>40</v>
+      </c>
+      <c r="I596" t="n">
+        <v>0</v>
+      </c>
+      <c r="J596" t="b">
+        <v>0</v>
+      </c>
+      <c r="K596" t="inlineStr"/>
+      <c r="L596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>672</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>40</v>
+      </c>
+      <c r="I597" t="n">
+        <v>0</v>
+      </c>
+      <c r="J597" t="b">
+        <v>0</v>
+      </c>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>673</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H598" t="n">
+        <v>40</v>
+      </c>
+      <c r="I598" t="n">
+        <v>0</v>
+      </c>
+      <c r="J598" t="b">
+        <v>0</v>
+      </c>
+      <c r="K598" t="inlineStr"/>
+      <c r="L598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>674</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H599" t="n">
+        <v>60</v>
+      </c>
+      <c r="I599" t="n">
+        <v>0</v>
+      </c>
+      <c r="J599" t="b">
+        <v>0</v>
+      </c>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>675</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2027-01-10</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>120</v>
+      </c>
+      <c r="I600" t="n">
+        <v>0</v>
+      </c>
+      <c r="J600" t="b">
+        <v>0</v>
+      </c>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>676</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2027-01-11</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H601" t="n">
+        <v>40</v>
+      </c>
+      <c r="I601" t="n">
+        <v>0</v>
+      </c>
+      <c r="J601" t="b">
+        <v>0</v>
+      </c>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>677</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H602" t="n">
+        <v>40</v>
+      </c>
+      <c r="I602" t="n">
+        <v>0</v>
+      </c>
+      <c r="J602" t="b">
+        <v>0</v>
+      </c>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>678</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H603" t="n">
+        <v>40</v>
+      </c>
+      <c r="I603" t="n">
+        <v>0</v>
+      </c>
+      <c r="J603" t="b">
+        <v>0</v>
+      </c>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>679</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H604" t="n">
+        <v>40</v>
+      </c>
+      <c r="I604" t="n">
+        <v>0</v>
+      </c>
+      <c r="J604" t="b">
+        <v>0</v>
+      </c>
+      <c r="K604" t="inlineStr"/>
+      <c r="L604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>680</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H605" t="n">
+        <v>40</v>
+      </c>
+      <c r="I605" t="n">
+        <v>0</v>
+      </c>
+      <c r="J605" t="b">
+        <v>0</v>
+      </c>
+      <c r="K605" t="inlineStr"/>
+      <c r="L605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>681</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2027-01-16</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H606" t="n">
+        <v>60</v>
+      </c>
+      <c r="I606" t="n">
+        <v>0</v>
+      </c>
+      <c r="J606" t="b">
+        <v>0</v>
+      </c>
+      <c r="K606" t="inlineStr"/>
+      <c r="L606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>682</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H607" t="n">
+        <v>120</v>
+      </c>
+      <c r="I607" t="n">
+        <v>0</v>
+      </c>
+      <c r="J607" t="b">
+        <v>0</v>
+      </c>
+      <c r="K607" t="inlineStr"/>
+      <c r="L607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>683</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H608" t="n">
+        <v>40</v>
+      </c>
+      <c r="I608" t="n">
+        <v>0</v>
+      </c>
+      <c r="J608" t="b">
+        <v>0</v>
+      </c>
+      <c r="K608" t="inlineStr"/>
+      <c r="L608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>684</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H609" t="n">
+        <v>40</v>
+      </c>
+      <c r="I609" t="n">
+        <v>0</v>
+      </c>
+      <c r="J609" t="b">
+        <v>0</v>
+      </c>
+      <c r="K609" t="inlineStr"/>
+      <c r="L609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>685</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H610" t="n">
+        <v>40</v>
+      </c>
+      <c r="I610" t="n">
+        <v>0</v>
+      </c>
+      <c r="J610" t="b">
+        <v>0</v>
+      </c>
+      <c r="K610" t="inlineStr"/>
+      <c r="L610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>686</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H611" t="n">
+        <v>40</v>
+      </c>
+      <c r="I611" t="n">
+        <v>0</v>
+      </c>
+      <c r="J611" t="b">
+        <v>0</v>
+      </c>
+      <c r="K611" t="inlineStr"/>
+      <c r="L611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>687</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H612" t="n">
+        <v>40</v>
+      </c>
+      <c r="I612" t="n">
+        <v>0</v>
+      </c>
+      <c r="J612" t="b">
+        <v>0</v>
+      </c>
+      <c r="K612" t="inlineStr"/>
+      <c r="L612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>688</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H613" t="n">
+        <v>60</v>
+      </c>
+      <c r="I613" t="n">
+        <v>0</v>
+      </c>
+      <c r="J613" t="b">
+        <v>0</v>
+      </c>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>689</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H614" t="n">
+        <v>120</v>
+      </c>
+      <c r="I614" t="n">
+        <v>0</v>
+      </c>
+      <c r="J614" t="b">
+        <v>0</v>
+      </c>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>690</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H615" t="n">
+        <v>40</v>
+      </c>
+      <c r="I615" t="n">
+        <v>0</v>
+      </c>
+      <c r="J615" t="b">
+        <v>0</v>
+      </c>
+      <c r="K615" t="inlineStr"/>
+      <c r="L615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>691</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H616" t="n">
+        <v>40</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0</v>
+      </c>
+      <c r="J616" t="b">
+        <v>0</v>
+      </c>
+      <c r="K616" t="inlineStr"/>
+      <c r="L616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>692</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H617" t="n">
+        <v>40</v>
+      </c>
+      <c r="I617" t="n">
+        <v>0</v>
+      </c>
+      <c r="J617" t="b">
+        <v>0</v>
+      </c>
+      <c r="K617" t="inlineStr"/>
+      <c r="L617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>693</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H618" t="n">
+        <v>40</v>
+      </c>
+      <c r="I618" t="n">
+        <v>0</v>
+      </c>
+      <c r="J618" t="b">
+        <v>0</v>
+      </c>
+      <c r="K618" t="inlineStr"/>
+      <c r="L618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>694</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H619" t="n">
+        <v>40</v>
+      </c>
+      <c r="I619" t="n">
+        <v>0</v>
+      </c>
+      <c r="J619" t="b">
+        <v>0</v>
+      </c>
+      <c r="K619" t="inlineStr"/>
+      <c r="L619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>695</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H620" t="n">
+        <v>60</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0</v>
+      </c>
+      <c r="J620" t="b">
+        <v>0</v>
+      </c>
+      <c r="K620" t="inlineStr"/>
+      <c r="L620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>696</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H621" t="n">
+        <v>120</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0</v>
+      </c>
+      <c r="J621" t="b">
+        <v>0</v>
+      </c>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>697</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H622" t="n">
+        <v>40</v>
+      </c>
+      <c r="I622" t="n">
+        <v>0</v>
+      </c>
+      <c r="J622" t="b">
+        <v>0</v>
+      </c>
+      <c r="K622" t="inlineStr"/>
+      <c r="L622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>698</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2027-02-02</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H623" t="n">
+        <v>40</v>
+      </c>
+      <c r="I623" t="n">
+        <v>0</v>
+      </c>
+      <c r="J623" t="b">
+        <v>0</v>
+      </c>
+      <c r="K623" t="inlineStr"/>
+      <c r="L623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>699</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2027-02-03</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H624" t="n">
+        <v>40</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0</v>
+      </c>
+      <c r="J624" t="b">
+        <v>0</v>
+      </c>
+      <c r="K624" t="inlineStr"/>
+      <c r="L624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>700</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H625" t="n">
+        <v>40</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0</v>
+      </c>
+      <c r="J625" t="b">
+        <v>0</v>
+      </c>
+      <c r="K625" t="inlineStr"/>
+      <c r="L625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>701</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2027-02-05</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H626" t="n">
+        <v>40</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0</v>
+      </c>
+      <c r="J626" t="b">
+        <v>0</v>
+      </c>
+      <c r="K626" t="inlineStr"/>
+      <c r="L626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>702</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2027-02-06</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H627" t="n">
+        <v>60</v>
+      </c>
+      <c r="I627" t="n">
+        <v>0</v>
+      </c>
+      <c r="J627" t="b">
+        <v>0</v>
+      </c>
+      <c r="K627" t="inlineStr"/>
+      <c r="L627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>703</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2027-02-07</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H628" t="n">
+        <v>120</v>
+      </c>
+      <c r="I628" t="n">
+        <v>0</v>
+      </c>
+      <c r="J628" t="b">
+        <v>0</v>
+      </c>
+      <c r="K628" t="inlineStr"/>
+      <c r="L628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>704</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2027-02-08</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H629" t="n">
+        <v>40</v>
+      </c>
+      <c r="I629" t="n">
+        <v>0</v>
+      </c>
+      <c r="J629" t="b">
+        <v>0</v>
+      </c>
+      <c r="K629" t="inlineStr"/>
+      <c r="L629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>705</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2027-02-09</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H630" t="n">
+        <v>40</v>
+      </c>
+      <c r="I630" t="n">
+        <v>0</v>
+      </c>
+      <c r="J630" t="b">
+        <v>0</v>
+      </c>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>706</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2027-02-10</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H631" t="n">
+        <v>40</v>
+      </c>
+      <c r="I631" t="n">
+        <v>0</v>
+      </c>
+      <c r="J631" t="b">
+        <v>0</v>
+      </c>
+      <c r="K631" t="inlineStr"/>
+      <c r="L631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>707</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2027-02-11</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H632" t="n">
+        <v>40</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0</v>
+      </c>
+      <c r="J632" t="b">
+        <v>0</v>
+      </c>
+      <c r="K632" t="inlineStr"/>
+      <c r="L632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>708</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2027-02-12</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H633" t="n">
+        <v>40</v>
+      </c>
+      <c r="I633" t="n">
+        <v>0</v>
+      </c>
+      <c r="J633" t="b">
+        <v>0</v>
+      </c>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>709</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2027-02-13</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H634" t="n">
+        <v>60</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0</v>
+      </c>
+      <c r="J634" t="b">
+        <v>0</v>
+      </c>
+      <c r="K634" t="inlineStr"/>
+      <c r="L634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>710</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2027-02-14</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H635" t="n">
+        <v>120</v>
+      </c>
+      <c r="I635" t="n">
+        <v>0</v>
+      </c>
+      <c r="J635" t="b">
+        <v>0</v>
+      </c>
+      <c r="K635" t="inlineStr"/>
+      <c r="L635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>711</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2027-02-15</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H636" t="n">
+        <v>40</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0</v>
+      </c>
+      <c r="J636" t="b">
+        <v>0</v>
+      </c>
+      <c r="K636" t="inlineStr"/>
+      <c r="L636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>712</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2027-02-16</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H637" t="n">
+        <v>40</v>
+      </c>
+      <c r="I637" t="n">
+        <v>0</v>
+      </c>
+      <c r="J637" t="b">
+        <v>0</v>
+      </c>
+      <c r="K637" t="inlineStr"/>
+      <c r="L637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>713</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2027-02-17</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H638" t="n">
+        <v>40</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0</v>
+      </c>
+      <c r="J638" t="b">
+        <v>0</v>
+      </c>
+      <c r="K638" t="inlineStr"/>
+      <c r="L638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>714</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2027-02-18</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H639" t="n">
+        <v>40</v>
+      </c>
+      <c r="I639" t="n">
+        <v>0</v>
+      </c>
+      <c r="J639" t="b">
+        <v>0</v>
+      </c>
+      <c r="K639" t="inlineStr"/>
+      <c r="L639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>715</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H640" t="n">
+        <v>40</v>
+      </c>
+      <c r="I640" t="n">
+        <v>0</v>
+      </c>
+      <c r="J640" t="b">
+        <v>0</v>
+      </c>
+      <c r="K640" t="inlineStr"/>
+      <c r="L640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>716</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2027-02-20</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H641" t="n">
+        <v>60</v>
+      </c>
+      <c r="I641" t="n">
+        <v>0</v>
+      </c>
+      <c r="J641" t="b">
+        <v>0</v>
+      </c>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>717</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2027-02-21</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H642" t="n">
+        <v>120</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0</v>
+      </c>
+      <c r="J642" t="b">
+        <v>0</v>
+      </c>
+      <c r="K642" t="inlineStr"/>
+      <c r="L642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>718</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2027-02-22</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H643" t="n">
+        <v>40</v>
+      </c>
+      <c r="I643" t="n">
+        <v>0</v>
+      </c>
+      <c r="J643" t="b">
+        <v>0</v>
+      </c>
+      <c r="K643" t="inlineStr"/>
+      <c r="L643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>719</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H644" t="n">
+        <v>40</v>
+      </c>
+      <c r="I644" t="n">
+        <v>0</v>
+      </c>
+      <c r="J644" t="b">
+        <v>0</v>
+      </c>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>720</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2027-02-24</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H645" t="n">
+        <v>40</v>
+      </c>
+      <c r="I645" t="n">
+        <v>0</v>
+      </c>
+      <c r="J645" t="b">
+        <v>0</v>
+      </c>
+      <c r="K645" t="inlineStr"/>
+      <c r="L645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>721</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2027-02-25</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H646" t="n">
+        <v>40</v>
+      </c>
+      <c r="I646" t="n">
+        <v>0</v>
+      </c>
+      <c r="J646" t="b">
+        <v>0</v>
+      </c>
+      <c r="K646" t="inlineStr"/>
+      <c r="L646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>722</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2027-02-26</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>4:00</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>English Live - Conversação em grupo</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H647" t="n">
+        <v>40</v>
+      </c>
+      <c r="I647" t="n">
+        <v>0</v>
+      </c>
+      <c r="J647" t="b">
+        <v>0</v>
+      </c>
+      <c r="K647" t="inlineStr"/>
+      <c r="L647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>723</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Livro/Leitura</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H648" t="n">
+        <v>60</v>
+      </c>
+      <c r="I648" t="n">
+        <v>0</v>
+      </c>
+      <c r="J648" t="b">
+        <v>0</v>
+      </c>
+      <c r="K648" t="inlineStr"/>
+      <c r="L648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>724</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>5:00</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Podcast em inglês</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H649" t="n">
+        <v>120</v>
+      </c>
+      <c r="I649" t="n">
+        <v>0</v>
+      </c>
+      <c r="J649" t="b">
+        <v>0</v>
+      </c>
+      <c r="K649" t="inlineStr"/>
+      <c r="L649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>725</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>English Live - Exercício de gramática</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H650" t="n">
+        <v>40</v>
+      </c>
+      <c r="I650" t="n">
+        <v>0</v>
+      </c>
+      <c r="J650" t="b">
+        <v>0</v>
+      </c>
+      <c r="K650" t="inlineStr"/>
+      <c r="L650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>726</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>English Live - Aula com professor</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H651" t="n">
+        <v>40</v>
+      </c>
+      <c r="I651" t="n">
+        <v>0</v>
+      </c>
+      <c r="J651" t="b">
+        <v>0</v>
+      </c>
+      <c r="K651" t="inlineStr"/>
+      <c r="L651" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22042,7 +30414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22105,6 +30477,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Time Fluência</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>#f97316</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>05744ee6ac5e4d4d6fe17c3a30ff222ac662743a1753c992914ca8a034ae9f66</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22069,13 +22069,17 @@
         <v>40</v>
       </c>
       <c r="I470" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J470" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr"/>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>2026-09-02 18:41</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L651"/>
+  <dimension ref="A1:L469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22030,8382 +22030,6 @@
       </c>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" t="n">
-        <v>545</v>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E470" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F470" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G470" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H470" t="n">
-        <v>40</v>
-      </c>
-      <c r="I470" t="n">
-        <v>40</v>
-      </c>
-      <c r="J470" t="b">
-        <v>1</v>
-      </c>
-      <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>2026-09-02 18:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="n">
-        <v>546</v>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G471" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H471" t="n">
-        <v>40</v>
-      </c>
-      <c r="I471" t="n">
-        <v>0</v>
-      </c>
-      <c r="J471" t="b">
-        <v>0</v>
-      </c>
-      <c r="K471" t="inlineStr"/>
-      <c r="L471" t="inlineStr"/>
-    </row>
-    <row r="472">
-      <c r="A472" t="n">
-        <v>547</v>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H472" t="n">
-        <v>40</v>
-      </c>
-      <c r="I472" t="n">
-        <v>0</v>
-      </c>
-      <c r="J472" t="b">
-        <v>0</v>
-      </c>
-      <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
-    </row>
-    <row r="473">
-      <c r="A473" t="n">
-        <v>548</v>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H473" t="n">
-        <v>60</v>
-      </c>
-      <c r="I473" t="n">
-        <v>0</v>
-      </c>
-      <c r="J473" t="b">
-        <v>0</v>
-      </c>
-      <c r="K473" t="inlineStr"/>
-      <c r="L473" t="inlineStr"/>
-    </row>
-    <row r="474">
-      <c r="A474" t="n">
-        <v>549</v>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F474" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G474" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H474" t="n">
-        <v>120</v>
-      </c>
-      <c r="I474" t="n">
-        <v>0</v>
-      </c>
-      <c r="J474" t="b">
-        <v>0</v>
-      </c>
-      <c r="K474" t="inlineStr"/>
-      <c r="L474" t="inlineStr"/>
-    </row>
-    <row r="475">
-      <c r="A475" t="n">
-        <v>550</v>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H475" t="n">
-        <v>40</v>
-      </c>
-      <c r="I475" t="n">
-        <v>0</v>
-      </c>
-      <c r="J475" t="b">
-        <v>0</v>
-      </c>
-      <c r="K475" t="inlineStr"/>
-      <c r="L475" t="inlineStr"/>
-    </row>
-    <row r="476">
-      <c r="A476" t="n">
-        <v>551</v>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H476" t="n">
-        <v>40</v>
-      </c>
-      <c r="I476" t="n">
-        <v>0</v>
-      </c>
-      <c r="J476" t="b">
-        <v>0</v>
-      </c>
-      <c r="K476" t="inlineStr"/>
-      <c r="L476" t="inlineStr"/>
-    </row>
-    <row r="477">
-      <c r="A477" t="n">
-        <v>552</v>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H477" t="n">
-        <v>40</v>
-      </c>
-      <c r="I477" t="n">
-        <v>0</v>
-      </c>
-      <c r="J477" t="b">
-        <v>0</v>
-      </c>
-      <c r="K477" t="inlineStr"/>
-      <c r="L477" t="inlineStr"/>
-    </row>
-    <row r="478">
-      <c r="A478" t="n">
-        <v>553</v>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F478" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H478" t="n">
-        <v>40</v>
-      </c>
-      <c r="I478" t="n">
-        <v>0</v>
-      </c>
-      <c r="J478" t="b">
-        <v>0</v>
-      </c>
-      <c r="K478" t="inlineStr"/>
-      <c r="L478" t="inlineStr"/>
-    </row>
-    <row r="479">
-      <c r="A479" t="n">
-        <v>554</v>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G479" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H479" t="n">
-        <v>40</v>
-      </c>
-      <c r="I479" t="n">
-        <v>0</v>
-      </c>
-      <c r="J479" t="b">
-        <v>0</v>
-      </c>
-      <c r="K479" t="inlineStr"/>
-      <c r="L479" t="inlineStr"/>
-    </row>
-    <row r="480">
-      <c r="A480" t="n">
-        <v>555</v>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H480" t="n">
-        <v>60</v>
-      </c>
-      <c r="I480" t="n">
-        <v>0</v>
-      </c>
-      <c r="J480" t="b">
-        <v>0</v>
-      </c>
-      <c r="K480" t="inlineStr"/>
-      <c r="L480" t="inlineStr"/>
-    </row>
-    <row r="481">
-      <c r="A481" t="n">
-        <v>556</v>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G481" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H481" t="n">
-        <v>120</v>
-      </c>
-      <c r="I481" t="n">
-        <v>0</v>
-      </c>
-      <c r="J481" t="b">
-        <v>0</v>
-      </c>
-      <c r="K481" t="inlineStr"/>
-      <c r="L481" t="inlineStr"/>
-    </row>
-    <row r="482">
-      <c r="A482" t="n">
-        <v>557</v>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E482" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F482" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G482" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H482" t="n">
-        <v>40</v>
-      </c>
-      <c r="I482" t="n">
-        <v>0</v>
-      </c>
-      <c r="J482" t="b">
-        <v>0</v>
-      </c>
-      <c r="K482" t="inlineStr"/>
-      <c r="L482" t="inlineStr"/>
-    </row>
-    <row r="483">
-      <c r="A483" t="n">
-        <v>558</v>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F483" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H483" t="n">
-        <v>40</v>
-      </c>
-      <c r="I483" t="n">
-        <v>0</v>
-      </c>
-      <c r="J483" t="b">
-        <v>0</v>
-      </c>
-      <c r="K483" t="inlineStr"/>
-      <c r="L483" t="inlineStr"/>
-    </row>
-    <row r="484">
-      <c r="A484" t="n">
-        <v>559</v>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F484" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H484" t="n">
-        <v>40</v>
-      </c>
-      <c r="I484" t="n">
-        <v>0</v>
-      </c>
-      <c r="J484" t="b">
-        <v>0</v>
-      </c>
-      <c r="K484" t="inlineStr"/>
-      <c r="L484" t="inlineStr"/>
-    </row>
-    <row r="485">
-      <c r="A485" t="n">
-        <v>560</v>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H485" t="n">
-        <v>40</v>
-      </c>
-      <c r="I485" t="n">
-        <v>0</v>
-      </c>
-      <c r="J485" t="b">
-        <v>0</v>
-      </c>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" t="n">
-        <v>561</v>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H486" t="n">
-        <v>40</v>
-      </c>
-      <c r="I486" t="n">
-        <v>0</v>
-      </c>
-      <c r="J486" t="b">
-        <v>0</v>
-      </c>
-      <c r="K486" t="inlineStr"/>
-      <c r="L486" t="inlineStr"/>
-    </row>
-    <row r="487">
-      <c r="A487" t="n">
-        <v>562</v>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H487" t="n">
-        <v>60</v>
-      </c>
-      <c r="I487" t="n">
-        <v>0</v>
-      </c>
-      <c r="J487" t="b">
-        <v>0</v>
-      </c>
-      <c r="K487" t="inlineStr"/>
-      <c r="L487" t="inlineStr"/>
-    </row>
-    <row r="488">
-      <c r="A488" t="n">
-        <v>563</v>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H488" t="n">
-        <v>120</v>
-      </c>
-      <c r="I488" t="n">
-        <v>0</v>
-      </c>
-      <c r="J488" t="b">
-        <v>0</v>
-      </c>
-      <c r="K488" t="inlineStr"/>
-      <c r="L488" t="inlineStr"/>
-    </row>
-    <row r="489">
-      <c r="A489" t="n">
-        <v>564</v>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H489" t="n">
-        <v>40</v>
-      </c>
-      <c r="I489" t="n">
-        <v>0</v>
-      </c>
-      <c r="J489" t="b">
-        <v>0</v>
-      </c>
-      <c r="K489" t="inlineStr"/>
-      <c r="L489" t="inlineStr"/>
-    </row>
-    <row r="490">
-      <c r="A490" t="n">
-        <v>565</v>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H490" t="n">
-        <v>40</v>
-      </c>
-      <c r="I490" t="n">
-        <v>0</v>
-      </c>
-      <c r="J490" t="b">
-        <v>0</v>
-      </c>
-      <c r="K490" t="inlineStr"/>
-      <c r="L490" t="inlineStr"/>
-    </row>
-    <row r="491">
-      <c r="A491" t="n">
-        <v>566</v>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F491" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G491" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H491" t="n">
-        <v>40</v>
-      </c>
-      <c r="I491" t="n">
-        <v>0</v>
-      </c>
-      <c r="J491" t="b">
-        <v>0</v>
-      </c>
-      <c r="K491" t="inlineStr"/>
-      <c r="L491" t="inlineStr"/>
-    </row>
-    <row r="492">
-      <c r="A492" t="n">
-        <v>567</v>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H492" t="n">
-        <v>40</v>
-      </c>
-      <c r="I492" t="n">
-        <v>0</v>
-      </c>
-      <c r="J492" t="b">
-        <v>0</v>
-      </c>
-      <c r="K492" t="inlineStr"/>
-      <c r="L492" t="inlineStr"/>
-    </row>
-    <row r="493">
-      <c r="A493" t="n">
-        <v>568</v>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H493" t="n">
-        <v>40</v>
-      </c>
-      <c r="I493" t="n">
-        <v>0</v>
-      </c>
-      <c r="J493" t="b">
-        <v>0</v>
-      </c>
-      <c r="K493" t="inlineStr"/>
-      <c r="L493" t="inlineStr"/>
-    </row>
-    <row r="494">
-      <c r="A494" t="n">
-        <v>569</v>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G494" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H494" t="n">
-        <v>60</v>
-      </c>
-      <c r="I494" t="n">
-        <v>0</v>
-      </c>
-      <c r="J494" t="b">
-        <v>0</v>
-      </c>
-      <c r="K494" t="inlineStr"/>
-      <c r="L494" t="inlineStr"/>
-    </row>
-    <row r="495">
-      <c r="A495" t="n">
-        <v>570</v>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F495" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G495" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H495" t="n">
-        <v>120</v>
-      </c>
-      <c r="I495" t="n">
-        <v>0</v>
-      </c>
-      <c r="J495" t="b">
-        <v>0</v>
-      </c>
-      <c r="K495" t="inlineStr"/>
-      <c r="L495" t="inlineStr"/>
-    </row>
-    <row r="496">
-      <c r="A496" t="n">
-        <v>571</v>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H496" t="n">
-        <v>40</v>
-      </c>
-      <c r="I496" t="n">
-        <v>0</v>
-      </c>
-      <c r="J496" t="b">
-        <v>0</v>
-      </c>
-      <c r="K496" t="inlineStr"/>
-      <c r="L496" t="inlineStr"/>
-    </row>
-    <row r="497">
-      <c r="A497" t="n">
-        <v>572</v>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H497" t="n">
-        <v>40</v>
-      </c>
-      <c r="I497" t="n">
-        <v>0</v>
-      </c>
-      <c r="J497" t="b">
-        <v>0</v>
-      </c>
-      <c r="K497" t="inlineStr"/>
-      <c r="L497" t="inlineStr"/>
-    </row>
-    <row r="498">
-      <c r="A498" t="n">
-        <v>573</v>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H498" t="n">
-        <v>40</v>
-      </c>
-      <c r="I498" t="n">
-        <v>0</v>
-      </c>
-      <c r="J498" t="b">
-        <v>0</v>
-      </c>
-      <c r="K498" t="inlineStr"/>
-      <c r="L498" t="inlineStr"/>
-    </row>
-    <row r="499">
-      <c r="A499" t="n">
-        <v>574</v>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F499" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H499" t="n">
-        <v>40</v>
-      </c>
-      <c r="I499" t="n">
-        <v>0</v>
-      </c>
-      <c r="J499" t="b">
-        <v>0</v>
-      </c>
-      <c r="K499" t="inlineStr"/>
-      <c r="L499" t="inlineStr"/>
-    </row>
-    <row r="500">
-      <c r="A500" t="n">
-        <v>575</v>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E500" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H500" t="n">
-        <v>40</v>
-      </c>
-      <c r="I500" t="n">
-        <v>0</v>
-      </c>
-      <c r="J500" t="b">
-        <v>0</v>
-      </c>
-      <c r="K500" t="inlineStr"/>
-      <c r="L500" t="inlineStr"/>
-    </row>
-    <row r="501">
-      <c r="A501" t="n">
-        <v>576</v>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H501" t="n">
-        <v>60</v>
-      </c>
-      <c r="I501" t="n">
-        <v>0</v>
-      </c>
-      <c r="J501" t="b">
-        <v>0</v>
-      </c>
-      <c r="K501" t="inlineStr"/>
-      <c r="L501" t="inlineStr"/>
-    </row>
-    <row r="502">
-      <c r="A502" t="n">
-        <v>577</v>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E502" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H502" t="n">
-        <v>120</v>
-      </c>
-      <c r="I502" t="n">
-        <v>0</v>
-      </c>
-      <c r="J502" t="b">
-        <v>0</v>
-      </c>
-      <c r="K502" t="inlineStr"/>
-      <c r="L502" t="inlineStr"/>
-    </row>
-    <row r="503">
-      <c r="A503" t="n">
-        <v>578</v>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F503" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H503" t="n">
-        <v>40</v>
-      </c>
-      <c r="I503" t="n">
-        <v>0</v>
-      </c>
-      <c r="J503" t="b">
-        <v>0</v>
-      </c>
-      <c r="K503" t="inlineStr"/>
-      <c r="L503" t="inlineStr"/>
-    </row>
-    <row r="504">
-      <c r="A504" t="n">
-        <v>579</v>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F504" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H504" t="n">
-        <v>40</v>
-      </c>
-      <c r="I504" t="n">
-        <v>0</v>
-      </c>
-      <c r="J504" t="b">
-        <v>0</v>
-      </c>
-      <c r="K504" t="inlineStr"/>
-      <c r="L504" t="inlineStr"/>
-    </row>
-    <row r="505">
-      <c r="A505" t="n">
-        <v>580</v>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E505" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F505" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G505" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H505" t="n">
-        <v>40</v>
-      </c>
-      <c r="I505" t="n">
-        <v>0</v>
-      </c>
-      <c r="J505" t="b">
-        <v>0</v>
-      </c>
-      <c r="K505" t="inlineStr"/>
-      <c r="L505" t="inlineStr"/>
-    </row>
-    <row r="506">
-      <c r="A506" t="n">
-        <v>581</v>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E506" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F506" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G506" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H506" t="n">
-        <v>40</v>
-      </c>
-      <c r="I506" t="n">
-        <v>0</v>
-      </c>
-      <c r="J506" t="b">
-        <v>0</v>
-      </c>
-      <c r="K506" t="inlineStr"/>
-      <c r="L506" t="inlineStr"/>
-    </row>
-    <row r="507">
-      <c r="A507" t="n">
-        <v>582</v>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E507" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H507" t="n">
-        <v>40</v>
-      </c>
-      <c r="I507" t="n">
-        <v>0</v>
-      </c>
-      <c r="J507" t="b">
-        <v>0</v>
-      </c>
-      <c r="K507" t="inlineStr"/>
-      <c r="L507" t="inlineStr"/>
-    </row>
-    <row r="508">
-      <c r="A508" t="n">
-        <v>583</v>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E508" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H508" t="n">
-        <v>60</v>
-      </c>
-      <c r="I508" t="n">
-        <v>0</v>
-      </c>
-      <c r="J508" t="b">
-        <v>0</v>
-      </c>
-      <c r="K508" t="inlineStr"/>
-      <c r="L508" t="inlineStr"/>
-    </row>
-    <row r="509">
-      <c r="A509" t="n">
-        <v>584</v>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E509" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F509" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H509" t="n">
-        <v>120</v>
-      </c>
-      <c r="I509" t="n">
-        <v>0</v>
-      </c>
-      <c r="J509" t="b">
-        <v>0</v>
-      </c>
-      <c r="K509" t="inlineStr"/>
-      <c r="L509" t="inlineStr"/>
-    </row>
-    <row r="510">
-      <c r="A510" t="n">
-        <v>585</v>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E510" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F510" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H510" t="n">
-        <v>40</v>
-      </c>
-      <c r="I510" t="n">
-        <v>0</v>
-      </c>
-      <c r="J510" t="b">
-        <v>0</v>
-      </c>
-      <c r="K510" t="inlineStr"/>
-      <c r="L510" t="inlineStr"/>
-    </row>
-    <row r="511">
-      <c r="A511" t="n">
-        <v>586</v>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E511" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H511" t="n">
-        <v>40</v>
-      </c>
-      <c r="I511" t="n">
-        <v>0</v>
-      </c>
-      <c r="J511" t="b">
-        <v>0</v>
-      </c>
-      <c r="K511" t="inlineStr"/>
-      <c r="L511" t="inlineStr"/>
-    </row>
-    <row r="512">
-      <c r="A512" t="n">
-        <v>587</v>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F512" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H512" t="n">
-        <v>40</v>
-      </c>
-      <c r="I512" t="n">
-        <v>0</v>
-      </c>
-      <c r="J512" t="b">
-        <v>0</v>
-      </c>
-      <c r="K512" t="inlineStr"/>
-      <c r="L512" t="inlineStr"/>
-    </row>
-    <row r="513">
-      <c r="A513" t="n">
-        <v>588</v>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E513" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F513" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G513" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H513" t="n">
-        <v>40</v>
-      </c>
-      <c r="I513" t="n">
-        <v>0</v>
-      </c>
-      <c r="J513" t="b">
-        <v>0</v>
-      </c>
-      <c r="K513" t="inlineStr"/>
-      <c r="L513" t="inlineStr"/>
-    </row>
-    <row r="514">
-      <c r="A514" t="n">
-        <v>589</v>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E514" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F514" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G514" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H514" t="n">
-        <v>40</v>
-      </c>
-      <c r="I514" t="n">
-        <v>0</v>
-      </c>
-      <c r="J514" t="b">
-        <v>0</v>
-      </c>
-      <c r="K514" t="inlineStr"/>
-      <c r="L514" t="inlineStr"/>
-    </row>
-    <row r="515">
-      <c r="A515" t="n">
-        <v>590</v>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H515" t="n">
-        <v>60</v>
-      </c>
-      <c r="I515" t="n">
-        <v>0</v>
-      </c>
-      <c r="J515" t="b">
-        <v>0</v>
-      </c>
-      <c r="K515" t="inlineStr"/>
-      <c r="L515" t="inlineStr"/>
-    </row>
-    <row r="516">
-      <c r="A516" t="n">
-        <v>591</v>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F516" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G516" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H516" t="n">
-        <v>120</v>
-      </c>
-      <c r="I516" t="n">
-        <v>0</v>
-      </c>
-      <c r="J516" t="b">
-        <v>0</v>
-      </c>
-      <c r="K516" t="inlineStr"/>
-      <c r="L516" t="inlineStr"/>
-    </row>
-    <row r="517">
-      <c r="A517" t="n">
-        <v>592</v>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H517" t="n">
-        <v>40</v>
-      </c>
-      <c r="I517" t="n">
-        <v>0</v>
-      </c>
-      <c r="J517" t="b">
-        <v>0</v>
-      </c>
-      <c r="K517" t="inlineStr"/>
-      <c r="L517" t="inlineStr"/>
-    </row>
-    <row r="518">
-      <c r="A518" t="n">
-        <v>593</v>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F518" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H518" t="n">
-        <v>40</v>
-      </c>
-      <c r="I518" t="n">
-        <v>0</v>
-      </c>
-      <c r="J518" t="b">
-        <v>0</v>
-      </c>
-      <c r="K518" t="inlineStr"/>
-      <c r="L518" t="inlineStr"/>
-    </row>
-    <row r="519">
-      <c r="A519" t="n">
-        <v>594</v>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F519" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H519" t="n">
-        <v>40</v>
-      </c>
-      <c r="I519" t="n">
-        <v>0</v>
-      </c>
-      <c r="J519" t="b">
-        <v>0</v>
-      </c>
-      <c r="K519" t="inlineStr"/>
-      <c r="L519" t="inlineStr"/>
-    </row>
-    <row r="520">
-      <c r="A520" t="n">
-        <v>595</v>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E520" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F520" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G520" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H520" t="n">
-        <v>40</v>
-      </c>
-      <c r="I520" t="n">
-        <v>0</v>
-      </c>
-      <c r="J520" t="b">
-        <v>0</v>
-      </c>
-      <c r="K520" t="inlineStr"/>
-      <c r="L520" t="inlineStr"/>
-    </row>
-    <row r="521">
-      <c r="A521" t="n">
-        <v>596</v>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E521" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F521" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G521" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H521" t="n">
-        <v>40</v>
-      </c>
-      <c r="I521" t="n">
-        <v>0</v>
-      </c>
-      <c r="J521" t="b">
-        <v>0</v>
-      </c>
-      <c r="K521" t="inlineStr"/>
-      <c r="L521" t="inlineStr"/>
-    </row>
-    <row r="522">
-      <c r="A522" t="n">
-        <v>597</v>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E522" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G522" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H522" t="n">
-        <v>60</v>
-      </c>
-      <c r="I522" t="n">
-        <v>0</v>
-      </c>
-      <c r="J522" t="b">
-        <v>0</v>
-      </c>
-      <c r="K522" t="inlineStr"/>
-      <c r="L522" t="inlineStr"/>
-    </row>
-    <row r="523">
-      <c r="A523" t="n">
-        <v>598</v>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F523" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H523" t="n">
-        <v>120</v>
-      </c>
-      <c r="I523" t="n">
-        <v>0</v>
-      </c>
-      <c r="J523" t="b">
-        <v>0</v>
-      </c>
-      <c r="K523" t="inlineStr"/>
-      <c r="L523" t="inlineStr"/>
-    </row>
-    <row r="524">
-      <c r="A524" t="n">
-        <v>599</v>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F524" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H524" t="n">
-        <v>40</v>
-      </c>
-      <c r="I524" t="n">
-        <v>0</v>
-      </c>
-      <c r="J524" t="b">
-        <v>0</v>
-      </c>
-      <c r="K524" t="inlineStr"/>
-      <c r="L524" t="inlineStr"/>
-    </row>
-    <row r="525">
-      <c r="A525" t="n">
-        <v>600</v>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F525" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H525" t="n">
-        <v>40</v>
-      </c>
-      <c r="I525" t="n">
-        <v>0</v>
-      </c>
-      <c r="J525" t="b">
-        <v>0</v>
-      </c>
-      <c r="K525" t="inlineStr"/>
-      <c r="L525" t="inlineStr"/>
-    </row>
-    <row r="526">
-      <c r="A526" t="n">
-        <v>601</v>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F526" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H526" t="n">
-        <v>40</v>
-      </c>
-      <c r="I526" t="n">
-        <v>0</v>
-      </c>
-      <c r="J526" t="b">
-        <v>0</v>
-      </c>
-      <c r="K526" t="inlineStr"/>
-      <c r="L526" t="inlineStr"/>
-    </row>
-    <row r="527">
-      <c r="A527" t="n">
-        <v>602</v>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E527" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H527" t="n">
-        <v>40</v>
-      </c>
-      <c r="I527" t="n">
-        <v>0</v>
-      </c>
-      <c r="J527" t="b">
-        <v>0</v>
-      </c>
-      <c r="K527" t="inlineStr"/>
-      <c r="L527" t="inlineStr"/>
-    </row>
-    <row r="528">
-      <c r="A528" t="n">
-        <v>603</v>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H528" t="n">
-        <v>40</v>
-      </c>
-      <c r="I528" t="n">
-        <v>0</v>
-      </c>
-      <c r="J528" t="b">
-        <v>0</v>
-      </c>
-      <c r="K528" t="inlineStr"/>
-      <c r="L528" t="inlineStr"/>
-    </row>
-    <row r="529">
-      <c r="A529" t="n">
-        <v>604</v>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H529" t="n">
-        <v>60</v>
-      </c>
-      <c r="I529" t="n">
-        <v>0</v>
-      </c>
-      <c r="J529" t="b">
-        <v>0</v>
-      </c>
-      <c r="K529" t="inlineStr"/>
-      <c r="L529" t="inlineStr"/>
-    </row>
-    <row r="530">
-      <c r="A530" t="n">
-        <v>605</v>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G530" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H530" t="n">
-        <v>120</v>
-      </c>
-      <c r="I530" t="n">
-        <v>0</v>
-      </c>
-      <c r="J530" t="b">
-        <v>0</v>
-      </c>
-      <c r="K530" t="inlineStr"/>
-      <c r="L530" t="inlineStr"/>
-    </row>
-    <row r="531">
-      <c r="A531" t="n">
-        <v>606</v>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H531" t="n">
-        <v>40</v>
-      </c>
-      <c r="I531" t="n">
-        <v>0</v>
-      </c>
-      <c r="J531" t="b">
-        <v>0</v>
-      </c>
-      <c r="K531" t="inlineStr"/>
-      <c r="L531" t="inlineStr"/>
-    </row>
-    <row r="532">
-      <c r="A532" t="n">
-        <v>607</v>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E532" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F532" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G532" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H532" t="n">
-        <v>40</v>
-      </c>
-      <c r="I532" t="n">
-        <v>0</v>
-      </c>
-      <c r="J532" t="b">
-        <v>0</v>
-      </c>
-      <c r="K532" t="inlineStr"/>
-      <c r="L532" t="inlineStr"/>
-    </row>
-    <row r="533">
-      <c r="A533" t="n">
-        <v>608</v>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>2026-11-04</t>
-        </is>
-      </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F533" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G533" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H533" t="n">
-        <v>40</v>
-      </c>
-      <c r="I533" t="n">
-        <v>0</v>
-      </c>
-      <c r="J533" t="b">
-        <v>0</v>
-      </c>
-      <c r="K533" t="inlineStr"/>
-      <c r="L533" t="inlineStr"/>
-    </row>
-    <row r="534">
-      <c r="A534" t="n">
-        <v>609</v>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F534" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H534" t="n">
-        <v>40</v>
-      </c>
-      <c r="I534" t="n">
-        <v>0</v>
-      </c>
-      <c r="J534" t="b">
-        <v>0</v>
-      </c>
-      <c r="K534" t="inlineStr"/>
-      <c r="L534" t="inlineStr"/>
-    </row>
-    <row r="535">
-      <c r="A535" t="n">
-        <v>610</v>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C535" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F535" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H535" t="n">
-        <v>40</v>
-      </c>
-      <c r="I535" t="n">
-        <v>0</v>
-      </c>
-      <c r="J535" t="b">
-        <v>0</v>
-      </c>
-      <c r="K535" t="inlineStr"/>
-      <c r="L535" t="inlineStr"/>
-    </row>
-    <row r="536">
-      <c r="A536" t="n">
-        <v>611</v>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C536" t="inlineStr">
-        <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F536" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H536" t="n">
-        <v>60</v>
-      </c>
-      <c r="I536" t="n">
-        <v>0</v>
-      </c>
-      <c r="J536" t="b">
-        <v>0</v>
-      </c>
-      <c r="K536" t="inlineStr"/>
-      <c r="L536" t="inlineStr"/>
-    </row>
-    <row r="537">
-      <c r="A537" t="n">
-        <v>612</v>
-      </c>
-      <c r="B537" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C537" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H537" t="n">
-        <v>120</v>
-      </c>
-      <c r="I537" t="n">
-        <v>0</v>
-      </c>
-      <c r="J537" t="b">
-        <v>0</v>
-      </c>
-      <c r="K537" t="inlineStr"/>
-      <c r="L537" t="inlineStr"/>
-    </row>
-    <row r="538">
-      <c r="A538" t="n">
-        <v>613</v>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H538" t="n">
-        <v>40</v>
-      </c>
-      <c r="I538" t="n">
-        <v>0</v>
-      </c>
-      <c r="J538" t="b">
-        <v>0</v>
-      </c>
-      <c r="K538" t="inlineStr"/>
-      <c r="L538" t="inlineStr"/>
-    </row>
-    <row r="539">
-      <c r="A539" t="n">
-        <v>614</v>
-      </c>
-      <c r="B539" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C539" t="inlineStr">
-        <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F539" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G539" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H539" t="n">
-        <v>40</v>
-      </c>
-      <c r="I539" t="n">
-        <v>0</v>
-      </c>
-      <c r="J539" t="b">
-        <v>0</v>
-      </c>
-      <c r="K539" t="inlineStr"/>
-      <c r="L539" t="inlineStr"/>
-    </row>
-    <row r="540">
-      <c r="A540" t="n">
-        <v>615</v>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F540" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G540" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H540" t="n">
-        <v>40</v>
-      </c>
-      <c r="I540" t="n">
-        <v>0</v>
-      </c>
-      <c r="J540" t="b">
-        <v>0</v>
-      </c>
-      <c r="K540" t="inlineStr"/>
-      <c r="L540" t="inlineStr"/>
-    </row>
-    <row r="541">
-      <c r="A541" t="n">
-        <v>616</v>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C541" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F541" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G541" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H541" t="n">
-        <v>40</v>
-      </c>
-      <c r="I541" t="n">
-        <v>0</v>
-      </c>
-      <c r="J541" t="b">
-        <v>0</v>
-      </c>
-      <c r="K541" t="inlineStr"/>
-      <c r="L541" t="inlineStr"/>
-    </row>
-    <row r="542">
-      <c r="A542" t="n">
-        <v>617</v>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C542" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F542" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G542" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H542" t="n">
-        <v>40</v>
-      </c>
-      <c r="I542" t="n">
-        <v>0</v>
-      </c>
-      <c r="J542" t="b">
-        <v>0</v>
-      </c>
-      <c r="K542" t="inlineStr"/>
-      <c r="L542" t="inlineStr"/>
-    </row>
-    <row r="543">
-      <c r="A543" t="n">
-        <v>618</v>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>2026-11-14</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H543" t="n">
-        <v>60</v>
-      </c>
-      <c r="I543" t="n">
-        <v>0</v>
-      </c>
-      <c r="J543" t="b">
-        <v>0</v>
-      </c>
-      <c r="K543" t="inlineStr"/>
-      <c r="L543" t="inlineStr"/>
-    </row>
-    <row r="544">
-      <c r="A544" t="n">
-        <v>619</v>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>2026-11-15</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E544" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G544" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H544" t="n">
-        <v>120</v>
-      </c>
-      <c r="I544" t="n">
-        <v>0</v>
-      </c>
-      <c r="J544" t="b">
-        <v>0</v>
-      </c>
-      <c r="K544" t="inlineStr"/>
-      <c r="L544" t="inlineStr"/>
-    </row>
-    <row r="545">
-      <c r="A545" t="n">
-        <v>620</v>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E545" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H545" t="n">
-        <v>40</v>
-      </c>
-      <c r="I545" t="n">
-        <v>0</v>
-      </c>
-      <c r="J545" t="b">
-        <v>0</v>
-      </c>
-      <c r="K545" t="inlineStr"/>
-      <c r="L545" t="inlineStr"/>
-    </row>
-    <row r="546">
-      <c r="A546" t="n">
-        <v>621</v>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>2026-11-17</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G546" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H546" t="n">
-        <v>40</v>
-      </c>
-      <c r="I546" t="n">
-        <v>0</v>
-      </c>
-      <c r="J546" t="b">
-        <v>0</v>
-      </c>
-      <c r="K546" t="inlineStr"/>
-      <c r="L546" t="inlineStr"/>
-    </row>
-    <row r="547">
-      <c r="A547" t="n">
-        <v>622</v>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E547" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H547" t="n">
-        <v>40</v>
-      </c>
-      <c r="I547" t="n">
-        <v>0</v>
-      </c>
-      <c r="J547" t="b">
-        <v>0</v>
-      </c>
-      <c r="K547" t="inlineStr"/>
-      <c r="L547" t="inlineStr"/>
-    </row>
-    <row r="548">
-      <c r="A548" t="n">
-        <v>623</v>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E548" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F548" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H548" t="n">
-        <v>40</v>
-      </c>
-      <c r="I548" t="n">
-        <v>0</v>
-      </c>
-      <c r="J548" t="b">
-        <v>0</v>
-      </c>
-      <c r="K548" t="inlineStr"/>
-      <c r="L548" t="inlineStr"/>
-    </row>
-    <row r="549">
-      <c r="A549" t="n">
-        <v>624</v>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E549" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G549" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H549" t="n">
-        <v>40</v>
-      </c>
-      <c r="I549" t="n">
-        <v>0</v>
-      </c>
-      <c r="J549" t="b">
-        <v>0</v>
-      </c>
-      <c r="K549" t="inlineStr"/>
-      <c r="L549" t="inlineStr"/>
-    </row>
-    <row r="550">
-      <c r="A550" t="n">
-        <v>625</v>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>2026-11-21</t>
-        </is>
-      </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H550" t="n">
-        <v>60</v>
-      </c>
-      <c r="I550" t="n">
-        <v>0</v>
-      </c>
-      <c r="J550" t="b">
-        <v>0</v>
-      </c>
-      <c r="K550" t="inlineStr"/>
-      <c r="L550" t="inlineStr"/>
-    </row>
-    <row r="551">
-      <c r="A551" t="n">
-        <v>626</v>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>2026-11-22</t>
-        </is>
-      </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E551" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F551" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G551" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H551" t="n">
-        <v>120</v>
-      </c>
-      <c r="I551" t="n">
-        <v>0</v>
-      </c>
-      <c r="J551" t="b">
-        <v>0</v>
-      </c>
-      <c r="K551" t="inlineStr"/>
-      <c r="L551" t="inlineStr"/>
-    </row>
-    <row r="552">
-      <c r="A552" t="n">
-        <v>627</v>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E552" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G552" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H552" t="n">
-        <v>40</v>
-      </c>
-      <c r="I552" t="n">
-        <v>0</v>
-      </c>
-      <c r="J552" t="b">
-        <v>0</v>
-      </c>
-      <c r="K552" t="inlineStr"/>
-      <c r="L552" t="inlineStr"/>
-    </row>
-    <row r="553">
-      <c r="A553" t="n">
-        <v>628</v>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr">
-        <is>
-          <t>2026-11-24</t>
-        </is>
-      </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G553" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H553" t="n">
-        <v>40</v>
-      </c>
-      <c r="I553" t="n">
-        <v>0</v>
-      </c>
-      <c r="J553" t="b">
-        <v>0</v>
-      </c>
-      <c r="K553" t="inlineStr"/>
-      <c r="L553" t="inlineStr"/>
-    </row>
-    <row r="554">
-      <c r="A554" t="n">
-        <v>629</v>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C554" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F554" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G554" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H554" t="n">
-        <v>40</v>
-      </c>
-      <c r="I554" t="n">
-        <v>0</v>
-      </c>
-      <c r="J554" t="b">
-        <v>0</v>
-      </c>
-      <c r="K554" t="inlineStr"/>
-      <c r="L554" t="inlineStr"/>
-    </row>
-    <row r="555">
-      <c r="A555" t="n">
-        <v>630</v>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>2026-11-26</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F555" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G555" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H555" t="n">
-        <v>40</v>
-      </c>
-      <c r="I555" t="n">
-        <v>0</v>
-      </c>
-      <c r="J555" t="b">
-        <v>0</v>
-      </c>
-      <c r="K555" t="inlineStr"/>
-      <c r="L555" t="inlineStr"/>
-    </row>
-    <row r="556">
-      <c r="A556" t="n">
-        <v>631</v>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C556" t="inlineStr">
-        <is>
-          <t>2026-11-27</t>
-        </is>
-      </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F556" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G556" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H556" t="n">
-        <v>40</v>
-      </c>
-      <c r="I556" t="n">
-        <v>0</v>
-      </c>
-      <c r="J556" t="b">
-        <v>0</v>
-      </c>
-      <c r="K556" t="inlineStr"/>
-      <c r="L556" t="inlineStr"/>
-    </row>
-    <row r="557">
-      <c r="A557" t="n">
-        <v>632</v>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>2026-11-28</t>
-        </is>
-      </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F557" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G557" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H557" t="n">
-        <v>60</v>
-      </c>
-      <c r="I557" t="n">
-        <v>0</v>
-      </c>
-      <c r="J557" t="b">
-        <v>0</v>
-      </c>
-      <c r="K557" t="inlineStr"/>
-      <c r="L557" t="inlineStr"/>
-    </row>
-    <row r="558">
-      <c r="A558" t="n">
-        <v>633</v>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>2026-11-29</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F558" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H558" t="n">
-        <v>120</v>
-      </c>
-      <c r="I558" t="n">
-        <v>0</v>
-      </c>
-      <c r="J558" t="b">
-        <v>0</v>
-      </c>
-      <c r="K558" t="inlineStr"/>
-      <c r="L558" t="inlineStr"/>
-    </row>
-    <row r="559">
-      <c r="A559" t="n">
-        <v>634</v>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F559" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H559" t="n">
-        <v>40</v>
-      </c>
-      <c r="I559" t="n">
-        <v>0</v>
-      </c>
-      <c r="J559" t="b">
-        <v>0</v>
-      </c>
-      <c r="K559" t="inlineStr"/>
-      <c r="L559" t="inlineStr"/>
-    </row>
-    <row r="560">
-      <c r="A560" t="n">
-        <v>635</v>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H560" t="n">
-        <v>40</v>
-      </c>
-      <c r="I560" t="n">
-        <v>0</v>
-      </c>
-      <c r="J560" t="b">
-        <v>0</v>
-      </c>
-      <c r="K560" t="inlineStr"/>
-      <c r="L560" t="inlineStr"/>
-    </row>
-    <row r="561">
-      <c r="A561" t="n">
-        <v>636</v>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F561" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H561" t="n">
-        <v>40</v>
-      </c>
-      <c r="I561" t="n">
-        <v>0</v>
-      </c>
-      <c r="J561" t="b">
-        <v>0</v>
-      </c>
-      <c r="K561" t="inlineStr"/>
-      <c r="L561" t="inlineStr"/>
-    </row>
-    <row r="562">
-      <c r="A562" t="n">
-        <v>637</v>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>2026-12-03</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E562" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F562" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G562" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H562" t="n">
-        <v>40</v>
-      </c>
-      <c r="I562" t="n">
-        <v>0</v>
-      </c>
-      <c r="J562" t="b">
-        <v>0</v>
-      </c>
-      <c r="K562" t="inlineStr"/>
-      <c r="L562" t="inlineStr"/>
-    </row>
-    <row r="563">
-      <c r="A563" t="n">
-        <v>638</v>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E563" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H563" t="n">
-        <v>40</v>
-      </c>
-      <c r="I563" t="n">
-        <v>0</v>
-      </c>
-      <c r="J563" t="b">
-        <v>0</v>
-      </c>
-      <c r="K563" t="inlineStr"/>
-      <c r="L563" t="inlineStr"/>
-    </row>
-    <row r="564">
-      <c r="A564" t="n">
-        <v>639</v>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>2026-12-05</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E564" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H564" t="n">
-        <v>60</v>
-      </c>
-      <c r="I564" t="n">
-        <v>0</v>
-      </c>
-      <c r="J564" t="b">
-        <v>0</v>
-      </c>
-      <c r="K564" t="inlineStr"/>
-      <c r="L564" t="inlineStr"/>
-    </row>
-    <row r="565">
-      <c r="A565" t="n">
-        <v>640</v>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>2026-12-06</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E565" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H565" t="n">
-        <v>120</v>
-      </c>
-      <c r="I565" t="n">
-        <v>0</v>
-      </c>
-      <c r="J565" t="b">
-        <v>0</v>
-      </c>
-      <c r="K565" t="inlineStr"/>
-      <c r="L565" t="inlineStr"/>
-    </row>
-    <row r="566">
-      <c r="A566" t="n">
-        <v>641</v>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>2026-12-07</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E566" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F566" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G566" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H566" t="n">
-        <v>40</v>
-      </c>
-      <c r="I566" t="n">
-        <v>0</v>
-      </c>
-      <c r="J566" t="b">
-        <v>0</v>
-      </c>
-      <c r="K566" t="inlineStr"/>
-      <c r="L566" t="inlineStr"/>
-    </row>
-    <row r="567">
-      <c r="A567" t="n">
-        <v>642</v>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>2026-12-08</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H567" t="n">
-        <v>40</v>
-      </c>
-      <c r="I567" t="n">
-        <v>0</v>
-      </c>
-      <c r="J567" t="b">
-        <v>0</v>
-      </c>
-      <c r="K567" t="inlineStr"/>
-      <c r="L567" t="inlineStr"/>
-    </row>
-    <row r="568">
-      <c r="A568" t="n">
-        <v>643</v>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>2026-12-09</t>
-        </is>
-      </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F568" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G568" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H568" t="n">
-        <v>40</v>
-      </c>
-      <c r="I568" t="n">
-        <v>0</v>
-      </c>
-      <c r="J568" t="b">
-        <v>0</v>
-      </c>
-      <c r="K568" t="inlineStr"/>
-      <c r="L568" t="inlineStr"/>
-    </row>
-    <row r="569">
-      <c r="A569" t="n">
-        <v>644</v>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F569" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G569" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H569" t="n">
-        <v>40</v>
-      </c>
-      <c r="I569" t="n">
-        <v>0</v>
-      </c>
-      <c r="J569" t="b">
-        <v>0</v>
-      </c>
-      <c r="K569" t="inlineStr"/>
-      <c r="L569" t="inlineStr"/>
-    </row>
-    <row r="570">
-      <c r="A570" t="n">
-        <v>645</v>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>2026-12-11</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F570" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H570" t="n">
-        <v>40</v>
-      </c>
-      <c r="I570" t="n">
-        <v>0</v>
-      </c>
-      <c r="J570" t="b">
-        <v>0</v>
-      </c>
-      <c r="K570" t="inlineStr"/>
-      <c r="L570" t="inlineStr"/>
-    </row>
-    <row r="571">
-      <c r="A571" t="n">
-        <v>646</v>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>2026-12-12</t>
-        </is>
-      </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F571" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G571" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H571" t="n">
-        <v>60</v>
-      </c>
-      <c r="I571" t="n">
-        <v>0</v>
-      </c>
-      <c r="J571" t="b">
-        <v>0</v>
-      </c>
-      <c r="K571" t="inlineStr"/>
-      <c r="L571" t="inlineStr"/>
-    </row>
-    <row r="572">
-      <c r="A572" t="n">
-        <v>647</v>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F572" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H572" t="n">
-        <v>120</v>
-      </c>
-      <c r="I572" t="n">
-        <v>0</v>
-      </c>
-      <c r="J572" t="b">
-        <v>0</v>
-      </c>
-      <c r="K572" t="inlineStr"/>
-      <c r="L572" t="inlineStr"/>
-    </row>
-    <row r="573">
-      <c r="A573" t="n">
-        <v>648</v>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C573" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E573" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F573" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G573" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H573" t="n">
-        <v>40</v>
-      </c>
-      <c r="I573" t="n">
-        <v>0</v>
-      </c>
-      <c r="J573" t="b">
-        <v>0</v>
-      </c>
-      <c r="K573" t="inlineStr"/>
-      <c r="L573" t="inlineStr"/>
-    </row>
-    <row r="574">
-      <c r="A574" t="n">
-        <v>649</v>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E574" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F574" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G574" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H574" t="n">
-        <v>40</v>
-      </c>
-      <c r="I574" t="n">
-        <v>0</v>
-      </c>
-      <c r="J574" t="b">
-        <v>0</v>
-      </c>
-      <c r="K574" t="inlineStr"/>
-      <c r="L574" t="inlineStr"/>
-    </row>
-    <row r="575">
-      <c r="A575" t="n">
-        <v>650</v>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E575" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F575" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H575" t="n">
-        <v>40</v>
-      </c>
-      <c r="I575" t="n">
-        <v>0</v>
-      </c>
-      <c r="J575" t="b">
-        <v>0</v>
-      </c>
-      <c r="K575" t="inlineStr"/>
-      <c r="L575" t="inlineStr"/>
-    </row>
-    <row r="576">
-      <c r="A576" t="n">
-        <v>651</v>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F576" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H576" t="n">
-        <v>40</v>
-      </c>
-      <c r="I576" t="n">
-        <v>0</v>
-      </c>
-      <c r="J576" t="b">
-        <v>0</v>
-      </c>
-      <c r="K576" t="inlineStr"/>
-      <c r="L576" t="inlineStr"/>
-    </row>
-    <row r="577">
-      <c r="A577" t="n">
-        <v>652</v>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>2026-12-18</t>
-        </is>
-      </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E577" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F577" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H577" t="n">
-        <v>40</v>
-      </c>
-      <c r="I577" t="n">
-        <v>0</v>
-      </c>
-      <c r="J577" t="b">
-        <v>0</v>
-      </c>
-      <c r="K577" t="inlineStr"/>
-      <c r="L577" t="inlineStr"/>
-    </row>
-    <row r="578">
-      <c r="A578" t="n">
-        <v>653</v>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>2026-12-19</t>
-        </is>
-      </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G578" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H578" t="n">
-        <v>60</v>
-      </c>
-      <c r="I578" t="n">
-        <v>0</v>
-      </c>
-      <c r="J578" t="b">
-        <v>0</v>
-      </c>
-      <c r="K578" t="inlineStr"/>
-      <c r="L578" t="inlineStr"/>
-    </row>
-    <row r="579">
-      <c r="A579" t="n">
-        <v>654</v>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F579" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G579" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H579" t="n">
-        <v>120</v>
-      </c>
-      <c r="I579" t="n">
-        <v>0</v>
-      </c>
-      <c r="J579" t="b">
-        <v>0</v>
-      </c>
-      <c r="K579" t="inlineStr"/>
-      <c r="L579" t="inlineStr"/>
-    </row>
-    <row r="580">
-      <c r="A580" t="n">
-        <v>655</v>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>2026-12-21</t>
-        </is>
-      </c>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F580" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G580" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H580" t="n">
-        <v>40</v>
-      </c>
-      <c r="I580" t="n">
-        <v>0</v>
-      </c>
-      <c r="J580" t="b">
-        <v>0</v>
-      </c>
-      <c r="K580" t="inlineStr"/>
-      <c r="L580" t="inlineStr"/>
-    </row>
-    <row r="581">
-      <c r="A581" t="n">
-        <v>656</v>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr">
-        <is>
-          <t>2026-12-22</t>
-        </is>
-      </c>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F581" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G581" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H581" t="n">
-        <v>40</v>
-      </c>
-      <c r="I581" t="n">
-        <v>0</v>
-      </c>
-      <c r="J581" t="b">
-        <v>0</v>
-      </c>
-      <c r="K581" t="inlineStr"/>
-      <c r="L581" t="inlineStr"/>
-    </row>
-    <row r="582">
-      <c r="A582" t="n">
-        <v>657</v>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F582" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G582" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H582" t="n">
-        <v>40</v>
-      </c>
-      <c r="I582" t="n">
-        <v>0</v>
-      </c>
-      <c r="J582" t="b">
-        <v>0</v>
-      </c>
-      <c r="K582" t="inlineStr"/>
-      <c r="L582" t="inlineStr"/>
-    </row>
-    <row r="583">
-      <c r="A583" t="n">
-        <v>658</v>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>2026-12-24</t>
-        </is>
-      </c>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F583" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G583" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H583" t="n">
-        <v>40</v>
-      </c>
-      <c r="I583" t="n">
-        <v>0</v>
-      </c>
-      <c r="J583" t="b">
-        <v>0</v>
-      </c>
-      <c r="K583" t="inlineStr"/>
-      <c r="L583" t="inlineStr"/>
-    </row>
-    <row r="584">
-      <c r="A584" t="n">
-        <v>659</v>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C584" t="inlineStr">
-        <is>
-          <t>2026-12-25</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E584" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F584" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G584" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H584" t="n">
-        <v>40</v>
-      </c>
-      <c r="I584" t="n">
-        <v>0</v>
-      </c>
-      <c r="J584" t="b">
-        <v>0</v>
-      </c>
-      <c r="K584" t="inlineStr"/>
-      <c r="L584" t="inlineStr"/>
-    </row>
-    <row r="585">
-      <c r="A585" t="n">
-        <v>660</v>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C585" t="inlineStr">
-        <is>
-          <t>2026-12-26</t>
-        </is>
-      </c>
-      <c r="D585" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E585" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F585" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G585" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H585" t="n">
-        <v>60</v>
-      </c>
-      <c r="I585" t="n">
-        <v>0</v>
-      </c>
-      <c r="J585" t="b">
-        <v>0</v>
-      </c>
-      <c r="K585" t="inlineStr"/>
-      <c r="L585" t="inlineStr"/>
-    </row>
-    <row r="586">
-      <c r="A586" t="n">
-        <v>661</v>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>2026-12-27</t>
-        </is>
-      </c>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E586" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F586" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G586" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H586" t="n">
-        <v>120</v>
-      </c>
-      <c r="I586" t="n">
-        <v>0</v>
-      </c>
-      <c r="J586" t="b">
-        <v>0</v>
-      </c>
-      <c r="K586" t="inlineStr"/>
-      <c r="L586" t="inlineStr"/>
-    </row>
-    <row r="587">
-      <c r="A587" t="n">
-        <v>662</v>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>2026-12-28</t>
-        </is>
-      </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E587" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F587" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G587" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H587" t="n">
-        <v>40</v>
-      </c>
-      <c r="I587" t="n">
-        <v>0</v>
-      </c>
-      <c r="J587" t="b">
-        <v>0</v>
-      </c>
-      <c r="K587" t="inlineStr"/>
-      <c r="L587" t="inlineStr"/>
-    </row>
-    <row r="588">
-      <c r="A588" t="n">
-        <v>663</v>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E588" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F588" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G588" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H588" t="n">
-        <v>40</v>
-      </c>
-      <c r="I588" t="n">
-        <v>0</v>
-      </c>
-      <c r="J588" t="b">
-        <v>0</v>
-      </c>
-      <c r="K588" t="inlineStr"/>
-      <c r="L588" t="inlineStr"/>
-    </row>
-    <row r="589">
-      <c r="A589" t="n">
-        <v>664</v>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>2026-12-30</t>
-        </is>
-      </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F589" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H589" t="n">
-        <v>40</v>
-      </c>
-      <c r="I589" t="n">
-        <v>0</v>
-      </c>
-      <c r="J589" t="b">
-        <v>0</v>
-      </c>
-      <c r="K589" t="inlineStr"/>
-      <c r="L589" t="inlineStr"/>
-    </row>
-    <row r="590">
-      <c r="A590" t="n">
-        <v>665</v>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F590" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G590" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H590" t="n">
-        <v>40</v>
-      </c>
-      <c r="I590" t="n">
-        <v>0</v>
-      </c>
-      <c r="J590" t="b">
-        <v>0</v>
-      </c>
-      <c r="K590" t="inlineStr"/>
-      <c r="L590" t="inlineStr"/>
-    </row>
-    <row r="591">
-      <c r="A591" t="n">
-        <v>666</v>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
-      </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E591" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F591" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G591" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H591" t="n">
-        <v>40</v>
-      </c>
-      <c r="I591" t="n">
-        <v>0</v>
-      </c>
-      <c r="J591" t="b">
-        <v>0</v>
-      </c>
-      <c r="K591" t="inlineStr"/>
-      <c r="L591" t="inlineStr"/>
-    </row>
-    <row r="592">
-      <c r="A592" t="n">
-        <v>667</v>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>2027-01-02</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F592" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H592" t="n">
-        <v>60</v>
-      </c>
-      <c r="I592" t="n">
-        <v>0</v>
-      </c>
-      <c r="J592" t="b">
-        <v>0</v>
-      </c>
-      <c r="K592" t="inlineStr"/>
-      <c r="L592" t="inlineStr"/>
-    </row>
-    <row r="593">
-      <c r="A593" t="n">
-        <v>668</v>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>2027-01-03</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F593" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G593" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H593" t="n">
-        <v>120</v>
-      </c>
-      <c r="I593" t="n">
-        <v>0</v>
-      </c>
-      <c r="J593" t="b">
-        <v>0</v>
-      </c>
-      <c r="K593" t="inlineStr"/>
-      <c r="L593" t="inlineStr"/>
-    </row>
-    <row r="594">
-      <c r="A594" t="n">
-        <v>669</v>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>2027-01-04</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F594" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G594" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H594" t="n">
-        <v>40</v>
-      </c>
-      <c r="I594" t="n">
-        <v>0</v>
-      </c>
-      <c r="J594" t="b">
-        <v>0</v>
-      </c>
-      <c r="K594" t="inlineStr"/>
-      <c r="L594" t="inlineStr"/>
-    </row>
-    <row r="595">
-      <c r="A595" t="n">
-        <v>670</v>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>2027-01-05</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F595" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G595" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H595" t="n">
-        <v>40</v>
-      </c>
-      <c r="I595" t="n">
-        <v>0</v>
-      </c>
-      <c r="J595" t="b">
-        <v>0</v>
-      </c>
-      <c r="K595" t="inlineStr"/>
-      <c r="L595" t="inlineStr"/>
-    </row>
-    <row r="596">
-      <c r="A596" t="n">
-        <v>671</v>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>2027-01-06</t>
-        </is>
-      </c>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F596" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G596" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H596" t="n">
-        <v>40</v>
-      </c>
-      <c r="I596" t="n">
-        <v>0</v>
-      </c>
-      <c r="J596" t="b">
-        <v>0</v>
-      </c>
-      <c r="K596" t="inlineStr"/>
-      <c r="L596" t="inlineStr"/>
-    </row>
-    <row r="597">
-      <c r="A597" t="n">
-        <v>672</v>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>2027-01-07</t>
-        </is>
-      </c>
-      <c r="D597" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F597" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G597" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H597" t="n">
-        <v>40</v>
-      </c>
-      <c r="I597" t="n">
-        <v>0</v>
-      </c>
-      <c r="J597" t="b">
-        <v>0</v>
-      </c>
-      <c r="K597" t="inlineStr"/>
-      <c r="L597" t="inlineStr"/>
-    </row>
-    <row r="598">
-      <c r="A598" t="n">
-        <v>673</v>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>2027-01-08</t>
-        </is>
-      </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F598" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G598" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H598" t="n">
-        <v>40</v>
-      </c>
-      <c r="I598" t="n">
-        <v>0</v>
-      </c>
-      <c r="J598" t="b">
-        <v>0</v>
-      </c>
-      <c r="K598" t="inlineStr"/>
-      <c r="L598" t="inlineStr"/>
-    </row>
-    <row r="599">
-      <c r="A599" t="n">
-        <v>674</v>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>2027-01-09</t>
-        </is>
-      </c>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F599" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G599" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H599" t="n">
-        <v>60</v>
-      </c>
-      <c r="I599" t="n">
-        <v>0</v>
-      </c>
-      <c r="J599" t="b">
-        <v>0</v>
-      </c>
-      <c r="K599" t="inlineStr"/>
-      <c r="L599" t="inlineStr"/>
-    </row>
-    <row r="600">
-      <c r="A600" t="n">
-        <v>675</v>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>2027-01-10</t>
-        </is>
-      </c>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E600" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F600" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G600" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H600" t="n">
-        <v>120</v>
-      </c>
-      <c r="I600" t="n">
-        <v>0</v>
-      </c>
-      <c r="J600" t="b">
-        <v>0</v>
-      </c>
-      <c r="K600" t="inlineStr"/>
-      <c r="L600" t="inlineStr"/>
-    </row>
-    <row r="601">
-      <c r="A601" t="n">
-        <v>676</v>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>2027-01-11</t>
-        </is>
-      </c>
-      <c r="D601" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F601" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H601" t="n">
-        <v>40</v>
-      </c>
-      <c r="I601" t="n">
-        <v>0</v>
-      </c>
-      <c r="J601" t="b">
-        <v>0</v>
-      </c>
-      <c r="K601" t="inlineStr"/>
-      <c r="L601" t="inlineStr"/>
-    </row>
-    <row r="602">
-      <c r="A602" t="n">
-        <v>677</v>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>2027-01-12</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F602" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G602" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H602" t="n">
-        <v>40</v>
-      </c>
-      <c r="I602" t="n">
-        <v>0</v>
-      </c>
-      <c r="J602" t="b">
-        <v>0</v>
-      </c>
-      <c r="K602" t="inlineStr"/>
-      <c r="L602" t="inlineStr"/>
-    </row>
-    <row r="603">
-      <c r="A603" t="n">
-        <v>678</v>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>2027-01-13</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F603" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H603" t="n">
-        <v>40</v>
-      </c>
-      <c r="I603" t="n">
-        <v>0</v>
-      </c>
-      <c r="J603" t="b">
-        <v>0</v>
-      </c>
-      <c r="K603" t="inlineStr"/>
-      <c r="L603" t="inlineStr"/>
-    </row>
-    <row r="604">
-      <c r="A604" t="n">
-        <v>679</v>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>2027-01-14</t>
-        </is>
-      </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E604" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F604" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G604" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H604" t="n">
-        <v>40</v>
-      </c>
-      <c r="I604" t="n">
-        <v>0</v>
-      </c>
-      <c r="J604" t="b">
-        <v>0</v>
-      </c>
-      <c r="K604" t="inlineStr"/>
-      <c r="L604" t="inlineStr"/>
-    </row>
-    <row r="605">
-      <c r="A605" t="n">
-        <v>680</v>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>2027-01-15</t>
-        </is>
-      </c>
-      <c r="D605" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F605" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G605" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H605" t="n">
-        <v>40</v>
-      </c>
-      <c r="I605" t="n">
-        <v>0</v>
-      </c>
-      <c r="J605" t="b">
-        <v>0</v>
-      </c>
-      <c r="K605" t="inlineStr"/>
-      <c r="L605" t="inlineStr"/>
-    </row>
-    <row r="606">
-      <c r="A606" t="n">
-        <v>681</v>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>2027-01-16</t>
-        </is>
-      </c>
-      <c r="D606" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E606" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F606" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G606" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H606" t="n">
-        <v>60</v>
-      </c>
-      <c r="I606" t="n">
-        <v>0</v>
-      </c>
-      <c r="J606" t="b">
-        <v>0</v>
-      </c>
-      <c r="K606" t="inlineStr"/>
-      <c r="L606" t="inlineStr"/>
-    </row>
-    <row r="607">
-      <c r="A607" t="n">
-        <v>682</v>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>2027-01-17</t>
-        </is>
-      </c>
-      <c r="D607" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F607" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G607" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H607" t="n">
-        <v>120</v>
-      </c>
-      <c r="I607" t="n">
-        <v>0</v>
-      </c>
-      <c r="J607" t="b">
-        <v>0</v>
-      </c>
-      <c r="K607" t="inlineStr"/>
-      <c r="L607" t="inlineStr"/>
-    </row>
-    <row r="608">
-      <c r="A608" t="n">
-        <v>683</v>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>2027-01-18</t>
-        </is>
-      </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E608" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F608" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G608" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H608" t="n">
-        <v>40</v>
-      </c>
-      <c r="I608" t="n">
-        <v>0</v>
-      </c>
-      <c r="J608" t="b">
-        <v>0</v>
-      </c>
-      <c r="K608" t="inlineStr"/>
-      <c r="L608" t="inlineStr"/>
-    </row>
-    <row r="609">
-      <c r="A609" t="n">
-        <v>684</v>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>2027-01-19</t>
-        </is>
-      </c>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E609" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F609" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G609" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H609" t="n">
-        <v>40</v>
-      </c>
-      <c r="I609" t="n">
-        <v>0</v>
-      </c>
-      <c r="J609" t="b">
-        <v>0</v>
-      </c>
-      <c r="K609" t="inlineStr"/>
-      <c r="L609" t="inlineStr"/>
-    </row>
-    <row r="610">
-      <c r="A610" t="n">
-        <v>685</v>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-      <c r="D610" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E610" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F610" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G610" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H610" t="n">
-        <v>40</v>
-      </c>
-      <c r="I610" t="n">
-        <v>0</v>
-      </c>
-      <c r="J610" t="b">
-        <v>0</v>
-      </c>
-      <c r="K610" t="inlineStr"/>
-      <c r="L610" t="inlineStr"/>
-    </row>
-    <row r="611">
-      <c r="A611" t="n">
-        <v>686</v>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>2027-01-21</t>
-        </is>
-      </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E611" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F611" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G611" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H611" t="n">
-        <v>40</v>
-      </c>
-      <c r="I611" t="n">
-        <v>0</v>
-      </c>
-      <c r="J611" t="b">
-        <v>0</v>
-      </c>
-      <c r="K611" t="inlineStr"/>
-      <c r="L611" t="inlineStr"/>
-    </row>
-    <row r="612">
-      <c r="A612" t="n">
-        <v>687</v>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>2027-01-22</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E612" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F612" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G612" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H612" t="n">
-        <v>40</v>
-      </c>
-      <c r="I612" t="n">
-        <v>0</v>
-      </c>
-      <c r="J612" t="b">
-        <v>0</v>
-      </c>
-      <c r="K612" t="inlineStr"/>
-      <c r="L612" t="inlineStr"/>
-    </row>
-    <row r="613">
-      <c r="A613" t="n">
-        <v>688</v>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>2027-01-23</t>
-        </is>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E613" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F613" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G613" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H613" t="n">
-        <v>60</v>
-      </c>
-      <c r="I613" t="n">
-        <v>0</v>
-      </c>
-      <c r="J613" t="b">
-        <v>0</v>
-      </c>
-      <c r="K613" t="inlineStr"/>
-      <c r="L613" t="inlineStr"/>
-    </row>
-    <row r="614">
-      <c r="A614" t="n">
-        <v>689</v>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>2027-01-24</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E614" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F614" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G614" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H614" t="n">
-        <v>120</v>
-      </c>
-      <c r="I614" t="n">
-        <v>0</v>
-      </c>
-      <c r="J614" t="b">
-        <v>0</v>
-      </c>
-      <c r="K614" t="inlineStr"/>
-      <c r="L614" t="inlineStr"/>
-    </row>
-    <row r="615">
-      <c r="A615" t="n">
-        <v>690</v>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>2027-01-25</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E615" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F615" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G615" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H615" t="n">
-        <v>40</v>
-      </c>
-      <c r="I615" t="n">
-        <v>0</v>
-      </c>
-      <c r="J615" t="b">
-        <v>0</v>
-      </c>
-      <c r="K615" t="inlineStr"/>
-      <c r="L615" t="inlineStr"/>
-    </row>
-    <row r="616">
-      <c r="A616" t="n">
-        <v>691</v>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>2027-01-26</t>
-        </is>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E616" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F616" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G616" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H616" t="n">
-        <v>40</v>
-      </c>
-      <c r="I616" t="n">
-        <v>0</v>
-      </c>
-      <c r="J616" t="b">
-        <v>0</v>
-      </c>
-      <c r="K616" t="inlineStr"/>
-      <c r="L616" t="inlineStr"/>
-    </row>
-    <row r="617">
-      <c r="A617" t="n">
-        <v>692</v>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>2027-01-27</t>
-        </is>
-      </c>
-      <c r="D617" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E617" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F617" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G617" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H617" t="n">
-        <v>40</v>
-      </c>
-      <c r="I617" t="n">
-        <v>0</v>
-      </c>
-      <c r="J617" t="b">
-        <v>0</v>
-      </c>
-      <c r="K617" t="inlineStr"/>
-      <c r="L617" t="inlineStr"/>
-    </row>
-    <row r="618">
-      <c r="A618" t="n">
-        <v>693</v>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>2027-01-28</t>
-        </is>
-      </c>
-      <c r="D618" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E618" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F618" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G618" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H618" t="n">
-        <v>40</v>
-      </c>
-      <c r="I618" t="n">
-        <v>0</v>
-      </c>
-      <c r="J618" t="b">
-        <v>0</v>
-      </c>
-      <c r="K618" t="inlineStr"/>
-      <c r="L618" t="inlineStr"/>
-    </row>
-    <row r="619">
-      <c r="A619" t="n">
-        <v>694</v>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>2027-01-29</t>
-        </is>
-      </c>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E619" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F619" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G619" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H619" t="n">
-        <v>40</v>
-      </c>
-      <c r="I619" t="n">
-        <v>0</v>
-      </c>
-      <c r="J619" t="b">
-        <v>0</v>
-      </c>
-      <c r="K619" t="inlineStr"/>
-      <c r="L619" t="inlineStr"/>
-    </row>
-    <row r="620">
-      <c r="A620" t="n">
-        <v>695</v>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>2027-01-30</t>
-        </is>
-      </c>
-      <c r="D620" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E620" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F620" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G620" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H620" t="n">
-        <v>60</v>
-      </c>
-      <c r="I620" t="n">
-        <v>0</v>
-      </c>
-      <c r="J620" t="b">
-        <v>0</v>
-      </c>
-      <c r="K620" t="inlineStr"/>
-      <c r="L620" t="inlineStr"/>
-    </row>
-    <row r="621">
-      <c r="A621" t="n">
-        <v>696</v>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>2027-01-31</t>
-        </is>
-      </c>
-      <c r="D621" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E621" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F621" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G621" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H621" t="n">
-        <v>120</v>
-      </c>
-      <c r="I621" t="n">
-        <v>0</v>
-      </c>
-      <c r="J621" t="b">
-        <v>0</v>
-      </c>
-      <c r="K621" t="inlineStr"/>
-      <c r="L621" t="inlineStr"/>
-    </row>
-    <row r="622">
-      <c r="A622" t="n">
-        <v>697</v>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>2027-02-01</t>
-        </is>
-      </c>
-      <c r="D622" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E622" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F622" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G622" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H622" t="n">
-        <v>40</v>
-      </c>
-      <c r="I622" t="n">
-        <v>0</v>
-      </c>
-      <c r="J622" t="b">
-        <v>0</v>
-      </c>
-      <c r="K622" t="inlineStr"/>
-      <c r="L622" t="inlineStr"/>
-    </row>
-    <row r="623">
-      <c r="A623" t="n">
-        <v>698</v>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>2027-02-02</t>
-        </is>
-      </c>
-      <c r="D623" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F623" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G623" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H623" t="n">
-        <v>40</v>
-      </c>
-      <c r="I623" t="n">
-        <v>0</v>
-      </c>
-      <c r="J623" t="b">
-        <v>0</v>
-      </c>
-      <c r="K623" t="inlineStr"/>
-      <c r="L623" t="inlineStr"/>
-    </row>
-    <row r="624">
-      <c r="A624" t="n">
-        <v>699</v>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>2027-02-03</t>
-        </is>
-      </c>
-      <c r="D624" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E624" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F624" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G624" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H624" t="n">
-        <v>40</v>
-      </c>
-      <c r="I624" t="n">
-        <v>0</v>
-      </c>
-      <c r="J624" t="b">
-        <v>0</v>
-      </c>
-      <c r="K624" t="inlineStr"/>
-      <c r="L624" t="inlineStr"/>
-    </row>
-    <row r="625">
-      <c r="A625" t="n">
-        <v>700</v>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>2027-02-04</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E625" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F625" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G625" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H625" t="n">
-        <v>40</v>
-      </c>
-      <c r="I625" t="n">
-        <v>0</v>
-      </c>
-      <c r="J625" t="b">
-        <v>0</v>
-      </c>
-      <c r="K625" t="inlineStr"/>
-      <c r="L625" t="inlineStr"/>
-    </row>
-    <row r="626">
-      <c r="A626" t="n">
-        <v>701</v>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>2027-02-05</t>
-        </is>
-      </c>
-      <c r="D626" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E626" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F626" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G626" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H626" t="n">
-        <v>40</v>
-      </c>
-      <c r="I626" t="n">
-        <v>0</v>
-      </c>
-      <c r="J626" t="b">
-        <v>0</v>
-      </c>
-      <c r="K626" t="inlineStr"/>
-      <c r="L626" t="inlineStr"/>
-    </row>
-    <row r="627">
-      <c r="A627" t="n">
-        <v>702</v>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>2027-02-06</t>
-        </is>
-      </c>
-      <c r="D627" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E627" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F627" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G627" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H627" t="n">
-        <v>60</v>
-      </c>
-      <c r="I627" t="n">
-        <v>0</v>
-      </c>
-      <c r="J627" t="b">
-        <v>0</v>
-      </c>
-      <c r="K627" t="inlineStr"/>
-      <c r="L627" t="inlineStr"/>
-    </row>
-    <row r="628">
-      <c r="A628" t="n">
-        <v>703</v>
-      </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>2027-02-07</t>
-        </is>
-      </c>
-      <c r="D628" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E628" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F628" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G628" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H628" t="n">
-        <v>120</v>
-      </c>
-      <c r="I628" t="n">
-        <v>0</v>
-      </c>
-      <c r="J628" t="b">
-        <v>0</v>
-      </c>
-      <c r="K628" t="inlineStr"/>
-      <c r="L628" t="inlineStr"/>
-    </row>
-    <row r="629">
-      <c r="A629" t="n">
-        <v>704</v>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>2027-02-08</t>
-        </is>
-      </c>
-      <c r="D629" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E629" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F629" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G629" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H629" t="n">
-        <v>40</v>
-      </c>
-      <c r="I629" t="n">
-        <v>0</v>
-      </c>
-      <c r="J629" t="b">
-        <v>0</v>
-      </c>
-      <c r="K629" t="inlineStr"/>
-      <c r="L629" t="inlineStr"/>
-    </row>
-    <row r="630">
-      <c r="A630" t="n">
-        <v>705</v>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>2027-02-09</t>
-        </is>
-      </c>
-      <c r="D630" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E630" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F630" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G630" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H630" t="n">
-        <v>40</v>
-      </c>
-      <c r="I630" t="n">
-        <v>0</v>
-      </c>
-      <c r="J630" t="b">
-        <v>0</v>
-      </c>
-      <c r="K630" t="inlineStr"/>
-      <c r="L630" t="inlineStr"/>
-    </row>
-    <row r="631">
-      <c r="A631" t="n">
-        <v>706</v>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
-      </c>
-      <c r="D631" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E631" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F631" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G631" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H631" t="n">
-        <v>40</v>
-      </c>
-      <c r="I631" t="n">
-        <v>0</v>
-      </c>
-      <c r="J631" t="b">
-        <v>0</v>
-      </c>
-      <c r="K631" t="inlineStr"/>
-      <c r="L631" t="inlineStr"/>
-    </row>
-    <row r="632">
-      <c r="A632" t="n">
-        <v>707</v>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
-        <is>
-          <t>2027-02-11</t>
-        </is>
-      </c>
-      <c r="D632" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E632" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F632" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G632" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H632" t="n">
-        <v>40</v>
-      </c>
-      <c r="I632" t="n">
-        <v>0</v>
-      </c>
-      <c r="J632" t="b">
-        <v>0</v>
-      </c>
-      <c r="K632" t="inlineStr"/>
-      <c r="L632" t="inlineStr"/>
-    </row>
-    <row r="633">
-      <c r="A633" t="n">
-        <v>708</v>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
-        <is>
-          <t>2027-02-12</t>
-        </is>
-      </c>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E633" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F633" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G633" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H633" t="n">
-        <v>40</v>
-      </c>
-      <c r="I633" t="n">
-        <v>0</v>
-      </c>
-      <c r="J633" t="b">
-        <v>0</v>
-      </c>
-      <c r="K633" t="inlineStr"/>
-      <c r="L633" t="inlineStr"/>
-    </row>
-    <row r="634">
-      <c r="A634" t="n">
-        <v>709</v>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>2027-02-13</t>
-        </is>
-      </c>
-      <c r="D634" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F634" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G634" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H634" t="n">
-        <v>60</v>
-      </c>
-      <c r="I634" t="n">
-        <v>0</v>
-      </c>
-      <c r="J634" t="b">
-        <v>0</v>
-      </c>
-      <c r="K634" t="inlineStr"/>
-      <c r="L634" t="inlineStr"/>
-    </row>
-    <row r="635">
-      <c r="A635" t="n">
-        <v>710</v>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>2027-02-14</t>
-        </is>
-      </c>
-      <c r="D635" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E635" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F635" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G635" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H635" t="n">
-        <v>120</v>
-      </c>
-      <c r="I635" t="n">
-        <v>0</v>
-      </c>
-      <c r="J635" t="b">
-        <v>0</v>
-      </c>
-      <c r="K635" t="inlineStr"/>
-      <c r="L635" t="inlineStr"/>
-    </row>
-    <row r="636">
-      <c r="A636" t="n">
-        <v>711</v>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>2027-02-15</t>
-        </is>
-      </c>
-      <c r="D636" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E636" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F636" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G636" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H636" t="n">
-        <v>40</v>
-      </c>
-      <c r="I636" t="n">
-        <v>0</v>
-      </c>
-      <c r="J636" t="b">
-        <v>0</v>
-      </c>
-      <c r="K636" t="inlineStr"/>
-      <c r="L636" t="inlineStr"/>
-    </row>
-    <row r="637">
-      <c r="A637" t="n">
-        <v>712</v>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>2027-02-16</t>
-        </is>
-      </c>
-      <c r="D637" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E637" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F637" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H637" t="n">
-        <v>40</v>
-      </c>
-      <c r="I637" t="n">
-        <v>0</v>
-      </c>
-      <c r="J637" t="b">
-        <v>0</v>
-      </c>
-      <c r="K637" t="inlineStr"/>
-      <c r="L637" t="inlineStr"/>
-    </row>
-    <row r="638">
-      <c r="A638" t="n">
-        <v>713</v>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>2027-02-17</t>
-        </is>
-      </c>
-      <c r="D638" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F638" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G638" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H638" t="n">
-        <v>40</v>
-      </c>
-      <c r="I638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J638" t="b">
-        <v>0</v>
-      </c>
-      <c r="K638" t="inlineStr"/>
-      <c r="L638" t="inlineStr"/>
-    </row>
-    <row r="639">
-      <c r="A639" t="n">
-        <v>714</v>
-      </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>2027-02-18</t>
-        </is>
-      </c>
-      <c r="D639" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E639" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F639" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G639" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H639" t="n">
-        <v>40</v>
-      </c>
-      <c r="I639" t="n">
-        <v>0</v>
-      </c>
-      <c r="J639" t="b">
-        <v>0</v>
-      </c>
-      <c r="K639" t="inlineStr"/>
-      <c r="L639" t="inlineStr"/>
-    </row>
-    <row r="640">
-      <c r="A640" t="n">
-        <v>715</v>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>2027-02-19</t>
-        </is>
-      </c>
-      <c r="D640" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F640" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G640" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H640" t="n">
-        <v>40</v>
-      </c>
-      <c r="I640" t="n">
-        <v>0</v>
-      </c>
-      <c r="J640" t="b">
-        <v>0</v>
-      </c>
-      <c r="K640" t="inlineStr"/>
-      <c r="L640" t="inlineStr"/>
-    </row>
-    <row r="641">
-      <c r="A641" t="n">
-        <v>716</v>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr">
-        <is>
-          <t>2027-02-20</t>
-        </is>
-      </c>
-      <c r="D641" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E641" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F641" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G641" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H641" t="n">
-        <v>60</v>
-      </c>
-      <c r="I641" t="n">
-        <v>0</v>
-      </c>
-      <c r="J641" t="b">
-        <v>0</v>
-      </c>
-      <c r="K641" t="inlineStr"/>
-      <c r="L641" t="inlineStr"/>
-    </row>
-    <row r="642">
-      <c r="A642" t="n">
-        <v>717</v>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>2027-02-21</t>
-        </is>
-      </c>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E642" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F642" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G642" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H642" t="n">
-        <v>120</v>
-      </c>
-      <c r="I642" t="n">
-        <v>0</v>
-      </c>
-      <c r="J642" t="b">
-        <v>0</v>
-      </c>
-      <c r="K642" t="inlineStr"/>
-      <c r="L642" t="inlineStr"/>
-    </row>
-    <row r="643">
-      <c r="A643" t="n">
-        <v>718</v>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>2027-02-22</t>
-        </is>
-      </c>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E643" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F643" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G643" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H643" t="n">
-        <v>40</v>
-      </c>
-      <c r="I643" t="n">
-        <v>0</v>
-      </c>
-      <c r="J643" t="b">
-        <v>0</v>
-      </c>
-      <c r="K643" t="inlineStr"/>
-      <c r="L643" t="inlineStr"/>
-    </row>
-    <row r="644">
-      <c r="A644" t="n">
-        <v>719</v>
-      </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>2027-02-23</t>
-        </is>
-      </c>
-      <c r="D644" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F644" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G644" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H644" t="n">
-        <v>40</v>
-      </c>
-      <c r="I644" t="n">
-        <v>0</v>
-      </c>
-      <c r="J644" t="b">
-        <v>0</v>
-      </c>
-      <c r="K644" t="inlineStr"/>
-      <c r="L644" t="inlineStr"/>
-    </row>
-    <row r="645">
-      <c r="A645" t="n">
-        <v>720</v>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>2027-02-24</t>
-        </is>
-      </c>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E645" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F645" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G645" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H645" t="n">
-        <v>40</v>
-      </c>
-      <c r="I645" t="n">
-        <v>0</v>
-      </c>
-      <c r="J645" t="b">
-        <v>0</v>
-      </c>
-      <c r="K645" t="inlineStr"/>
-      <c r="L645" t="inlineStr"/>
-    </row>
-    <row r="646">
-      <c r="A646" t="n">
-        <v>721</v>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>2027-02-25</t>
-        </is>
-      </c>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E646" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F646" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G646" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H646" t="n">
-        <v>40</v>
-      </c>
-      <c r="I646" t="n">
-        <v>0</v>
-      </c>
-      <c r="J646" t="b">
-        <v>0</v>
-      </c>
-      <c r="K646" t="inlineStr"/>
-      <c r="L646" t="inlineStr"/>
-    </row>
-    <row r="647">
-      <c r="A647" t="n">
-        <v>722</v>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>2027-02-26</t>
-        </is>
-      </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>4:00</t>
-        </is>
-      </c>
-      <c r="E647" t="inlineStr">
-        <is>
-          <t>English Live - Conversação em grupo</t>
-        </is>
-      </c>
-      <c r="F647" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G647" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H647" t="n">
-        <v>40</v>
-      </c>
-      <c r="I647" t="n">
-        <v>0</v>
-      </c>
-      <c r="J647" t="b">
-        <v>0</v>
-      </c>
-      <c r="K647" t="inlineStr"/>
-      <c r="L647" t="inlineStr"/>
-    </row>
-    <row r="648">
-      <c r="A648" t="n">
-        <v>723</v>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>2027-02-27</t>
-        </is>
-      </c>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E648" t="inlineStr">
-        <is>
-          <t>Livro/Leitura</t>
-        </is>
-      </c>
-      <c r="F648" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G648" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H648" t="n">
-        <v>60</v>
-      </c>
-      <c r="I648" t="n">
-        <v>0</v>
-      </c>
-      <c r="J648" t="b">
-        <v>0</v>
-      </c>
-      <c r="K648" t="inlineStr"/>
-      <c r="L648" t="inlineStr"/>
-    </row>
-    <row r="649">
-      <c r="A649" t="n">
-        <v>724</v>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>2027-02-28</t>
-        </is>
-      </c>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>5:00</t>
-        </is>
-      </c>
-      <c r="E649" t="inlineStr">
-        <is>
-          <t>Podcast em inglês</t>
-        </is>
-      </c>
-      <c r="F649" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-      <c r="G649" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H649" t="n">
-        <v>120</v>
-      </c>
-      <c r="I649" t="n">
-        <v>0</v>
-      </c>
-      <c r="J649" t="b">
-        <v>0</v>
-      </c>
-      <c r="K649" t="inlineStr"/>
-      <c r="L649" t="inlineStr"/>
-    </row>
-    <row r="650">
-      <c r="A650" t="n">
-        <v>725</v>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
-      </c>
-      <c r="D650" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="E650" t="inlineStr">
-        <is>
-          <t>English Live - Exercício de gramática</t>
-        </is>
-      </c>
-      <c r="F650" t="inlineStr">
-        <is>
-          <t>Grammar</t>
-        </is>
-      </c>
-      <c r="G650" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H650" t="n">
-        <v>40</v>
-      </c>
-      <c r="I650" t="n">
-        <v>0</v>
-      </c>
-      <c r="J650" t="b">
-        <v>0</v>
-      </c>
-      <c r="K650" t="inlineStr"/>
-      <c r="L650" t="inlineStr"/>
-    </row>
-    <row r="651">
-      <c r="A651" t="n">
-        <v>726</v>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>2027-03-02</t>
-        </is>
-      </c>
-      <c r="D651" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="E651" t="inlineStr">
-        <is>
-          <t>English Live - Aula com professor</t>
-        </is>
-      </c>
-      <c r="F651" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G651" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H651" t="n">
-        <v>40</v>
-      </c>
-      <c r="I651" t="n">
-        <v>0</v>
-      </c>
-      <c r="J651" t="b">
-        <v>0</v>
-      </c>
-      <c r="K651" t="inlineStr"/>
-      <c r="L651" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30418,7 +22042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30481,34 +22105,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Time Fluência</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>#f97316</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>05744ee6ac5e4d4d6fe17c3a30ff222ac662743a1753c992914ca8a034ae9f66</t>
-        </is>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18714,10 +18714,14 @@
         <v>30</v>
       </c>
       <c r="J397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-09-03 03:12</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18807,13 +18807,17 @@
         <v>60</v>
       </c>
       <c r="I399" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr"/>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:19</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -18810,14 +18810,10 @@
         <v>60</v>
       </c>
       <c r="J399" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>2026-09-03 10:19</t>
-        </is>
-      </c>
+      <c r="L399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L469"/>
+  <dimension ref="A1:L470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22034,6 +22034,52 @@
       </c>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>545</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Darlei</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texto com audio Mairo Vergara </t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Mairo Vergara</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>30</v>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J470" t="b">
+        <v>0</v>
+      </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -22073,13 +22073,17 @@
         <v>30</v>
       </c>
       <c r="I470" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J470" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K470" t="inlineStr"/>
-      <c r="L470" t="inlineStr"/>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:20</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -50810,7 +50810,7 @@
         </is>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -29221,13 +29221,17 @@
         <v>40</v>
       </c>
       <c r="I626" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J626" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K626" t="inlineStr"/>
-      <c r="L626" t="inlineStr"/>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:04</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -29224,14 +29224,10 @@
         <v>40</v>
       </c>
       <c r="J626" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K626" t="inlineStr"/>
-      <c r="L626" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:04</t>
-        </is>
-      </c>
+      <c r="L626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -48357,13 +48357,17 @@
         <v>15</v>
       </c>
       <c r="I1042" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1042" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1042" t="inlineStr"/>
-      <c r="L1042" t="inlineStr"/>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:17</t>
+        </is>
+      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -48360,14 +48360,10 @@
         <v>15</v>
       </c>
       <c r="J1042" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1042" t="inlineStr"/>
-      <c r="L1042" t="inlineStr">
-        <is>
-          <t>2026-09-03 14:17</t>
-        </is>
-      </c>
+      <c r="L1042" t="inlineStr"/>
     </row>
     <row r="1043">
       <c r="A1043" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -517,13 +517,17 @@
         <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-09-03 14:54</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -567,13 +567,17 @@
         <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:02</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -663,13 +663,17 @@
         <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-04 03:19</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -617,13 +617,17 @@
         <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:06</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -717,13 +717,17 @@
         <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:06</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1612"/>
+  <dimension ref="A1:L1613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74604,6 +74604,52 @@
       </c>
       <c r="K1612" t="inlineStr"/>
       <c r="L1612" t="inlineStr"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="n">
+        <v>2080</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Darlei Delfino</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>Assistir videos em Ingles</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1613" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1613" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1613" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1613" t="inlineStr"/>
+      <c r="L1613" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -74643,13 +74643,17 @@
         <v>10</v>
       </c>
       <c r="I1613" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1613" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1613" t="inlineStr"/>
-      <c r="L1613" t="inlineStr"/>
+      <c r="L1613" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:46</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1613"/>
+  <dimension ref="A1:L1614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74654,6 +74654,52 @@
           <t>2026-09-04 12:46</t>
         </is>
       </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="n">
+        <v>2081</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Darlei Delfino</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English Live - Aula com professor - Venesa </t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>English Live</t>
+        </is>
+      </c>
+      <c r="H1614" t="n">
+        <v>40</v>
+      </c>
+      <c r="I1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1614" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1614" t="inlineStr"/>
+      <c r="L1614" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -74693,13 +74693,17 @@
         <v>40</v>
       </c>
       <c r="I1614" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1614" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1614" t="inlineStr"/>
-      <c r="L1614" t="inlineStr"/>
+      <c r="L1614" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:49</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1614"/>
+  <dimension ref="A1:L1615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74704,6 +74704,52 @@
           <t>2026-09-04 13:49</t>
         </is>
       </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="n">
+        <v>2082</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Darlei Delfino</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>Aula</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>English Live</t>
+        </is>
+      </c>
+      <c r="H1615" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1615" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1615" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1615" t="inlineStr"/>
+      <c r="L1615" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -74726,7 +74726,7 @@
       </c>
       <c r="E1615" t="inlineStr">
         <is>
-          <t>Aula</t>
+          <t>Mairo Vergara - Aula Tarefas</t>
         </is>
       </c>
       <c r="F1615" t="inlineStr">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1615"/>
+  <dimension ref="A1:L1614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74704,52 +74704,6 @@
           <t>2026-09-04 13:49</t>
         </is>
       </c>
-    </row>
-    <row r="1615">
-      <c r="A1615" t="n">
-        <v>2082</v>
-      </c>
-      <c r="B1615" t="inlineStr">
-        <is>
-          <t>Darlei Delfino</t>
-        </is>
-      </c>
-      <c r="C1615" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D1615" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E1615" t="inlineStr">
-        <is>
-          <t>Mairo Vergara - Aula Tarefas</t>
-        </is>
-      </c>
-      <c r="F1615" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G1615" t="inlineStr">
-        <is>
-          <t>English Live</t>
-        </is>
-      </c>
-      <c r="H1615" t="n">
-        <v>30</v>
-      </c>
-      <c r="I1615" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1615" t="b">
-        <v>0</v>
-      </c>
-      <c r="K1615" t="inlineStr"/>
-      <c r="L1615" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1615"/>
+  <dimension ref="A1:L1614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74704,52 +74704,6 @@
           <t>2026-09-04 13:49</t>
         </is>
       </c>
-    </row>
-    <row r="1615">
-      <c r="A1615" t="n">
-        <v>2082</v>
-      </c>
-      <c r="B1615" t="inlineStr">
-        <is>
-          <t>Darlei Delfino</t>
-        </is>
-      </c>
-      <c r="C1615" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D1615" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E1615" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="F1615" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G1615" t="inlineStr">
-        <is>
-          <t>English Live</t>
-        </is>
-      </c>
-      <c r="H1615" t="n">
-        <v>30</v>
-      </c>
-      <c r="I1615" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1615" t="b">
-        <v>0</v>
-      </c>
-      <c r="K1615" t="inlineStr"/>
-      <c r="L1615" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -813,7 +813,7 @@
         <v>40</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -816,10 +816,14 @@
         <v>45</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-05 02:16</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -909,13 +909,17 @@
         <v>30</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-05 09:54</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -74751,7 +74751,7 @@
         <v>60</v>
       </c>
       <c r="I1615" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1615" t="b">
         <v>0</v>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -74797,7 +74797,7 @@
         <v>40</v>
       </c>
       <c r="I1616" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1616" t="b">
         <v>0</v>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -74843,13 +74843,17 @@
         <v>40</v>
       </c>
       <c r="I1617" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1617" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1617" t="inlineStr"/>
-      <c r="L1617" t="inlineStr"/>
+      <c r="L1617" t="inlineStr">
+        <is>
+          <t>2026-09-05 11:01</t>
+        </is>
+      </c>
     </row>
     <row r="1618">
       <c r="A1618" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -74846,14 +74846,10 @@
         <v>40</v>
       </c>
       <c r="J1617" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1617" t="inlineStr"/>
-      <c r="L1617" t="inlineStr">
-        <is>
-          <t>2026-09-05 11:01</t>
-        </is>
-      </c>
+      <c r="L1617" t="inlineStr"/>
     </row>
     <row r="1618">
       <c r="A1618" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1564,13 +1564,17 @@
         <v>30</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:40</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1614,13 +1614,17 @@
         <v>20</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:09</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1664,13 +1664,17 @@
         <v>30</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:09</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1567,14 +1567,10 @@
         <v>30</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-09-09 10:40</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1570"/>
+  <dimension ref="A1:L1571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72757,6 +72757,52 @@
       </c>
       <c r="K1570" t="inlineStr"/>
       <c r="L1570" t="inlineStr"/>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="n">
+        <v>3493</v>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>Aula De Conversação</t>
+        </is>
+      </c>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>English Live</t>
+        </is>
+      </c>
+      <c r="H1571" t="n">
+        <v>40</v>
+      </c>
+      <c r="I1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1571" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1571" t="inlineStr"/>
+      <c r="L1571" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -72796,13 +72796,17 @@
         <v>40</v>
       </c>
       <c r="I1571" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1571" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1571" t="inlineStr"/>
-      <c r="L1571" t="inlineStr"/>
+      <c r="L1571" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1571"/>
+  <dimension ref="A1:L1572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72807,6 +72807,52 @@
           <t>2026-09-09 17:16</t>
         </is>
       </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="n">
+        <v>3494</v>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1572" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1572" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1572" t="inlineStr"/>
+      <c r="L1572" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1572"/>
+  <dimension ref="A1:L1754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72853,6 +72853,8378 @@
       </c>
       <c r="K1572" t="inlineStr"/>
       <c r="L1572" t="inlineStr"/>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="n">
+        <v>3495</v>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1573" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1573" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1573" t="inlineStr"/>
+      <c r="L1573" t="inlineStr"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="n">
+        <v>3496</v>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1574" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1574" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1574" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1574" t="inlineStr"/>
+      <c r="L1574" t="inlineStr"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="n">
+        <v>3497</v>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1575" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1575" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1575" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1575" t="inlineStr"/>
+      <c r="L1575" t="inlineStr"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="n">
+        <v>3498</v>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1576" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1576" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1576" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1576" t="inlineStr"/>
+      <c r="L1576" t="inlineStr"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="n">
+        <v>3499</v>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1577" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1577" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1577" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1577" t="inlineStr"/>
+      <c r="L1577" t="inlineStr"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1578" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1578" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1578" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1578" t="inlineStr"/>
+      <c r="L1578" t="inlineStr"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1579" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1579" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1579" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1579" t="inlineStr"/>
+      <c r="L1579" t="inlineStr"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>3502</v>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1580" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1580" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1580" t="inlineStr"/>
+      <c r="L1580" t="inlineStr"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1581" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1581" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1581" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1581" t="inlineStr"/>
+      <c r="L1581" t="inlineStr"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1582" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1582" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1582" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1582" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1582" t="inlineStr"/>
+      <c r="L1582" t="inlineStr"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>3505</v>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1583" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1583" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1583" t="inlineStr"/>
+      <c r="L1583" t="inlineStr"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1584" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1584" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1584" t="inlineStr"/>
+      <c r="L1584" t="inlineStr"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1585" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1585" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1585" t="inlineStr"/>
+      <c r="L1585" t="inlineStr"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="n">
+        <v>3508</v>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1586" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1586" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1586" t="inlineStr"/>
+      <c r="L1586" t="inlineStr"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1587" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1587" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1587" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1587" t="inlineStr"/>
+      <c r="L1587" t="inlineStr"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1588" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1588" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1588" t="inlineStr"/>
+      <c r="L1588" t="inlineStr"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="n">
+        <v>3511</v>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1589" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1589" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1589" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1589" t="inlineStr"/>
+      <c r="L1589" t="inlineStr"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1590" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1590" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1590" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1590" t="inlineStr"/>
+      <c r="L1590" t="inlineStr"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1591" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1591" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1591" t="inlineStr"/>
+      <c r="L1591" t="inlineStr"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="n">
+        <v>3514</v>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1592" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1592" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1592" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1592" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1592" t="inlineStr"/>
+      <c r="L1592" t="inlineStr"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1593" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1593" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1593" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1593" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1593" t="inlineStr"/>
+      <c r="L1593" t="inlineStr"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="n">
+        <v>3516</v>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1594" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1594" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1594" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1594" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1594" t="inlineStr"/>
+      <c r="L1594" t="inlineStr"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="n">
+        <v>3517</v>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1595" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1595" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1595" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1595" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1595" t="inlineStr"/>
+      <c r="L1595" t="inlineStr"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="n">
+        <v>3518</v>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1596" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1596" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1596" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1596" t="inlineStr"/>
+      <c r="L1596" t="inlineStr"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="n">
+        <v>3519</v>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1597" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1597" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1597" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1597" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1597" t="inlineStr"/>
+      <c r="L1597" t="inlineStr"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1598" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1598" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1598" t="inlineStr"/>
+      <c r="L1598" t="inlineStr"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="n">
+        <v>3521</v>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1599" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1599" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1599" t="inlineStr"/>
+      <c r="L1599" t="inlineStr"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="n">
+        <v>3522</v>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1600" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1600" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1600" t="inlineStr"/>
+      <c r="L1600" t="inlineStr"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="n">
+        <v>3523</v>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1601" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1601" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1601" t="inlineStr"/>
+      <c r="L1601" t="inlineStr"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="n">
+        <v>3524</v>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1602" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1602" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1602" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1602" t="inlineStr"/>
+      <c r="L1602" t="inlineStr"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="n">
+        <v>3525</v>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1603" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1603" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1603" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1603" t="inlineStr"/>
+      <c r="L1603" t="inlineStr"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="n">
+        <v>3526</v>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1604" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1604" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1604" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1604" t="inlineStr"/>
+      <c r="L1604" t="inlineStr"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="n">
+        <v>3527</v>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1605" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1605" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1605" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1605" t="inlineStr"/>
+      <c r="L1605" t="inlineStr"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="n">
+        <v>3528</v>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1606" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1606" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1606" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1606" t="inlineStr"/>
+      <c r="L1606" t="inlineStr"/>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="n">
+        <v>3529</v>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1607" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1607" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1607" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1607" t="inlineStr"/>
+      <c r="L1607" t="inlineStr"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="n">
+        <v>3530</v>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1608" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1608" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1608" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1608" t="inlineStr"/>
+      <c r="L1608" t="inlineStr"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="n">
+        <v>3531</v>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1609" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1609" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1609" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1609" t="inlineStr"/>
+      <c r="L1609" t="inlineStr"/>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="n">
+        <v>3532</v>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1610" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1610" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1610" t="inlineStr"/>
+      <c r="L1610" t="inlineStr"/>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="n">
+        <v>3533</v>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1611" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1611" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1611" t="inlineStr"/>
+      <c r="L1611" t="inlineStr"/>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="n">
+        <v>3534</v>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1612" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1612" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1612" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1612" t="inlineStr"/>
+      <c r="L1612" t="inlineStr"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="n">
+        <v>3535</v>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1613" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1613" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1613" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1613" t="inlineStr"/>
+      <c r="L1613" t="inlineStr"/>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="n">
+        <v>3536</v>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1614" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1614" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1614" t="inlineStr"/>
+      <c r="L1614" t="inlineStr"/>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="n">
+        <v>3537</v>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1615" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1615" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1615" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1615" t="inlineStr"/>
+      <c r="L1615" t="inlineStr"/>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="n">
+        <v>3538</v>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1616" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1616" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1616" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1616" t="inlineStr"/>
+      <c r="L1616" t="inlineStr"/>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="n">
+        <v>3539</v>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1617" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1617" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1617" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1617" t="inlineStr"/>
+      <c r="L1617" t="inlineStr"/>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="n">
+        <v>3540</v>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1618" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1618" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1618" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1618" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1618" t="inlineStr"/>
+      <c r="L1618" t="inlineStr"/>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="n">
+        <v>3541</v>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1619" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1619" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1619" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1619" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1619" t="inlineStr"/>
+      <c r="L1619" t="inlineStr"/>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="n">
+        <v>3542</v>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1620" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1620" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1620" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1620" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1620" t="inlineStr"/>
+      <c r="L1620" t="inlineStr"/>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="n">
+        <v>3543</v>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1621" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1621" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1621" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1621" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1621" t="inlineStr"/>
+      <c r="L1621" t="inlineStr"/>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="n">
+        <v>3544</v>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1622" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1622" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1622" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1622" t="inlineStr"/>
+      <c r="L1622" t="inlineStr"/>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="n">
+        <v>3545</v>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1623" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1623" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1623" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1623" t="inlineStr"/>
+      <c r="L1623" t="inlineStr"/>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="n">
+        <v>3546</v>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1624" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1624" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1624" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1624" t="inlineStr"/>
+      <c r="L1624" t="inlineStr"/>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="n">
+        <v>3547</v>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1625" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1625" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1625" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1625" t="inlineStr"/>
+      <c r="L1625" t="inlineStr"/>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="n">
+        <v>3548</v>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1626" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1626" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1626" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1626" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1626" t="inlineStr"/>
+      <c r="L1626" t="inlineStr"/>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="n">
+        <v>3549</v>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1627" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1627" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1627" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1627" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1627" t="inlineStr"/>
+      <c r="L1627" t="inlineStr"/>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="n">
+        <v>3550</v>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1628" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1628" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1628" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1628" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1628" t="inlineStr"/>
+      <c r="L1628" t="inlineStr"/>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="n">
+        <v>3551</v>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1629" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1629" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1629" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1629" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1629" t="inlineStr"/>
+      <c r="L1629" t="inlineStr"/>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="n">
+        <v>3552</v>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1630" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1630" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1630" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1630" t="inlineStr"/>
+      <c r="L1630" t="inlineStr"/>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="n">
+        <v>3553</v>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1631" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1631" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1631" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1631" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1631" t="inlineStr"/>
+      <c r="L1631" t="inlineStr"/>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="n">
+        <v>3554</v>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1632" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1632" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1632" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1632" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1632" t="inlineStr"/>
+      <c r="L1632" t="inlineStr"/>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="n">
+        <v>3555</v>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1633" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1633" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1633" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1633" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1633" t="inlineStr"/>
+      <c r="L1633" t="inlineStr"/>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="n">
+        <v>3556</v>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1634" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1634" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1634" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1634" t="inlineStr"/>
+      <c r="L1634" t="inlineStr"/>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="n">
+        <v>3557</v>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1635" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1635" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1635" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1635" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1635" t="inlineStr"/>
+      <c r="L1635" t="inlineStr"/>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="n">
+        <v>3558</v>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1636" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1636" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1636" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1636" t="inlineStr"/>
+      <c r="L1636" t="inlineStr"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="n">
+        <v>3559</v>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1637" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1637" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1637" t="inlineStr"/>
+      <c r="L1637" t="inlineStr"/>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="n">
+        <v>3560</v>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1638" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1638" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1638" t="inlineStr"/>
+      <c r="L1638" t="inlineStr"/>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="n">
+        <v>3561</v>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1639" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1639" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1639" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1639" t="inlineStr"/>
+      <c r="L1639" t="inlineStr"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="n">
+        <v>3562</v>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1640" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1640" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1640" t="inlineStr"/>
+      <c r="L1640" t="inlineStr"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="n">
+        <v>3563</v>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1641" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1641" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1641" t="inlineStr"/>
+      <c r="L1641" t="inlineStr"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="n">
+        <v>3564</v>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1642" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1642" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1642" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1642" t="inlineStr"/>
+      <c r="L1642" t="inlineStr"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="n">
+        <v>3565</v>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1643" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1643" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1643" t="inlineStr"/>
+      <c r="L1643" t="inlineStr"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="n">
+        <v>3566</v>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1644" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1644" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1644" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1644" t="inlineStr"/>
+      <c r="L1644" t="inlineStr"/>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="n">
+        <v>3567</v>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1645" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1645" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1645" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1645" t="inlineStr"/>
+      <c r="L1645" t="inlineStr"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="n">
+        <v>3568</v>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1646" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1646" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1646" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1646" t="inlineStr"/>
+      <c r="L1646" t="inlineStr"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="n">
+        <v>3569</v>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1647" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1647" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1647" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1647" t="inlineStr"/>
+      <c r="L1647" t="inlineStr"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="n">
+        <v>3570</v>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1648" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1648" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1648" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1648" t="inlineStr"/>
+      <c r="L1648" t="inlineStr"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="n">
+        <v>3571</v>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1649" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1649" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1649" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1649" t="inlineStr"/>
+      <c r="L1649" t="inlineStr"/>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="n">
+        <v>3572</v>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1650" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1650" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1650" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1650" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1650" t="inlineStr"/>
+      <c r="L1650" t="inlineStr"/>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="n">
+        <v>3573</v>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1651" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1651" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1651" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1651" t="inlineStr"/>
+      <c r="L1651" t="inlineStr"/>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="n">
+        <v>3574</v>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1652" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1652" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1652" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1652" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1652" t="inlineStr"/>
+      <c r="L1652" t="inlineStr"/>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="n">
+        <v>3575</v>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1653" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1653" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1653" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1653" t="inlineStr"/>
+      <c r="L1653" t="inlineStr"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="n">
+        <v>3576</v>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1654" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1654" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1654" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1654" t="inlineStr"/>
+      <c r="L1654" t="inlineStr"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="n">
+        <v>3577</v>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1655" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1655" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1655" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1655" t="inlineStr"/>
+      <c r="L1655" t="inlineStr"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1656" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1656" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1656" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1656" t="inlineStr"/>
+      <c r="L1656" t="inlineStr"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="n">
+        <v>3579</v>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1657" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1657" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1657" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1657" t="inlineStr"/>
+      <c r="L1657" t="inlineStr"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="n">
+        <v>3580</v>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1658" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1658" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1658" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1658" t="inlineStr"/>
+      <c r="L1658" t="inlineStr"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="n">
+        <v>3581</v>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1659" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1659" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1659" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1659" t="inlineStr"/>
+      <c r="L1659" t="inlineStr"/>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="n">
+        <v>3582</v>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1660" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1660" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1660" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1660" t="inlineStr"/>
+      <c r="L1660" t="inlineStr"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="n">
+        <v>3583</v>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1661" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1661" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1661" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1661" t="inlineStr"/>
+      <c r="L1661" t="inlineStr"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="n">
+        <v>3584</v>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1662" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1662" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1662" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1662" t="inlineStr"/>
+      <c r="L1662" t="inlineStr"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="n">
+        <v>3585</v>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1663" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1663" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1663" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1663" t="inlineStr"/>
+      <c r="L1663" t="inlineStr"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="n">
+        <v>3586</v>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1664" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1664" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1664" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1664" t="inlineStr"/>
+      <c r="L1664" t="inlineStr"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="n">
+        <v>3587</v>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1665" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1665" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1665" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1665" t="inlineStr"/>
+      <c r="L1665" t="inlineStr"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="n">
+        <v>3588</v>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1666" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1666" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1666" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1666" t="inlineStr"/>
+      <c r="L1666" t="inlineStr"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="n">
+        <v>3589</v>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1667" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1667" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1667" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1667" t="inlineStr"/>
+      <c r="L1667" t="inlineStr"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="n">
+        <v>3590</v>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1668" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1668" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1668" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1668" t="inlineStr"/>
+      <c r="L1668" t="inlineStr"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="n">
+        <v>3591</v>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1669" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1669" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1669" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1669" t="inlineStr"/>
+      <c r="L1669" t="inlineStr"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="n">
+        <v>3592</v>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1670" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1670" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1670" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1670" t="inlineStr"/>
+      <c r="L1670" t="inlineStr"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="n">
+        <v>3593</v>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1671" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1671" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1671" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1671" t="inlineStr"/>
+      <c r="L1671" t="inlineStr"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="n">
+        <v>3594</v>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1672" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1672" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1672" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1672" t="inlineStr"/>
+      <c r="L1672" t="inlineStr"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="n">
+        <v>3595</v>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1673" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1673" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1673" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1673" t="inlineStr"/>
+      <c r="L1673" t="inlineStr"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="n">
+        <v>3596</v>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1674" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1674" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1674" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1674" t="inlineStr"/>
+      <c r="L1674" t="inlineStr"/>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="n">
+        <v>3597</v>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1675" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1675" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1675" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1675" t="inlineStr"/>
+      <c r="L1675" t="inlineStr"/>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="n">
+        <v>3598</v>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1676" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1676" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1676" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1676" t="inlineStr"/>
+      <c r="L1676" t="inlineStr"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="n">
+        <v>3599</v>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1677" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1677" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1677" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1677" t="inlineStr"/>
+      <c r="L1677" t="inlineStr"/>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="n">
+        <v>3600</v>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1678" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1678" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1678" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1678" t="inlineStr"/>
+      <c r="L1678" t="inlineStr"/>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="n">
+        <v>3601</v>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1679" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1679" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1679" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1679" t="inlineStr"/>
+      <c r="L1679" t="inlineStr"/>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="n">
+        <v>3602</v>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1680" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1680" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1680" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1680" t="inlineStr"/>
+      <c r="L1680" t="inlineStr"/>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="n">
+        <v>3603</v>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1681" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1681" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1681" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1681" t="inlineStr"/>
+      <c r="L1681" t="inlineStr"/>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="n">
+        <v>3604</v>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1682" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1682" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1682" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1682" t="inlineStr"/>
+      <c r="L1682" t="inlineStr"/>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="n">
+        <v>3605</v>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1683" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1683" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1683" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1683" t="inlineStr"/>
+      <c r="L1683" t="inlineStr"/>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="n">
+        <v>3606</v>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1684" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1684" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1684" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1684" t="inlineStr"/>
+      <c r="L1684" t="inlineStr"/>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="n">
+        <v>3607</v>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1685" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1685" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1685" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1685" t="inlineStr"/>
+      <c r="L1685" t="inlineStr"/>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="n">
+        <v>3608</v>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1686" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1686" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1686" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1686" t="inlineStr"/>
+      <c r="L1686" t="inlineStr"/>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="n">
+        <v>3609</v>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1687" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1687" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1687" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1687" t="inlineStr"/>
+      <c r="L1687" t="inlineStr"/>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="n">
+        <v>3610</v>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1688" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1688" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1688" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1688" t="inlineStr"/>
+      <c r="L1688" t="inlineStr"/>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="n">
+        <v>3611</v>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1689" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1689" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1689" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1689" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1689" t="inlineStr"/>
+      <c r="L1689" t="inlineStr"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="n">
+        <v>3612</v>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1690" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1690" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1690" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1690" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1690" t="inlineStr"/>
+      <c r="L1690" t="inlineStr"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="n">
+        <v>3613</v>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1691" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1691" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1691" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1691" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1691" t="inlineStr"/>
+      <c r="L1691" t="inlineStr"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="n">
+        <v>3614</v>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1692" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1692" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1692" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1692" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1692" t="inlineStr"/>
+      <c r="L1692" t="inlineStr"/>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="n">
+        <v>3615</v>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1693" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1693" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1693" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1693" t="inlineStr"/>
+      <c r="L1693" t="inlineStr"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="n">
+        <v>3616</v>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1694" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1694" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1694" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1694" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1694" t="inlineStr"/>
+      <c r="L1694" t="inlineStr"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="n">
+        <v>3617</v>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1695" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1695" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1695" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1695" t="inlineStr"/>
+      <c r="L1695" t="inlineStr"/>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="n">
+        <v>3618</v>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>2027-01-10</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1696" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1696" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1696" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1696" t="inlineStr"/>
+      <c r="L1696" t="inlineStr"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="n">
+        <v>3619</v>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>2027-01-11</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1697" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1697" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1697" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1697" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1697" t="inlineStr"/>
+      <c r="L1697" t="inlineStr"/>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="n">
+        <v>3620</v>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1698" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1698" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1698" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1698" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1698" t="inlineStr"/>
+      <c r="L1698" t="inlineStr"/>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="n">
+        <v>3621</v>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1699" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1699" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1699" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1699" t="inlineStr"/>
+      <c r="L1699" t="inlineStr"/>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="n">
+        <v>3622</v>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1700" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1700" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1700" t="inlineStr"/>
+      <c r="L1700" t="inlineStr"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="n">
+        <v>3623</v>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1701" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1701" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1701" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1701" t="inlineStr"/>
+      <c r="L1701" t="inlineStr"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="n">
+        <v>3624</v>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>2027-01-16</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1702" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1702" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1702" t="inlineStr"/>
+      <c r="L1702" t="inlineStr"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="n">
+        <v>3625</v>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1703" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1703" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1703" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1703" t="inlineStr"/>
+      <c r="L1703" t="inlineStr"/>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="n">
+        <v>3626</v>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1704" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1704" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1704" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1704" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1704" t="inlineStr"/>
+      <c r="L1704" t="inlineStr"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="n">
+        <v>3627</v>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1705" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1705" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1705" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1705" t="inlineStr"/>
+      <c r="L1705" t="inlineStr"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="n">
+        <v>3628</v>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1706" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1706" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1706" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1706" t="inlineStr"/>
+      <c r="L1706" t="inlineStr"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="n">
+        <v>3629</v>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1707" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1707" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1707" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1707" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1707" t="inlineStr"/>
+      <c r="L1707" t="inlineStr"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="n">
+        <v>3630</v>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1708" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1708" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1708" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1708" t="inlineStr"/>
+      <c r="L1708" t="inlineStr"/>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="n">
+        <v>3631</v>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1709" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1709" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1709" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1709" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1709" t="inlineStr"/>
+      <c r="L1709" t="inlineStr"/>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="n">
+        <v>3632</v>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1710" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1710" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1710" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1710" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1710" t="inlineStr"/>
+      <c r="L1710" t="inlineStr"/>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="n">
+        <v>3633</v>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1711" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1711" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1711" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1711" t="inlineStr"/>
+      <c r="L1711" t="inlineStr"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="n">
+        <v>3634</v>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1712" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1712" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1712" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1712" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1712" t="inlineStr"/>
+      <c r="L1712" t="inlineStr"/>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="n">
+        <v>3635</v>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1713" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1713" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1713" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1713" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1713" t="inlineStr"/>
+      <c r="L1713" t="inlineStr"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="n">
+        <v>3636</v>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1714" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1714" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1714" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1714" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1714" t="inlineStr"/>
+      <c r="L1714" t="inlineStr"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="n">
+        <v>3637</v>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1715" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1715" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1715" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1715" t="inlineStr"/>
+      <c r="L1715" t="inlineStr"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="n">
+        <v>3638</v>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1716" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1716" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1716" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1716" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1716" t="inlineStr"/>
+      <c r="L1716" t="inlineStr"/>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="n">
+        <v>3639</v>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1717" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1717" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1717" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1717" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1717" t="inlineStr"/>
+      <c r="L1717" t="inlineStr"/>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="n">
+        <v>3640</v>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1718" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1718" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1718" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1718" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1718" t="inlineStr"/>
+      <c r="L1718" t="inlineStr"/>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="n">
+        <v>3641</v>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>2027-02-02</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1719" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1719" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1719" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1719" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1719" t="inlineStr"/>
+      <c r="L1719" t="inlineStr"/>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="n">
+        <v>3642</v>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>2027-02-03</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1720" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1720" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1720" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1720" t="inlineStr"/>
+      <c r="L1720" t="inlineStr"/>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="n">
+        <v>3643</v>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1721" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1721" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1721" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1721" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1721" t="inlineStr"/>
+      <c r="L1721" t="inlineStr"/>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="n">
+        <v>3644</v>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>2027-02-05</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1722" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1722" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1722" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1722" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1722" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1722" t="inlineStr"/>
+      <c r="L1722" t="inlineStr"/>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="n">
+        <v>3645</v>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>2027-02-06</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1723" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1723" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1723" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1723" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1723" t="inlineStr"/>
+      <c r="L1723" t="inlineStr"/>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="n">
+        <v>3646</v>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>2027-02-07</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1724" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1724" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1724" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1724" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1724" t="inlineStr"/>
+      <c r="L1724" t="inlineStr"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="n">
+        <v>3647</v>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>2027-02-08</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1725" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1725" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1725" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1725" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1725" t="inlineStr"/>
+      <c r="L1725" t="inlineStr"/>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="n">
+        <v>3648</v>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>2027-02-09</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1726" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1726" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1726" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1726" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1726" t="inlineStr"/>
+      <c r="L1726" t="inlineStr"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="n">
+        <v>3649</v>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>2027-02-10</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1727" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1727" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1727" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1727" t="inlineStr"/>
+      <c r="L1727" t="inlineStr"/>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="n">
+        <v>3650</v>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>2027-02-11</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1728" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1728" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1728" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1728" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1728" t="inlineStr"/>
+      <c r="L1728" t="inlineStr"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="n">
+        <v>3651</v>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>2027-02-12</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1729" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1729" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1729" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1729" t="inlineStr"/>
+      <c r="L1729" t="inlineStr"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="n">
+        <v>3652</v>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>2027-02-13</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1730" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1730" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1730" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1730" t="inlineStr"/>
+      <c r="L1730" t="inlineStr"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="n">
+        <v>3653</v>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>2027-02-14</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1731" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1731" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1731" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1731" t="inlineStr"/>
+      <c r="L1731" t="inlineStr"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="n">
+        <v>3654</v>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>2027-02-15</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1732" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1732" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1732" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1732" t="inlineStr"/>
+      <c r="L1732" t="inlineStr"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="n">
+        <v>3655</v>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>2027-02-16</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1733" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1733" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1733" t="inlineStr"/>
+      <c r="L1733" t="inlineStr"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="n">
+        <v>3656</v>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>2027-02-17</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1734" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1734" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1734" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1734" t="inlineStr"/>
+      <c r="L1734" t="inlineStr"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="n">
+        <v>3657</v>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>2027-02-18</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1735" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1735" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1735" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1735" t="inlineStr"/>
+      <c r="L1735" t="inlineStr"/>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="n">
+        <v>3658</v>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1736" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1736" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1736" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1736" t="inlineStr"/>
+      <c r="L1736" t="inlineStr"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="n">
+        <v>3659</v>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>2027-02-20</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1737" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1737" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1737" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1737" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1737" t="inlineStr"/>
+      <c r="L1737" t="inlineStr"/>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="n">
+        <v>3660</v>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>2027-02-21</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1738" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1738" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1738" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1738" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1738" t="inlineStr"/>
+      <c r="L1738" t="inlineStr"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="n">
+        <v>3661</v>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>2027-02-22</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1739" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1739" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1739" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1739" t="inlineStr"/>
+      <c r="L1739" t="inlineStr"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="n">
+        <v>3662</v>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1740" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1740" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1740" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1740" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1740" t="inlineStr"/>
+      <c r="L1740" t="inlineStr"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="n">
+        <v>3663</v>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>2027-02-24</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1741" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1741" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1741" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1741" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1741" t="inlineStr"/>
+      <c r="L1741" t="inlineStr"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="n">
+        <v>3664</v>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>2027-02-25</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1742" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1742" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1742" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1742" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1742" t="inlineStr"/>
+      <c r="L1742" t="inlineStr"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="n">
+        <v>3665</v>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>2027-02-26</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1743" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1743" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1743" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1743" t="inlineStr"/>
+      <c r="L1743" t="inlineStr"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="n">
+        <v>3666</v>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1744" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1744" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1744" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1744" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1744" t="inlineStr"/>
+      <c r="L1744" t="inlineStr"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="n">
+        <v>3667</v>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1745" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1745" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1745" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1745" t="inlineStr"/>
+      <c r="L1745" t="inlineStr"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="n">
+        <v>3668</v>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1746" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1746" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1746" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1746" t="inlineStr"/>
+      <c r="L1746" t="inlineStr"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="n">
+        <v>3669</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1747" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1747" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1747" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1747" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1747" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1747" t="inlineStr"/>
+      <c r="L1747" t="inlineStr"/>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="n">
+        <v>3670</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>2027-03-03</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1748" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1748" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1748" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1748" t="inlineStr"/>
+      <c r="L1748" t="inlineStr"/>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="n">
+        <v>3671</v>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>2027-03-04</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1749" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1749" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1749" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1749" t="inlineStr"/>
+      <c r="L1749" t="inlineStr"/>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="n">
+        <v>3672</v>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>2027-03-05</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1750" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1750" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1750" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1750" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1750" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1750" t="inlineStr"/>
+      <c r="L1750" t="inlineStr"/>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>2027-03-06</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1751" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1751" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1751" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1751" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1751" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1751" t="inlineStr"/>
+      <c r="L1751" t="inlineStr"/>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="n">
+        <v>3674</v>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>2027-03-07</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1752" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1752" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1752" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1752" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1752" t="inlineStr"/>
+      <c r="L1752" t="inlineStr"/>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="n">
+        <v>3675</v>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>2027-03-08</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1753" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1753" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1753" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1753" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1753" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1753" t="inlineStr"/>
+      <c r="L1753" t="inlineStr"/>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="n">
+        <v>3676</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>2027-03-09</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1754" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1754" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1754" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1754" t="inlineStr"/>
+      <c r="L1754" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1754"/>
+  <dimension ref="A1:L1753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72810,7 +72810,7 @@
     </row>
     <row r="1572">
       <c r="A1572" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
@@ -72856,7 +72856,7 @@
     </row>
     <row r="1573">
       <c r="A1573" t="n">
-        <v>3495</v>
+        <v>3496</v>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
@@ -72865,7 +72865,7 @@
       </c>
       <c r="C1573" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D1573" t="inlineStr">
@@ -72902,7 +72902,7 @@
     </row>
     <row r="1574">
       <c r="A1574" t="n">
-        <v>3496</v>
+        <v>3497</v>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
@@ -72911,7 +72911,7 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D1574" t="inlineStr">
@@ -72948,7 +72948,7 @@
     </row>
     <row r="1575">
       <c r="A1575" t="n">
-        <v>3497</v>
+        <v>3498</v>
       </c>
       <c r="B1575" t="inlineStr">
         <is>
@@ -72957,7 +72957,7 @@
       </c>
       <c r="C1575" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D1575" t="inlineStr">
@@ -72994,7 +72994,7 @@
     </row>
     <row r="1576">
       <c r="A1576" t="n">
-        <v>3498</v>
+        <v>3499</v>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
@@ -73003,7 +73003,7 @@
       </c>
       <c r="C1576" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D1576" t="inlineStr">
@@ -73040,7 +73040,7 @@
     </row>
     <row r="1577">
       <c r="A1577" t="n">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
@@ -73086,7 +73086,7 @@
     </row>
     <row r="1578">
       <c r="A1578" t="n">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
@@ -73095,7 +73095,7 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D1578" t="inlineStr">
@@ -73132,7 +73132,7 @@
     </row>
     <row r="1579">
       <c r="A1579" t="n">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="B1579" t="inlineStr">
         <is>
@@ -73141,7 +73141,7 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
@@ -73178,7 +73178,7 @@
     </row>
     <row r="1580">
       <c r="A1580" t="n">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="B1580" t="inlineStr">
         <is>
@@ -73187,7 +73187,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -73224,7 +73224,7 @@
     </row>
     <row r="1581">
       <c r="A1581" t="n">
-        <v>3503</v>
+        <v>3504</v>
       </c>
       <c r="B1581" t="inlineStr">
         <is>
@@ -73233,7 +73233,7 @@
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D1581" t="inlineStr">
@@ -73270,7 +73270,7 @@
     </row>
     <row r="1582">
       <c r="A1582" t="n">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="B1582" t="inlineStr">
         <is>
@@ -73279,7 +73279,7 @@
       </c>
       <c r="C1582" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D1582" t="inlineStr">
@@ -73316,7 +73316,7 @@
     </row>
     <row r="1583">
       <c r="A1583" t="n">
-        <v>3505</v>
+        <v>3506</v>
       </c>
       <c r="B1583" t="inlineStr">
         <is>
@@ -73325,7 +73325,7 @@
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D1583" t="inlineStr">
@@ -73362,7 +73362,7 @@
     </row>
     <row r="1584">
       <c r="A1584" t="n">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="B1584" t="inlineStr">
         <is>
@@ -73371,7 +73371,7 @@
       </c>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D1584" t="inlineStr">
@@ -73408,7 +73408,7 @@
     </row>
     <row r="1585">
       <c r="A1585" t="n">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="B1585" t="inlineStr">
         <is>
@@ -73417,7 +73417,7 @@
       </c>
       <c r="C1585" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D1585" t="inlineStr">
@@ -73454,7 +73454,7 @@
     </row>
     <row r="1586">
       <c r="A1586" t="n">
-        <v>3508</v>
+        <v>3509</v>
       </c>
       <c r="B1586" t="inlineStr">
         <is>
@@ -73463,7 +73463,7 @@
       </c>
       <c r="C1586" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D1586" t="inlineStr">
@@ -73500,7 +73500,7 @@
     </row>
     <row r="1587">
       <c r="A1587" t="n">
-        <v>3509</v>
+        <v>3510</v>
       </c>
       <c r="B1587" t="inlineStr">
         <is>
@@ -73509,7 +73509,7 @@
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
@@ -73546,7 +73546,7 @@
     </row>
     <row r="1588">
       <c r="A1588" t="n">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="B1588" t="inlineStr">
         <is>
@@ -73555,7 +73555,7 @@
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
@@ -73592,7 +73592,7 @@
     </row>
     <row r="1589">
       <c r="A1589" t="n">
-        <v>3511</v>
+        <v>3512</v>
       </c>
       <c r="B1589" t="inlineStr">
         <is>
@@ -73601,7 +73601,7 @@
       </c>
       <c r="C1589" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D1589" t="inlineStr">
@@ -73638,7 +73638,7 @@
     </row>
     <row r="1590">
       <c r="A1590" t="n">
-        <v>3512</v>
+        <v>3513</v>
       </c>
       <c r="B1590" t="inlineStr">
         <is>
@@ -73647,7 +73647,7 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -73684,7 +73684,7 @@
     </row>
     <row r="1591">
       <c r="A1591" t="n">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="B1591" t="inlineStr">
         <is>
@@ -73693,7 +73693,7 @@
       </c>
       <c r="C1591" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D1591" t="inlineStr">
@@ -73730,7 +73730,7 @@
     </row>
     <row r="1592">
       <c r="A1592" t="n">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="B1592" t="inlineStr">
         <is>
@@ -73739,7 +73739,7 @@
       </c>
       <c r="C1592" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D1592" t="inlineStr">
@@ -73776,7 +73776,7 @@
     </row>
     <row r="1593">
       <c r="A1593" t="n">
-        <v>3515</v>
+        <v>3516</v>
       </c>
       <c r="B1593" t="inlineStr">
         <is>
@@ -73785,7 +73785,7 @@
       </c>
       <c r="C1593" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D1593" t="inlineStr">
@@ -73822,7 +73822,7 @@
     </row>
     <row r="1594">
       <c r="A1594" t="n">
-        <v>3516</v>
+        <v>3517</v>
       </c>
       <c r="B1594" t="inlineStr">
         <is>
@@ -73831,7 +73831,7 @@
       </c>
       <c r="C1594" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D1594" t="inlineStr">
@@ -73868,7 +73868,7 @@
     </row>
     <row r="1595">
       <c r="A1595" t="n">
-        <v>3517</v>
+        <v>3518</v>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
@@ -73877,7 +73877,7 @@
       </c>
       <c r="C1595" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D1595" t="inlineStr">
@@ -73914,7 +73914,7 @@
     </row>
     <row r="1596">
       <c r="A1596" t="n">
-        <v>3518</v>
+        <v>3519</v>
       </c>
       <c r="B1596" t="inlineStr">
         <is>
@@ -73923,7 +73923,7 @@
       </c>
       <c r="C1596" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D1596" t="inlineStr">
@@ -73960,7 +73960,7 @@
     </row>
     <row r="1597">
       <c r="A1597" t="n">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="B1597" t="inlineStr">
         <is>
@@ -73969,7 +73969,7 @@
       </c>
       <c r="C1597" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D1597" t="inlineStr">
@@ -74006,7 +74006,7 @@
     </row>
     <row r="1598">
       <c r="A1598" t="n">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="B1598" t="inlineStr">
         <is>
@@ -74015,7 +74015,7 @@
       </c>
       <c r="C1598" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D1598" t="inlineStr">
@@ -74052,7 +74052,7 @@
     </row>
     <row r="1599">
       <c r="A1599" t="n">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="B1599" t="inlineStr">
         <is>
@@ -74061,7 +74061,7 @@
       </c>
       <c r="C1599" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D1599" t="inlineStr">
@@ -74098,7 +74098,7 @@
     </row>
     <row r="1600">
       <c r="A1600" t="n">
-        <v>3522</v>
+        <v>3523</v>
       </c>
       <c r="B1600" t="inlineStr">
         <is>
@@ -74107,7 +74107,7 @@
       </c>
       <c r="C1600" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D1600" t="inlineStr">
@@ -74144,7 +74144,7 @@
     </row>
     <row r="1601">
       <c r="A1601" t="n">
-        <v>3523</v>
+        <v>3524</v>
       </c>
       <c r="B1601" t="inlineStr">
         <is>
@@ -74153,7 +74153,7 @@
       </c>
       <c r="C1601" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D1601" t="inlineStr">
@@ -74190,7 +74190,7 @@
     </row>
     <row r="1602">
       <c r="A1602" t="n">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="B1602" t="inlineStr">
         <is>
@@ -74199,7 +74199,7 @@
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D1602" t="inlineStr">
@@ -74236,7 +74236,7 @@
     </row>
     <row r="1603">
       <c r="A1603" t="n">
-        <v>3525</v>
+        <v>3526</v>
       </c>
       <c r="B1603" t="inlineStr">
         <is>
@@ -74245,7 +74245,7 @@
       </c>
       <c r="C1603" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D1603" t="inlineStr">
@@ -74282,7 +74282,7 @@
     </row>
     <row r="1604">
       <c r="A1604" t="n">
-        <v>3526</v>
+        <v>3527</v>
       </c>
       <c r="B1604" t="inlineStr">
         <is>
@@ -74291,7 +74291,7 @@
       </c>
       <c r="C1604" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D1604" t="inlineStr">
@@ -74328,7 +74328,7 @@
     </row>
     <row r="1605">
       <c r="A1605" t="n">
-        <v>3527</v>
+        <v>3528</v>
       </c>
       <c r="B1605" t="inlineStr">
         <is>
@@ -74337,7 +74337,7 @@
       </c>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D1605" t="inlineStr">
@@ -74374,7 +74374,7 @@
     </row>
     <row r="1606">
       <c r="A1606" t="n">
-        <v>3528</v>
+        <v>3529</v>
       </c>
       <c r="B1606" t="inlineStr">
         <is>
@@ -74383,7 +74383,7 @@
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D1606" t="inlineStr">
@@ -74420,7 +74420,7 @@
     </row>
     <row r="1607">
       <c r="A1607" t="n">
-        <v>3529</v>
+        <v>3530</v>
       </c>
       <c r="B1607" t="inlineStr">
         <is>
@@ -74429,7 +74429,7 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D1607" t="inlineStr">
@@ -74466,7 +74466,7 @@
     </row>
     <row r="1608">
       <c r="A1608" t="n">
-        <v>3530</v>
+        <v>3531</v>
       </c>
       <c r="B1608" t="inlineStr">
         <is>
@@ -74475,7 +74475,7 @@
       </c>
       <c r="C1608" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D1608" t="inlineStr">
@@ -74512,7 +74512,7 @@
     </row>
     <row r="1609">
       <c r="A1609" t="n">
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="B1609" t="inlineStr">
         <is>
@@ -74521,7 +74521,7 @@
       </c>
       <c r="C1609" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D1609" t="inlineStr">
@@ -74558,7 +74558,7 @@
     </row>
     <row r="1610">
       <c r="A1610" t="n">
-        <v>3532</v>
+        <v>3533</v>
       </c>
       <c r="B1610" t="inlineStr">
         <is>
@@ -74567,7 +74567,7 @@
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D1610" t="inlineStr">
@@ -74604,7 +74604,7 @@
     </row>
     <row r="1611">
       <c r="A1611" t="n">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="B1611" t="inlineStr">
         <is>
@@ -74613,7 +74613,7 @@
       </c>
       <c r="C1611" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D1611" t="inlineStr">
@@ -74650,7 +74650,7 @@
     </row>
     <row r="1612">
       <c r="A1612" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="B1612" t="inlineStr">
         <is>
@@ -74659,7 +74659,7 @@
       </c>
       <c r="C1612" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1612" t="inlineStr">
@@ -74696,7 +74696,7 @@
     </row>
     <row r="1613">
       <c r="A1613" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
@@ -74705,7 +74705,7 @@
       </c>
       <c r="C1613" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D1613" t="inlineStr">
@@ -74742,7 +74742,7 @@
     </row>
     <row r="1614">
       <c r="A1614" t="n">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="B1614" t="inlineStr">
         <is>
@@ -74751,7 +74751,7 @@
       </c>
       <c r="C1614" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D1614" t="inlineStr">
@@ -74788,7 +74788,7 @@
     </row>
     <row r="1615">
       <c r="A1615" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="B1615" t="inlineStr">
         <is>
@@ -74797,7 +74797,7 @@
       </c>
       <c r="C1615" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D1615" t="inlineStr">
@@ -74834,7 +74834,7 @@
     </row>
     <row r="1616">
       <c r="A1616" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="B1616" t="inlineStr">
         <is>
@@ -74843,7 +74843,7 @@
       </c>
       <c r="C1616" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D1616" t="inlineStr">
@@ -74880,7 +74880,7 @@
     </row>
     <row r="1617">
       <c r="A1617" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="B1617" t="inlineStr">
         <is>
@@ -74889,7 +74889,7 @@
       </c>
       <c r="C1617" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D1617" t="inlineStr">
@@ -74926,7 +74926,7 @@
     </row>
     <row r="1618">
       <c r="A1618" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="B1618" t="inlineStr">
         <is>
@@ -74935,7 +74935,7 @@
       </c>
       <c r="C1618" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D1618" t="inlineStr">
@@ -74972,7 +74972,7 @@
     </row>
     <row r="1619">
       <c r="A1619" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="B1619" t="inlineStr">
         <is>
@@ -74981,7 +74981,7 @@
       </c>
       <c r="C1619" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D1619" t="inlineStr">
@@ -75018,7 +75018,7 @@
     </row>
     <row r="1620">
       <c r="A1620" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="B1620" t="inlineStr">
         <is>
@@ -75027,7 +75027,7 @@
       </c>
       <c r="C1620" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D1620" t="inlineStr">
@@ -75064,7 +75064,7 @@
     </row>
     <row r="1621">
       <c r="A1621" t="n">
-        <v>3543</v>
+        <v>3544</v>
       </c>
       <c r="B1621" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
       </c>
       <c r="C1621" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D1621" t="inlineStr">
@@ -75110,7 +75110,7 @@
     </row>
     <row r="1622">
       <c r="A1622" t="n">
-        <v>3544</v>
+        <v>3545</v>
       </c>
       <c r="B1622" t="inlineStr">
         <is>
@@ -75119,7 +75119,7 @@
       </c>
       <c r="C1622" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D1622" t="inlineStr">
@@ -75156,7 +75156,7 @@
     </row>
     <row r="1623">
       <c r="A1623" t="n">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="B1623" t="inlineStr">
         <is>
@@ -75165,7 +75165,7 @@
       </c>
       <c r="C1623" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D1623" t="inlineStr">
@@ -75202,7 +75202,7 @@
     </row>
     <row r="1624">
       <c r="A1624" t="n">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="B1624" t="inlineStr">
         <is>
@@ -75211,7 +75211,7 @@
       </c>
       <c r="C1624" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D1624" t="inlineStr">
@@ -75248,7 +75248,7 @@
     </row>
     <row r="1625">
       <c r="A1625" t="n">
-        <v>3547</v>
+        <v>3548</v>
       </c>
       <c r="B1625" t="inlineStr">
         <is>
@@ -75257,7 +75257,7 @@
       </c>
       <c r="C1625" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D1625" t="inlineStr">
@@ -75294,7 +75294,7 @@
     </row>
     <row r="1626">
       <c r="A1626" t="n">
-        <v>3548</v>
+        <v>3549</v>
       </c>
       <c r="B1626" t="inlineStr">
         <is>
@@ -75303,7 +75303,7 @@
       </c>
       <c r="C1626" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D1626" t="inlineStr">
@@ -75340,7 +75340,7 @@
     </row>
     <row r="1627">
       <c r="A1627" t="n">
-        <v>3549</v>
+        <v>3550</v>
       </c>
       <c r="B1627" t="inlineStr">
         <is>
@@ -75349,7 +75349,7 @@
       </c>
       <c r="C1627" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D1627" t="inlineStr">
@@ -75386,7 +75386,7 @@
     </row>
     <row r="1628">
       <c r="A1628" t="n">
-        <v>3550</v>
+        <v>3551</v>
       </c>
       <c r="B1628" t="inlineStr">
         <is>
@@ -75395,7 +75395,7 @@
       </c>
       <c r="C1628" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D1628" t="inlineStr">
@@ -75432,7 +75432,7 @@
     </row>
     <row r="1629">
       <c r="A1629" t="n">
-        <v>3551</v>
+        <v>3552</v>
       </c>
       <c r="B1629" t="inlineStr">
         <is>
@@ -75441,7 +75441,7 @@
       </c>
       <c r="C1629" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D1629" t="inlineStr">
@@ -75478,7 +75478,7 @@
     </row>
     <row r="1630">
       <c r="A1630" t="n">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="B1630" t="inlineStr">
         <is>
@@ -75487,7 +75487,7 @@
       </c>
       <c r="C1630" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D1630" t="inlineStr">
@@ -75524,7 +75524,7 @@
     </row>
     <row r="1631">
       <c r="A1631" t="n">
-        <v>3553</v>
+        <v>3554</v>
       </c>
       <c r="B1631" t="inlineStr">
         <is>
@@ -75533,7 +75533,7 @@
       </c>
       <c r="C1631" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D1631" t="inlineStr">
@@ -75570,7 +75570,7 @@
     </row>
     <row r="1632">
       <c r="A1632" t="n">
-        <v>3554</v>
+        <v>3555</v>
       </c>
       <c r="B1632" t="inlineStr">
         <is>
@@ -75579,7 +75579,7 @@
       </c>
       <c r="C1632" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D1632" t="inlineStr">
@@ -75616,7 +75616,7 @@
     </row>
     <row r="1633">
       <c r="A1633" t="n">
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="B1633" t="inlineStr">
         <is>
@@ -75625,7 +75625,7 @@
       </c>
       <c r="C1633" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D1633" t="inlineStr">
@@ -75662,7 +75662,7 @@
     </row>
     <row r="1634">
       <c r="A1634" t="n">
-        <v>3556</v>
+        <v>3557</v>
       </c>
       <c r="B1634" t="inlineStr">
         <is>
@@ -75671,7 +75671,7 @@
       </c>
       <c r="C1634" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D1634" t="inlineStr">
@@ -75708,7 +75708,7 @@
     </row>
     <row r="1635">
       <c r="A1635" t="n">
-        <v>3557</v>
+        <v>3558</v>
       </c>
       <c r="B1635" t="inlineStr">
         <is>
@@ -75717,7 +75717,7 @@
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D1635" t="inlineStr">
@@ -75754,7 +75754,7 @@
     </row>
     <row r="1636">
       <c r="A1636" t="n">
-        <v>3558</v>
+        <v>3559</v>
       </c>
       <c r="B1636" t="inlineStr">
         <is>
@@ -75763,7 +75763,7 @@
       </c>
       <c r="C1636" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D1636" t="inlineStr">
@@ -75800,7 +75800,7 @@
     </row>
     <row r="1637">
       <c r="A1637" t="n">
-        <v>3559</v>
+        <v>3560</v>
       </c>
       <c r="B1637" t="inlineStr">
         <is>
@@ -75809,7 +75809,7 @@
       </c>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
@@ -75846,7 +75846,7 @@
     </row>
     <row r="1638">
       <c r="A1638" t="n">
-        <v>3560</v>
+        <v>3561</v>
       </c>
       <c r="B1638" t="inlineStr">
         <is>
@@ -75855,7 +75855,7 @@
       </c>
       <c r="C1638" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D1638" t="inlineStr">
@@ -75892,7 +75892,7 @@
     </row>
     <row r="1639">
       <c r="A1639" t="n">
-        <v>3561</v>
+        <v>3562</v>
       </c>
       <c r="B1639" t="inlineStr">
         <is>
@@ -75901,7 +75901,7 @@
       </c>
       <c r="C1639" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D1639" t="inlineStr">
@@ -75938,7 +75938,7 @@
     </row>
     <row r="1640">
       <c r="A1640" t="n">
-        <v>3562</v>
+        <v>3563</v>
       </c>
       <c r="B1640" t="inlineStr">
         <is>
@@ -75947,7 +75947,7 @@
       </c>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D1640" t="inlineStr">
@@ -75984,7 +75984,7 @@
     </row>
     <row r="1641">
       <c r="A1641" t="n">
-        <v>3563</v>
+        <v>3564</v>
       </c>
       <c r="B1641" t="inlineStr">
         <is>
@@ -75993,7 +75993,7 @@
       </c>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D1641" t="inlineStr">
@@ -76030,7 +76030,7 @@
     </row>
     <row r="1642">
       <c r="A1642" t="n">
-        <v>3564</v>
+        <v>3565</v>
       </c>
       <c r="B1642" t="inlineStr">
         <is>
@@ -76039,7 +76039,7 @@
       </c>
       <c r="C1642" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D1642" t="inlineStr">
@@ -76076,7 +76076,7 @@
     </row>
     <row r="1643">
       <c r="A1643" t="n">
-        <v>3565</v>
+        <v>3566</v>
       </c>
       <c r="B1643" t="inlineStr">
         <is>
@@ -76085,7 +76085,7 @@
       </c>
       <c r="C1643" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D1643" t="inlineStr">
@@ -76122,7 +76122,7 @@
     </row>
     <row r="1644">
       <c r="A1644" t="n">
-        <v>3566</v>
+        <v>3567</v>
       </c>
       <c r="B1644" t="inlineStr">
         <is>
@@ -76131,7 +76131,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D1644" t="inlineStr">
@@ -76168,7 +76168,7 @@
     </row>
     <row r="1645">
       <c r="A1645" t="n">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="B1645" t="inlineStr">
         <is>
@@ -76177,7 +76177,7 @@
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D1645" t="inlineStr">
@@ -76214,7 +76214,7 @@
     </row>
     <row r="1646">
       <c r="A1646" t="n">
-        <v>3568</v>
+        <v>3569</v>
       </c>
       <c r="B1646" t="inlineStr">
         <is>
@@ -76223,7 +76223,7 @@
       </c>
       <c r="C1646" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D1646" t="inlineStr">
@@ -76260,7 +76260,7 @@
     </row>
     <row r="1647">
       <c r="A1647" t="n">
-        <v>3569</v>
+        <v>3570</v>
       </c>
       <c r="B1647" t="inlineStr">
         <is>
@@ -76269,7 +76269,7 @@
       </c>
       <c r="C1647" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D1647" t="inlineStr">
@@ -76306,7 +76306,7 @@
     </row>
     <row r="1648">
       <c r="A1648" t="n">
-        <v>3570</v>
+        <v>3571</v>
       </c>
       <c r="B1648" t="inlineStr">
         <is>
@@ -76315,7 +76315,7 @@
       </c>
       <c r="C1648" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D1648" t="inlineStr">
@@ -76352,7 +76352,7 @@
     </row>
     <row r="1649">
       <c r="A1649" t="n">
-        <v>3571</v>
+        <v>3572</v>
       </c>
       <c r="B1649" t="inlineStr">
         <is>
@@ -76361,7 +76361,7 @@
       </c>
       <c r="C1649" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D1649" t="inlineStr">
@@ -76398,7 +76398,7 @@
     </row>
     <row r="1650">
       <c r="A1650" t="n">
-        <v>3572</v>
+        <v>3573</v>
       </c>
       <c r="B1650" t="inlineStr">
         <is>
@@ -76407,7 +76407,7 @@
       </c>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D1650" t="inlineStr">
@@ -76444,7 +76444,7 @@
     </row>
     <row r="1651">
       <c r="A1651" t="n">
-        <v>3573</v>
+        <v>3574</v>
       </c>
       <c r="B1651" t="inlineStr">
         <is>
@@ -76453,7 +76453,7 @@
       </c>
       <c r="C1651" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D1651" t="inlineStr">
@@ -76490,7 +76490,7 @@
     </row>
     <row r="1652">
       <c r="A1652" t="n">
-        <v>3574</v>
+        <v>3575</v>
       </c>
       <c r="B1652" t="inlineStr">
         <is>
@@ -76499,7 +76499,7 @@
       </c>
       <c r="C1652" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D1652" t="inlineStr">
@@ -76536,7 +76536,7 @@
     </row>
     <row r="1653">
       <c r="A1653" t="n">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="B1653" t="inlineStr">
         <is>
@@ -76545,7 +76545,7 @@
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D1653" t="inlineStr">
@@ -76582,7 +76582,7 @@
     </row>
     <row r="1654">
       <c r="A1654" t="n">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="B1654" t="inlineStr">
         <is>
@@ -76591,7 +76591,7 @@
       </c>
       <c r="C1654" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D1654" t="inlineStr">
@@ -76628,7 +76628,7 @@
     </row>
     <row r="1655">
       <c r="A1655" t="n">
-        <v>3577</v>
+        <v>3578</v>
       </c>
       <c r="B1655" t="inlineStr">
         <is>
@@ -76637,7 +76637,7 @@
       </c>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
@@ -76674,7 +76674,7 @@
     </row>
     <row r="1656">
       <c r="A1656" t="n">
-        <v>3578</v>
+        <v>3579</v>
       </c>
       <c r="B1656" t="inlineStr">
         <is>
@@ -76683,7 +76683,7 @@
       </c>
       <c r="C1656" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D1656" t="inlineStr">
@@ -76720,7 +76720,7 @@
     </row>
     <row r="1657">
       <c r="A1657" t="n">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="B1657" t="inlineStr">
         <is>
@@ -76729,7 +76729,7 @@
       </c>
       <c r="C1657" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D1657" t="inlineStr">
@@ -76766,7 +76766,7 @@
     </row>
     <row r="1658">
       <c r="A1658" t="n">
-        <v>3580</v>
+        <v>3581</v>
       </c>
       <c r="B1658" t="inlineStr">
         <is>
@@ -76775,7 +76775,7 @@
       </c>
       <c r="C1658" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D1658" t="inlineStr">
@@ -76812,7 +76812,7 @@
     </row>
     <row r="1659">
       <c r="A1659" t="n">
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="B1659" t="inlineStr">
         <is>
@@ -76821,7 +76821,7 @@
       </c>
       <c r="C1659" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D1659" t="inlineStr">
@@ -76858,7 +76858,7 @@
     </row>
     <row r="1660">
       <c r="A1660" t="n">
-        <v>3582</v>
+        <v>3583</v>
       </c>
       <c r="B1660" t="inlineStr">
         <is>
@@ -76867,7 +76867,7 @@
       </c>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D1660" t="inlineStr">
@@ -76904,7 +76904,7 @@
     </row>
     <row r="1661">
       <c r="A1661" t="n">
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="B1661" t="inlineStr">
         <is>
@@ -76913,7 +76913,7 @@
       </c>
       <c r="C1661" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D1661" t="inlineStr">
@@ -76950,7 +76950,7 @@
     </row>
     <row r="1662">
       <c r="A1662" t="n">
-        <v>3584</v>
+        <v>3585</v>
       </c>
       <c r="B1662" t="inlineStr">
         <is>
@@ -76959,7 +76959,7 @@
       </c>
       <c r="C1662" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D1662" t="inlineStr">
@@ -76996,7 +76996,7 @@
     </row>
     <row r="1663">
       <c r="A1663" t="n">
-        <v>3585</v>
+        <v>3586</v>
       </c>
       <c r="B1663" t="inlineStr">
         <is>
@@ -77005,7 +77005,7 @@
       </c>
       <c r="C1663" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D1663" t="inlineStr">
@@ -77042,7 +77042,7 @@
     </row>
     <row r="1664">
       <c r="A1664" t="n">
-        <v>3586</v>
+        <v>3587</v>
       </c>
       <c r="B1664" t="inlineStr">
         <is>
@@ -77051,7 +77051,7 @@
       </c>
       <c r="C1664" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D1664" t="inlineStr">
@@ -77088,7 +77088,7 @@
     </row>
     <row r="1665">
       <c r="A1665" t="n">
-        <v>3587</v>
+        <v>3588</v>
       </c>
       <c r="B1665" t="inlineStr">
         <is>
@@ -77097,7 +77097,7 @@
       </c>
       <c r="C1665" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D1665" t="inlineStr">
@@ -77134,7 +77134,7 @@
     </row>
     <row r="1666">
       <c r="A1666" t="n">
-        <v>3588</v>
+        <v>3589</v>
       </c>
       <c r="B1666" t="inlineStr">
         <is>
@@ -77143,7 +77143,7 @@
       </c>
       <c r="C1666" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D1666" t="inlineStr">
@@ -77180,7 +77180,7 @@
     </row>
     <row r="1667">
       <c r="A1667" t="n">
-        <v>3589</v>
+        <v>3590</v>
       </c>
       <c r="B1667" t="inlineStr">
         <is>
@@ -77189,7 +77189,7 @@
       </c>
       <c r="C1667" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D1667" t="inlineStr">
@@ -77226,7 +77226,7 @@
     </row>
     <row r="1668">
       <c r="A1668" t="n">
-        <v>3590</v>
+        <v>3591</v>
       </c>
       <c r="B1668" t="inlineStr">
         <is>
@@ -77235,7 +77235,7 @@
       </c>
       <c r="C1668" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D1668" t="inlineStr">
@@ -77272,7 +77272,7 @@
     </row>
     <row r="1669">
       <c r="A1669" t="n">
-        <v>3591</v>
+        <v>3592</v>
       </c>
       <c r="B1669" t="inlineStr">
         <is>
@@ -77281,7 +77281,7 @@
       </c>
       <c r="C1669" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D1669" t="inlineStr">
@@ -77318,7 +77318,7 @@
     </row>
     <row r="1670">
       <c r="A1670" t="n">
-        <v>3592</v>
+        <v>3593</v>
       </c>
       <c r="B1670" t="inlineStr">
         <is>
@@ -77327,7 +77327,7 @@
       </c>
       <c r="C1670" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D1670" t="inlineStr">
@@ -77364,7 +77364,7 @@
     </row>
     <row r="1671">
       <c r="A1671" t="n">
-        <v>3593</v>
+        <v>3594</v>
       </c>
       <c r="B1671" t="inlineStr">
         <is>
@@ -77373,7 +77373,7 @@
       </c>
       <c r="C1671" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D1671" t="inlineStr">
@@ -77410,7 +77410,7 @@
     </row>
     <row r="1672">
       <c r="A1672" t="n">
-        <v>3594</v>
+        <v>3595</v>
       </c>
       <c r="B1672" t="inlineStr">
         <is>
@@ -77419,7 +77419,7 @@
       </c>
       <c r="C1672" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D1672" t="inlineStr">
@@ -77456,7 +77456,7 @@
     </row>
     <row r="1673">
       <c r="A1673" t="n">
-        <v>3595</v>
+        <v>3596</v>
       </c>
       <c r="B1673" t="inlineStr">
         <is>
@@ -77465,7 +77465,7 @@
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D1673" t="inlineStr">
@@ -77502,7 +77502,7 @@
     </row>
     <row r="1674">
       <c r="A1674" t="n">
-        <v>3596</v>
+        <v>3597</v>
       </c>
       <c r="B1674" t="inlineStr">
         <is>
@@ -77511,7 +77511,7 @@
       </c>
       <c r="C1674" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D1674" t="inlineStr">
@@ -77548,7 +77548,7 @@
     </row>
     <row r="1675">
       <c r="A1675" t="n">
-        <v>3597</v>
+        <v>3598</v>
       </c>
       <c r="B1675" t="inlineStr">
         <is>
@@ -77557,7 +77557,7 @@
       </c>
       <c r="C1675" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D1675" t="inlineStr">
@@ -77594,7 +77594,7 @@
     </row>
     <row r="1676">
       <c r="A1676" t="n">
-        <v>3598</v>
+        <v>3599</v>
       </c>
       <c r="B1676" t="inlineStr">
         <is>
@@ -77603,7 +77603,7 @@
       </c>
       <c r="C1676" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D1676" t="inlineStr">
@@ -77640,7 +77640,7 @@
     </row>
     <row r="1677">
       <c r="A1677" t="n">
-        <v>3599</v>
+        <v>3600</v>
       </c>
       <c r="B1677" t="inlineStr">
         <is>
@@ -77649,7 +77649,7 @@
       </c>
       <c r="C1677" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D1677" t="inlineStr">
@@ -77686,7 +77686,7 @@
     </row>
     <row r="1678">
       <c r="A1678" t="n">
-        <v>3600</v>
+        <v>3601</v>
       </c>
       <c r="B1678" t="inlineStr">
         <is>
@@ -77695,7 +77695,7 @@
       </c>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D1678" t="inlineStr">
@@ -77732,7 +77732,7 @@
     </row>
     <row r="1679">
       <c r="A1679" t="n">
-        <v>3601</v>
+        <v>3602</v>
       </c>
       <c r="B1679" t="inlineStr">
         <is>
@@ -77741,7 +77741,7 @@
       </c>
       <c r="C1679" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D1679" t="inlineStr">
@@ -77778,7 +77778,7 @@
     </row>
     <row r="1680">
       <c r="A1680" t="n">
-        <v>3602</v>
+        <v>3603</v>
       </c>
       <c r="B1680" t="inlineStr">
         <is>
@@ -77787,7 +77787,7 @@
       </c>
       <c r="C1680" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="D1680" t="inlineStr">
@@ -77824,7 +77824,7 @@
     </row>
     <row r="1681">
       <c r="A1681" t="n">
-        <v>3603</v>
+        <v>3604</v>
       </c>
       <c r="B1681" t="inlineStr">
         <is>
@@ -77833,7 +77833,7 @@
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D1681" t="inlineStr">
@@ -77870,7 +77870,7 @@
     </row>
     <row r="1682">
       <c r="A1682" t="n">
-        <v>3604</v>
+        <v>3605</v>
       </c>
       <c r="B1682" t="inlineStr">
         <is>
@@ -77879,7 +77879,7 @@
       </c>
       <c r="C1682" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D1682" t="inlineStr">
@@ -77916,7 +77916,7 @@
     </row>
     <row r="1683">
       <c r="A1683" t="n">
-        <v>3605</v>
+        <v>3606</v>
       </c>
       <c r="B1683" t="inlineStr">
         <is>
@@ -77925,7 +77925,7 @@
       </c>
       <c r="C1683" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D1683" t="inlineStr">
@@ -77962,7 +77962,7 @@
     </row>
     <row r="1684">
       <c r="A1684" t="n">
-        <v>3606</v>
+        <v>3607</v>
       </c>
       <c r="B1684" t="inlineStr">
         <is>
@@ -77971,7 +77971,7 @@
       </c>
       <c r="C1684" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D1684" t="inlineStr">
@@ -78008,7 +78008,7 @@
     </row>
     <row r="1685">
       <c r="A1685" t="n">
-        <v>3607</v>
+        <v>3608</v>
       </c>
       <c r="B1685" t="inlineStr">
         <is>
@@ -78017,7 +78017,7 @@
       </c>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
@@ -78054,7 +78054,7 @@
     </row>
     <row r="1686">
       <c r="A1686" t="n">
-        <v>3608</v>
+        <v>3609</v>
       </c>
       <c r="B1686" t="inlineStr">
         <is>
@@ -78063,7 +78063,7 @@
       </c>
       <c r="C1686" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D1686" t="inlineStr">
@@ -78100,7 +78100,7 @@
     </row>
     <row r="1687">
       <c r="A1687" t="n">
-        <v>3609</v>
+        <v>3610</v>
       </c>
       <c r="B1687" t="inlineStr">
         <is>
@@ -78109,7 +78109,7 @@
       </c>
       <c r="C1687" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="D1687" t="inlineStr">
@@ -78146,7 +78146,7 @@
     </row>
     <row r="1688">
       <c r="A1688" t="n">
-        <v>3610</v>
+        <v>3611</v>
       </c>
       <c r="B1688" t="inlineStr">
         <is>
@@ -78155,7 +78155,7 @@
       </c>
       <c r="C1688" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D1688" t="inlineStr">
@@ -78192,7 +78192,7 @@
     </row>
     <row r="1689">
       <c r="A1689" t="n">
-        <v>3611</v>
+        <v>3612</v>
       </c>
       <c r="B1689" t="inlineStr">
         <is>
@@ -78201,7 +78201,7 @@
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D1689" t="inlineStr">
@@ -78238,7 +78238,7 @@
     </row>
     <row r="1690">
       <c r="A1690" t="n">
-        <v>3612</v>
+        <v>3613</v>
       </c>
       <c r="B1690" t="inlineStr">
         <is>
@@ -78247,7 +78247,7 @@
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D1690" t="inlineStr">
@@ -78284,7 +78284,7 @@
     </row>
     <row r="1691">
       <c r="A1691" t="n">
-        <v>3613</v>
+        <v>3614</v>
       </c>
       <c r="B1691" t="inlineStr">
         <is>
@@ -78293,7 +78293,7 @@
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D1691" t="inlineStr">
@@ -78330,7 +78330,7 @@
     </row>
     <row r="1692">
       <c r="A1692" t="n">
-        <v>3614</v>
+        <v>3615</v>
       </c>
       <c r="B1692" t="inlineStr">
         <is>
@@ -78339,7 +78339,7 @@
       </c>
       <c r="C1692" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D1692" t="inlineStr">
@@ -78376,7 +78376,7 @@
     </row>
     <row r="1693">
       <c r="A1693" t="n">
-        <v>3615</v>
+        <v>3616</v>
       </c>
       <c r="B1693" t="inlineStr">
         <is>
@@ -78385,7 +78385,7 @@
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D1693" t="inlineStr">
@@ -78422,7 +78422,7 @@
     </row>
     <row r="1694">
       <c r="A1694" t="n">
-        <v>3616</v>
+        <v>3617</v>
       </c>
       <c r="B1694" t="inlineStr">
         <is>
@@ -78431,7 +78431,7 @@
       </c>
       <c r="C1694" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="D1694" t="inlineStr">
@@ -78468,7 +78468,7 @@
     </row>
     <row r="1695">
       <c r="A1695" t="n">
-        <v>3617</v>
+        <v>3618</v>
       </c>
       <c r="B1695" t="inlineStr">
         <is>
@@ -78477,7 +78477,7 @@
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D1695" t="inlineStr">
@@ -78514,7 +78514,7 @@
     </row>
     <row r="1696">
       <c r="A1696" t="n">
-        <v>3618</v>
+        <v>3619</v>
       </c>
       <c r="B1696" t="inlineStr">
         <is>
@@ -78523,7 +78523,7 @@
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
@@ -78560,7 +78560,7 @@
     </row>
     <row r="1697">
       <c r="A1697" t="n">
-        <v>3619</v>
+        <v>3620</v>
       </c>
       <c r="B1697" t="inlineStr">
         <is>
@@ -78569,7 +78569,7 @@
       </c>
       <c r="C1697" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D1697" t="inlineStr">
@@ -78606,7 +78606,7 @@
     </row>
     <row r="1698">
       <c r="A1698" t="n">
-        <v>3620</v>
+        <v>3621</v>
       </c>
       <c r="B1698" t="inlineStr">
         <is>
@@ -78615,7 +78615,7 @@
       </c>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D1698" t="inlineStr">
@@ -78652,7 +78652,7 @@
     </row>
     <row r="1699">
       <c r="A1699" t="n">
-        <v>3621</v>
+        <v>3622</v>
       </c>
       <c r="B1699" t="inlineStr">
         <is>
@@ -78661,7 +78661,7 @@
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D1699" t="inlineStr">
@@ -78698,7 +78698,7 @@
     </row>
     <row r="1700">
       <c r="A1700" t="n">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="B1700" t="inlineStr">
         <is>
@@ -78707,7 +78707,7 @@
       </c>
       <c r="C1700" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D1700" t="inlineStr">
@@ -78744,7 +78744,7 @@
     </row>
     <row r="1701">
       <c r="A1701" t="n">
-        <v>3623</v>
+        <v>3624</v>
       </c>
       <c r="B1701" t="inlineStr">
         <is>
@@ -78753,7 +78753,7 @@
       </c>
       <c r="C1701" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="D1701" t="inlineStr">
@@ -78790,7 +78790,7 @@
     </row>
     <row r="1702">
       <c r="A1702" t="n">
-        <v>3624</v>
+        <v>3625</v>
       </c>
       <c r="B1702" t="inlineStr">
         <is>
@@ -78799,7 +78799,7 @@
       </c>
       <c r="C1702" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D1702" t="inlineStr">
@@ -78836,7 +78836,7 @@
     </row>
     <row r="1703">
       <c r="A1703" t="n">
-        <v>3625</v>
+        <v>3626</v>
       </c>
       <c r="B1703" t="inlineStr">
         <is>
@@ -78845,7 +78845,7 @@
       </c>
       <c r="C1703" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D1703" t="inlineStr">
@@ -78882,7 +78882,7 @@
     </row>
     <row r="1704">
       <c r="A1704" t="n">
-        <v>3626</v>
+        <v>3627</v>
       </c>
       <c r="B1704" t="inlineStr">
         <is>
@@ -78891,7 +78891,7 @@
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D1704" t="inlineStr">
@@ -78928,7 +78928,7 @@
     </row>
     <row r="1705">
       <c r="A1705" t="n">
-        <v>3627</v>
+        <v>3628</v>
       </c>
       <c r="B1705" t="inlineStr">
         <is>
@@ -78937,7 +78937,7 @@
       </c>
       <c r="C1705" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D1705" t="inlineStr">
@@ -78974,7 +78974,7 @@
     </row>
     <row r="1706">
       <c r="A1706" t="n">
-        <v>3628</v>
+        <v>3629</v>
       </c>
       <c r="B1706" t="inlineStr">
         <is>
@@ -78983,7 +78983,7 @@
       </c>
       <c r="C1706" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D1706" t="inlineStr">
@@ -79020,7 +79020,7 @@
     </row>
     <row r="1707">
       <c r="A1707" t="n">
-        <v>3629</v>
+        <v>3630</v>
       </c>
       <c r="B1707" t="inlineStr">
         <is>
@@ -79029,7 +79029,7 @@
       </c>
       <c r="C1707" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D1707" t="inlineStr">
@@ -79066,7 +79066,7 @@
     </row>
     <row r="1708">
       <c r="A1708" t="n">
-        <v>3630</v>
+        <v>3631</v>
       </c>
       <c r="B1708" t="inlineStr">
         <is>
@@ -79075,7 +79075,7 @@
       </c>
       <c r="C1708" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="D1708" t="inlineStr">
@@ -79112,7 +79112,7 @@
     </row>
     <row r="1709">
       <c r="A1709" t="n">
-        <v>3631</v>
+        <v>3632</v>
       </c>
       <c r="B1709" t="inlineStr">
         <is>
@@ -79121,7 +79121,7 @@
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D1709" t="inlineStr">
@@ -79158,7 +79158,7 @@
     </row>
     <row r="1710">
       <c r="A1710" t="n">
-        <v>3632</v>
+        <v>3633</v>
       </c>
       <c r="B1710" t="inlineStr">
         <is>
@@ -79167,7 +79167,7 @@
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D1710" t="inlineStr">
@@ -79204,7 +79204,7 @@
     </row>
     <row r="1711">
       <c r="A1711" t="n">
-        <v>3633</v>
+        <v>3634</v>
       </c>
       <c r="B1711" t="inlineStr">
         <is>
@@ -79213,7 +79213,7 @@
       </c>
       <c r="C1711" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D1711" t="inlineStr">
@@ -79250,7 +79250,7 @@
     </row>
     <row r="1712">
       <c r="A1712" t="n">
-        <v>3634</v>
+        <v>3635</v>
       </c>
       <c r="B1712" t="inlineStr">
         <is>
@@ -79259,7 +79259,7 @@
       </c>
       <c r="C1712" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D1712" t="inlineStr">
@@ -79296,7 +79296,7 @@
     </row>
     <row r="1713">
       <c r="A1713" t="n">
-        <v>3635</v>
+        <v>3636</v>
       </c>
       <c r="B1713" t="inlineStr">
         <is>
@@ -79305,7 +79305,7 @@
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D1713" t="inlineStr">
@@ -79342,7 +79342,7 @@
     </row>
     <row r="1714">
       <c r="A1714" t="n">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="B1714" t="inlineStr">
         <is>
@@ -79351,7 +79351,7 @@
       </c>
       <c r="C1714" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D1714" t="inlineStr">
@@ -79388,7 +79388,7 @@
     </row>
     <row r="1715">
       <c r="A1715" t="n">
-        <v>3637</v>
+        <v>3638</v>
       </c>
       <c r="B1715" t="inlineStr">
         <is>
@@ -79397,7 +79397,7 @@
       </c>
       <c r="C1715" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="D1715" t="inlineStr">
@@ -79434,7 +79434,7 @@
     </row>
     <row r="1716">
       <c r="A1716" t="n">
-        <v>3638</v>
+        <v>3639</v>
       </c>
       <c r="B1716" t="inlineStr">
         <is>
@@ -79443,7 +79443,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D1716" t="inlineStr">
@@ -79480,7 +79480,7 @@
     </row>
     <row r="1717">
       <c r="A1717" t="n">
-        <v>3639</v>
+        <v>3640</v>
       </c>
       <c r="B1717" t="inlineStr">
         <is>
@@ -79489,7 +79489,7 @@
       </c>
       <c r="C1717" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D1717" t="inlineStr">
@@ -79526,7 +79526,7 @@
     </row>
     <row r="1718">
       <c r="A1718" t="n">
-        <v>3640</v>
+        <v>3641</v>
       </c>
       <c r="B1718" t="inlineStr">
         <is>
@@ -79535,7 +79535,7 @@
       </c>
       <c r="C1718" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D1718" t="inlineStr">
@@ -79572,7 +79572,7 @@
     </row>
     <row r="1719">
       <c r="A1719" t="n">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="B1719" t="inlineStr">
         <is>
@@ -79581,7 +79581,7 @@
       </c>
       <c r="C1719" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D1719" t="inlineStr">
@@ -79618,7 +79618,7 @@
     </row>
     <row r="1720">
       <c r="A1720" t="n">
-        <v>3642</v>
+        <v>3643</v>
       </c>
       <c r="B1720" t="inlineStr">
         <is>
@@ -79627,7 +79627,7 @@
       </c>
       <c r="C1720" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D1720" t="inlineStr">
@@ -79664,7 +79664,7 @@
     </row>
     <row r="1721">
       <c r="A1721" t="n">
-        <v>3643</v>
+        <v>3644</v>
       </c>
       <c r="B1721" t="inlineStr">
         <is>
@@ -79673,7 +79673,7 @@
       </c>
       <c r="C1721" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D1721" t="inlineStr">
@@ -79710,7 +79710,7 @@
     </row>
     <row r="1722">
       <c r="A1722" t="n">
-        <v>3644</v>
+        <v>3645</v>
       </c>
       <c r="B1722" t="inlineStr">
         <is>
@@ -79719,7 +79719,7 @@
       </c>
       <c r="C1722" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="D1722" t="inlineStr">
@@ -79756,7 +79756,7 @@
     </row>
     <row r="1723">
       <c r="A1723" t="n">
-        <v>3645</v>
+        <v>3646</v>
       </c>
       <c r="B1723" t="inlineStr">
         <is>
@@ -79765,7 +79765,7 @@
       </c>
       <c r="C1723" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D1723" t="inlineStr">
@@ -79802,7 +79802,7 @@
     </row>
     <row r="1724">
       <c r="A1724" t="n">
-        <v>3646</v>
+        <v>3647</v>
       </c>
       <c r="B1724" t="inlineStr">
         <is>
@@ -79811,7 +79811,7 @@
       </c>
       <c r="C1724" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D1724" t="inlineStr">
@@ -79848,7 +79848,7 @@
     </row>
     <row r="1725">
       <c r="A1725" t="n">
-        <v>3647</v>
+        <v>3648</v>
       </c>
       <c r="B1725" t="inlineStr">
         <is>
@@ -79857,7 +79857,7 @@
       </c>
       <c r="C1725" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D1725" t="inlineStr">
@@ -79894,7 +79894,7 @@
     </row>
     <row r="1726">
       <c r="A1726" t="n">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="B1726" t="inlineStr">
         <is>
@@ -79903,7 +79903,7 @@
       </c>
       <c r="C1726" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D1726" t="inlineStr">
@@ -79940,7 +79940,7 @@
     </row>
     <row r="1727">
       <c r="A1727" t="n">
-        <v>3649</v>
+        <v>3650</v>
       </c>
       <c r="B1727" t="inlineStr">
         <is>
@@ -79949,7 +79949,7 @@
       </c>
       <c r="C1727" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D1727" t="inlineStr">
@@ -79986,7 +79986,7 @@
     </row>
     <row r="1728">
       <c r="A1728" t="n">
-        <v>3650</v>
+        <v>3651</v>
       </c>
       <c r="B1728" t="inlineStr">
         <is>
@@ -79995,7 +79995,7 @@
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D1728" t="inlineStr">
@@ -80032,7 +80032,7 @@
     </row>
     <row r="1729">
       <c r="A1729" t="n">
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="B1729" t="inlineStr">
         <is>
@@ -80041,7 +80041,7 @@
       </c>
       <c r="C1729" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="D1729" t="inlineStr">
@@ -80078,7 +80078,7 @@
     </row>
     <row r="1730">
       <c r="A1730" t="n">
-        <v>3652</v>
+        <v>3653</v>
       </c>
       <c r="B1730" t="inlineStr">
         <is>
@@ -80087,7 +80087,7 @@
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D1730" t="inlineStr">
@@ -80124,7 +80124,7 @@
     </row>
     <row r="1731">
       <c r="A1731" t="n">
-        <v>3653</v>
+        <v>3654</v>
       </c>
       <c r="B1731" t="inlineStr">
         <is>
@@ -80133,7 +80133,7 @@
       </c>
       <c r="C1731" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D1731" t="inlineStr">
@@ -80170,7 +80170,7 @@
     </row>
     <row r="1732">
       <c r="A1732" t="n">
-        <v>3654</v>
+        <v>3655</v>
       </c>
       <c r="B1732" t="inlineStr">
         <is>
@@ -80179,7 +80179,7 @@
       </c>
       <c r="C1732" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D1732" t="inlineStr">
@@ -80216,7 +80216,7 @@
     </row>
     <row r="1733">
       <c r="A1733" t="n">
-        <v>3655</v>
+        <v>3656</v>
       </c>
       <c r="B1733" t="inlineStr">
         <is>
@@ -80225,7 +80225,7 @@
       </c>
       <c r="C1733" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D1733" t="inlineStr">
@@ -80262,7 +80262,7 @@
     </row>
     <row r="1734">
       <c r="A1734" t="n">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="B1734" t="inlineStr">
         <is>
@@ -80271,7 +80271,7 @@
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D1734" t="inlineStr">
@@ -80308,7 +80308,7 @@
     </row>
     <row r="1735">
       <c r="A1735" t="n">
-        <v>3657</v>
+        <v>3658</v>
       </c>
       <c r="B1735" t="inlineStr">
         <is>
@@ -80317,7 +80317,7 @@
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D1735" t="inlineStr">
@@ -80354,7 +80354,7 @@
     </row>
     <row r="1736">
       <c r="A1736" t="n">
-        <v>3658</v>
+        <v>3659</v>
       </c>
       <c r="B1736" t="inlineStr">
         <is>
@@ -80363,7 +80363,7 @@
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D1736" t="inlineStr">
@@ -80400,7 +80400,7 @@
     </row>
     <row r="1737">
       <c r="A1737" t="n">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="B1737" t="inlineStr">
         <is>
@@ -80409,7 +80409,7 @@
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D1737" t="inlineStr">
@@ -80446,7 +80446,7 @@
     </row>
     <row r="1738">
       <c r="A1738" t="n">
-        <v>3660</v>
+        <v>3661</v>
       </c>
       <c r="B1738" t="inlineStr">
         <is>
@@ -80455,7 +80455,7 @@
       </c>
       <c r="C1738" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D1738" t="inlineStr">
@@ -80492,7 +80492,7 @@
     </row>
     <row r="1739">
       <c r="A1739" t="n">
-        <v>3661</v>
+        <v>3662</v>
       </c>
       <c r="B1739" t="inlineStr">
         <is>
@@ -80501,7 +80501,7 @@
       </c>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
@@ -80538,7 +80538,7 @@
     </row>
     <row r="1740">
       <c r="A1740" t="n">
-        <v>3662</v>
+        <v>3663</v>
       </c>
       <c r="B1740" t="inlineStr">
         <is>
@@ -80547,7 +80547,7 @@
       </c>
       <c r="C1740" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D1740" t="inlineStr">
@@ -80584,7 +80584,7 @@
     </row>
     <row r="1741">
       <c r="A1741" t="n">
-        <v>3663</v>
+        <v>3664</v>
       </c>
       <c r="B1741" t="inlineStr">
         <is>
@@ -80593,7 +80593,7 @@
       </c>
       <c r="C1741" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D1741" t="inlineStr">
@@ -80630,7 +80630,7 @@
     </row>
     <row r="1742">
       <c r="A1742" t="n">
-        <v>3664</v>
+        <v>3665</v>
       </c>
       <c r="B1742" t="inlineStr">
         <is>
@@ -80639,7 +80639,7 @@
       </c>
       <c r="C1742" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D1742" t="inlineStr">
@@ -80676,7 +80676,7 @@
     </row>
     <row r="1743">
       <c r="A1743" t="n">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="B1743" t="inlineStr">
         <is>
@@ -80685,7 +80685,7 @@
       </c>
       <c r="C1743" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="D1743" t="inlineStr">
@@ -80722,7 +80722,7 @@
     </row>
     <row r="1744">
       <c r="A1744" t="n">
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="B1744" t="inlineStr">
         <is>
@@ -80731,7 +80731,7 @@
       </c>
       <c r="C1744" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D1744" t="inlineStr">
@@ -80768,7 +80768,7 @@
     </row>
     <row r="1745">
       <c r="A1745" t="n">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="B1745" t="inlineStr">
         <is>
@@ -80777,7 +80777,7 @@
       </c>
       <c r="C1745" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D1745" t="inlineStr">
@@ -80814,7 +80814,7 @@
     </row>
     <row r="1746">
       <c r="A1746" t="n">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="B1746" t="inlineStr">
         <is>
@@ -80823,7 +80823,7 @@
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D1746" t="inlineStr">
@@ -80860,7 +80860,7 @@
     </row>
     <row r="1747">
       <c r="A1747" t="n">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="B1747" t="inlineStr">
         <is>
@@ -80869,7 +80869,7 @@
       </c>
       <c r="C1747" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D1747" t="inlineStr">
@@ -80906,7 +80906,7 @@
     </row>
     <row r="1748">
       <c r="A1748" t="n">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="B1748" t="inlineStr">
         <is>
@@ -80915,7 +80915,7 @@
       </c>
       <c r="C1748" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D1748" t="inlineStr">
@@ -80952,7 +80952,7 @@
     </row>
     <row r="1749">
       <c r="A1749" t="n">
-        <v>3671</v>
+        <v>3672</v>
       </c>
       <c r="B1749" t="inlineStr">
         <is>
@@ -80961,7 +80961,7 @@
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D1749" t="inlineStr">
@@ -80998,7 +80998,7 @@
     </row>
     <row r="1750">
       <c r="A1750" t="n">
-        <v>3672</v>
+        <v>3673</v>
       </c>
       <c r="B1750" t="inlineStr">
         <is>
@@ -81007,7 +81007,7 @@
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="D1750" t="inlineStr">
@@ -81044,7 +81044,7 @@
     </row>
     <row r="1751">
       <c r="A1751" t="n">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="B1751" t="inlineStr">
         <is>
@@ -81053,7 +81053,7 @@
       </c>
       <c r="C1751" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D1751" t="inlineStr">
@@ -81090,7 +81090,7 @@
     </row>
     <row r="1752">
       <c r="A1752" t="n">
-        <v>3674</v>
+        <v>3675</v>
       </c>
       <c r="B1752" t="inlineStr">
         <is>
@@ -81099,7 +81099,7 @@
       </c>
       <c r="C1752" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="D1752" t="inlineStr">
@@ -81136,7 +81136,7 @@
     </row>
     <row r="1753">
       <c r="A1753" t="n">
-        <v>3675</v>
+        <v>3676</v>
       </c>
       <c r="B1753" t="inlineStr">
         <is>
@@ -81145,7 +81145,7 @@
       </c>
       <c r="C1753" t="inlineStr">
         <is>
-          <t>2027-03-08</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="D1753" t="inlineStr">
@@ -81179,52 +81179,6 @@
       </c>
       <c r="K1753" t="inlineStr"/>
       <c r="L1753" t="inlineStr"/>
-    </row>
-    <row r="1754">
-      <c r="A1754" t="n">
-        <v>3676</v>
-      </c>
-      <c r="B1754" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C1754" t="inlineStr">
-        <is>
-          <t>2027-03-09</t>
-        </is>
-      </c>
-      <c r="D1754" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E1754" t="inlineStr">
-        <is>
-          <t>Duolingo</t>
-        </is>
-      </c>
-      <c r="F1754" t="inlineStr">
-        <is>
-          <t>Speaking</t>
-        </is>
-      </c>
-      <c r="G1754" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H1754" t="n">
-        <v>15</v>
-      </c>
-      <c r="I1754" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1754" t="b">
-        <v>0</v>
-      </c>
-      <c r="K1754" t="inlineStr"/>
-      <c r="L1754" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1753"/>
+  <dimension ref="A1:L1754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81179,6 +81179,52 @@
       </c>
       <c r="K1753" t="inlineStr"/>
       <c r="L1753" t="inlineStr"/>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="n">
+        <v>3677</v>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>Duolingo</t>
+        </is>
+      </c>
+      <c r="F1754" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1754" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1754" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1754" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1754" t="inlineStr"/>
+      <c r="L1754" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -81218,13 +81218,17 @@
         <v>15</v>
       </c>
       <c r="I1754" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1754" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1754" t="inlineStr"/>
-      <c r="L1754" t="inlineStr"/>
+      <c r="L1754" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:18</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1754"/>
+  <dimension ref="A1:L1755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81229,6 +81229,52 @@
           <t>2026-09-09 17:18</t>
         </is>
       </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="n">
+        <v>3678</v>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>Atividade de gramática</t>
+        </is>
+      </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>Speaking</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>English Live</t>
+        </is>
+      </c>
+      <c r="H1755" t="n">
+        <v>60</v>
+      </c>
+      <c r="I1755" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1755" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1755" t="inlineStr"/>
+      <c r="L1755" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -81268,13 +81268,17 @@
         <v>60</v>
       </c>
       <c r="I1755" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J1755" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1755" t="inlineStr"/>
-      <c r="L1755" t="inlineStr"/>
+      <c r="L1755" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -72846,13 +72846,17 @@
         <v>15</v>
       </c>
       <c r="I1572" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1572" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1572" t="inlineStr"/>
-      <c r="L1572" t="inlineStr"/>
+      <c r="L1572" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:29</t>
+        </is>
+      </c>
     </row>
     <row r="1573">
       <c r="A1573" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1755"/>
+  <dimension ref="A1:L1756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72846,17 +72846,13 @@
         <v>15</v>
       </c>
       <c r="I1572" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1572" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1572" t="inlineStr"/>
-      <c r="L1572" t="inlineStr">
-        <is>
-          <t>2026-09-09 17:29</t>
-        </is>
-      </c>
+      <c r="L1572" t="inlineStr"/>
     </row>
     <row r="1573">
       <c r="A1573" t="n">
@@ -81283,6 +81279,52 @@
           <t>2026-09-09 17:19</t>
         </is>
       </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="n">
+        <v>3679</v>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>Darlei Delfino</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>Duolingo - Uma lição</t>
+        </is>
+      </c>
+      <c r="F1756" t="inlineStr">
+        <is>
+          <t>Grammar</t>
+        </is>
+      </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1756" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1756" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1756" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1756" t="inlineStr"/>
+      <c r="L1756" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -81318,13 +81318,17 @@
         <v>10</v>
       </c>
       <c r="I1756" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1756" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1756" t="inlineStr"/>
-      <c r="L1756" t="inlineStr"/>
+      <c r="L1756" t="inlineStr">
+        <is>
+          <t>2026-09-09 17:32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1660,13 +1660,17 @@
         <v>30</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-09-10 03:21</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1848,13 +1848,17 @@
         <v>45</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:03</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1756,13 +1756,17 @@
         <v>20</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-09-11 01:43</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1518,13 +1518,17 @@
         <v>20</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-09-11 02:58</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -72862,13 +72862,17 @@
         <v>15</v>
       </c>
       <c r="I1572" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1572" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1572" t="inlineStr"/>
-      <c r="L1572" t="inlineStr"/>
+      <c r="L1572" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:03</t>
+        </is>
+      </c>
     </row>
     <row r="1573">
       <c r="A1573" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -59472,13 +59472,17 @@
         <v>40</v>
       </c>
       <c r="I1281" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J1281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1281" t="inlineStr"/>
-      <c r="L1281" t="inlineStr"/>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:03</t>
+        </is>
+      </c>
     </row>
     <row r="1282">
       <c r="A1282" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -59522,13 +59522,17 @@
         <v>30</v>
       </c>
       <c r="I1282" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J1282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1282" t="inlineStr"/>
-      <c r="L1282" t="inlineStr"/>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:03</t>
+        </is>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -72920,13 +72920,17 @@
         <v>15</v>
       </c>
       <c r="I1573" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1573" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1573" t="inlineStr"/>
-      <c r="L1573" t="inlineStr"/>
+      <c r="L1573" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:03</t>
+        </is>
+      </c>
     </row>
     <row r="1574">
       <c r="A1574" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -72970,13 +72970,17 @@
         <v>15</v>
       </c>
       <c r="I1574" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1574" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1574" t="inlineStr"/>
-      <c r="L1574" t="inlineStr"/>
+      <c r="L1574" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:03</t>
+        </is>
+      </c>
     </row>
     <row r="1575">
       <c r="A1575" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1756"/>
+  <dimension ref="A1:L1757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81365,6 +81365,52 @@
           <t>2026-09-09 17:32</t>
         </is>
       </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="n">
+        <v>3680</v>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>Leitura de Livro</t>
+        </is>
+      </c>
+      <c r="F1757" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1757" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1757" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1757" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1757" t="inlineStr"/>
+      <c r="L1757" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1757"/>
+  <dimension ref="A1:L1938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81411,6 +81411,8332 @@
       </c>
       <c r="K1757" t="inlineStr"/>
       <c r="L1757" t="inlineStr"/>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="n">
+        <v>3681</v>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1758" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1758" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1758" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1758" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1758" t="inlineStr"/>
+      <c r="L1758" t="inlineStr"/>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="n">
+        <v>3682</v>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1759" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1759" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1759" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1759" t="inlineStr"/>
+      <c r="L1759" t="inlineStr"/>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="n">
+        <v>3683</v>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1760" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1760" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1760" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1760" t="inlineStr"/>
+      <c r="L1760" t="inlineStr"/>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="n">
+        <v>3684</v>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1761" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1761" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1761" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1761" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1761" t="inlineStr"/>
+      <c r="L1761" t="inlineStr"/>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="n">
+        <v>3685</v>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1762" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1762" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1762" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1762" t="inlineStr"/>
+      <c r="L1762" t="inlineStr"/>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="n">
+        <v>3686</v>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1763" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1763" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1763" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1763" t="inlineStr"/>
+      <c r="L1763" t="inlineStr"/>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="n">
+        <v>3687</v>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1764" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1764" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1764" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1764" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1764" t="inlineStr"/>
+      <c r="L1764" t="inlineStr"/>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="n">
+        <v>3688</v>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1765" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1765" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1765" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1765" t="inlineStr"/>
+      <c r="L1765" t="inlineStr"/>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="n">
+        <v>3689</v>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1766" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1766" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1766" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1766" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1766" t="inlineStr"/>
+      <c r="L1766" t="inlineStr"/>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="n">
+        <v>3690</v>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1767" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1767" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1767" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1767" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1767" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1767" t="inlineStr"/>
+      <c r="L1767" t="inlineStr"/>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="n">
+        <v>3691</v>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1768" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1768" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1768" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1768" t="inlineStr"/>
+      <c r="L1768" t="inlineStr"/>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="n">
+        <v>3692</v>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1769" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1769" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1769" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1769" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1769" t="inlineStr"/>
+      <c r="L1769" t="inlineStr"/>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="n">
+        <v>3693</v>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1770" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1770" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1770" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1770" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1770" t="inlineStr"/>
+      <c r="L1770" t="inlineStr"/>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="n">
+        <v>3694</v>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1771" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1771" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1771" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1771" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1771" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1771" t="inlineStr"/>
+      <c r="L1771" t="inlineStr"/>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="n">
+        <v>3695</v>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1772" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1772" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1772" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1772" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1772" t="inlineStr"/>
+      <c r="L1772" t="inlineStr"/>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="n">
+        <v>3696</v>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1773" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1773" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1773" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1773" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1773" t="inlineStr"/>
+      <c r="L1773" t="inlineStr"/>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="n">
+        <v>3697</v>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1774" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1774" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1774" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1774" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1774" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1774" t="inlineStr"/>
+      <c r="L1774" t="inlineStr"/>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="n">
+        <v>3698</v>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1775" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1775" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1775" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1775" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1775" t="inlineStr"/>
+      <c r="L1775" t="inlineStr"/>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="n">
+        <v>3699</v>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1776" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1776" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1776" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1776" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1776" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1776" t="inlineStr"/>
+      <c r="L1776" t="inlineStr"/>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="n">
+        <v>3700</v>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1777" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1777" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1777" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1777" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1777" t="inlineStr"/>
+      <c r="L1777" t="inlineStr"/>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="n">
+        <v>3701</v>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1778" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1778" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1778" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1778" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1778" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1778" t="inlineStr"/>
+      <c r="L1778" t="inlineStr"/>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="n">
+        <v>3702</v>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1779" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1779" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1779" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1779" t="inlineStr"/>
+      <c r="L1779" t="inlineStr"/>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="n">
+        <v>3703</v>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1780" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1780" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1780" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1780" t="inlineStr"/>
+      <c r="L1780" t="inlineStr"/>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="n">
+        <v>3704</v>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1781" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1781" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1781" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1781" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1781" t="inlineStr"/>
+      <c r="L1781" t="inlineStr"/>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="n">
+        <v>3705</v>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1782" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1782" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1782" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1782" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1782" t="inlineStr"/>
+      <c r="L1782" t="inlineStr"/>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="n">
+        <v>3706</v>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1783" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1783" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1783" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1783" t="inlineStr"/>
+      <c r="L1783" t="inlineStr"/>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="n">
+        <v>3707</v>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1784" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1784" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1784" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1784" t="inlineStr"/>
+      <c r="L1784" t="inlineStr"/>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="n">
+        <v>3708</v>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1785" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1785" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1785" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1785" t="inlineStr"/>
+      <c r="L1785" t="inlineStr"/>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="n">
+        <v>3709</v>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1786" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1786" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1786" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1786" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1786" t="inlineStr"/>
+      <c r="L1786" t="inlineStr"/>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="n">
+        <v>3710</v>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1787" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1787" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1787" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1787" t="inlineStr"/>
+      <c r="L1787" t="inlineStr"/>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="n">
+        <v>3711</v>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1788" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1788" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1788" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1788" t="inlineStr"/>
+      <c r="L1788" t="inlineStr"/>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="n">
+        <v>3712</v>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1789" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1789" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1789" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1789" t="inlineStr"/>
+      <c r="L1789" t="inlineStr"/>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="n">
+        <v>3713</v>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1790" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1790" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1790" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1790" t="inlineStr"/>
+      <c r="L1790" t="inlineStr"/>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="n">
+        <v>3714</v>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1791" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1791" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1791" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1791" t="inlineStr"/>
+      <c r="L1791" t="inlineStr"/>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="n">
+        <v>3715</v>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1792" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1792" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1792" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1792" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1792" t="inlineStr"/>
+      <c r="L1792" t="inlineStr"/>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="n">
+        <v>3716</v>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1793" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1793" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1793" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1793" t="inlineStr"/>
+      <c r="L1793" t="inlineStr"/>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="n">
+        <v>3717</v>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1794" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1794" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1794" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1794" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1794" t="inlineStr"/>
+      <c r="L1794" t="inlineStr"/>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="n">
+        <v>3718</v>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1795" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1795" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1795" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1795" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1795" t="inlineStr"/>
+      <c r="L1795" t="inlineStr"/>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="n">
+        <v>3719</v>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1796" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1796" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1796" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1796" t="inlineStr"/>
+      <c r="L1796" t="inlineStr"/>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="n">
+        <v>3720</v>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1797" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1797" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1797" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1797" t="inlineStr"/>
+      <c r="L1797" t="inlineStr"/>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="n">
+        <v>3721</v>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1798" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1798" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1798" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1798" t="inlineStr"/>
+      <c r="L1798" t="inlineStr"/>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="n">
+        <v>3722</v>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1799" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1799" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1799" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1799" t="inlineStr"/>
+      <c r="L1799" t="inlineStr"/>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="n">
+        <v>3723</v>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1800" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1800" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1800" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1800" t="inlineStr"/>
+      <c r="L1800" t="inlineStr"/>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="n">
+        <v>3724</v>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1801" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1801" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1801" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1801" t="inlineStr"/>
+      <c r="L1801" t="inlineStr"/>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="n">
+        <v>3725</v>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1802" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1802" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1802" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1802" t="inlineStr"/>
+      <c r="L1802" t="inlineStr"/>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="n">
+        <v>3726</v>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1803" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1803" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1803" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1803" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1803" t="inlineStr"/>
+      <c r="L1803" t="inlineStr"/>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="n">
+        <v>3727</v>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1804" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1804" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1804" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1804" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1804" t="inlineStr"/>
+      <c r="L1804" t="inlineStr"/>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="n">
+        <v>3728</v>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1805" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1805" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1805" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1805" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1805" t="inlineStr"/>
+      <c r="L1805" t="inlineStr"/>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="n">
+        <v>3729</v>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1806" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1806" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1806" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1806" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1806" t="inlineStr"/>
+      <c r="L1806" t="inlineStr"/>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="n">
+        <v>3730</v>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1807" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1807" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1807" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1807" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1807" t="inlineStr"/>
+      <c r="L1807" t="inlineStr"/>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="n">
+        <v>3731</v>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1808" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1808" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1808" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1808" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1808" t="inlineStr"/>
+      <c r="L1808" t="inlineStr"/>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="n">
+        <v>3732</v>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1809" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1809" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1809" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1809" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1809" t="inlineStr"/>
+      <c r="L1809" t="inlineStr"/>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="n">
+        <v>3733</v>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1810" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1810" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1810" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1810" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1810" t="inlineStr"/>
+      <c r="L1810" t="inlineStr"/>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="n">
+        <v>3734</v>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1811" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1811" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1811" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1811" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1811" t="inlineStr"/>
+      <c r="L1811" t="inlineStr"/>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="n">
+        <v>3735</v>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1812" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1812" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1812" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1812" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1812" t="inlineStr"/>
+      <c r="L1812" t="inlineStr"/>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="n">
+        <v>3736</v>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1813" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1813" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1813" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1813" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1813" t="inlineStr"/>
+      <c r="L1813" t="inlineStr"/>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="n">
+        <v>3737</v>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1814" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1814" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1814" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1814" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1814" t="inlineStr"/>
+      <c r="L1814" t="inlineStr"/>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="n">
+        <v>3738</v>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1815" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1815" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1815" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1815" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1815" t="inlineStr"/>
+      <c r="L1815" t="inlineStr"/>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="n">
+        <v>3739</v>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1816" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1816" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1816" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1816" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1816" t="inlineStr"/>
+      <c r="L1816" t="inlineStr"/>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="n">
+        <v>3740</v>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1817" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1817" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1817" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1817" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1817" t="inlineStr"/>
+      <c r="L1817" t="inlineStr"/>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="n">
+        <v>3741</v>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1818" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1818" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1818" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1818" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1818" t="inlineStr"/>
+      <c r="L1818" t="inlineStr"/>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="n">
+        <v>3742</v>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1819" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1819" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1819" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1819" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1819" t="inlineStr"/>
+      <c r="L1819" t="inlineStr"/>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="n">
+        <v>3743</v>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1820" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1820" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1820" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1820" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1820" t="inlineStr"/>
+      <c r="L1820" t="inlineStr"/>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="n">
+        <v>3744</v>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1821" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1821" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1821" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1821" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1821" t="inlineStr"/>
+      <c r="L1821" t="inlineStr"/>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="n">
+        <v>3745</v>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1822" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1822" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1822" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1822" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1822" t="inlineStr"/>
+      <c r="L1822" t="inlineStr"/>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="n">
+        <v>3746</v>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1823" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1823" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1823" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1823" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1823" t="inlineStr"/>
+      <c r="L1823" t="inlineStr"/>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="n">
+        <v>3747</v>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1824" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1824" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1824" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1824" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1824" t="inlineStr"/>
+      <c r="L1824" t="inlineStr"/>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="n">
+        <v>3748</v>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1825" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1825" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1825" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1825" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1825" t="inlineStr"/>
+      <c r="L1825" t="inlineStr"/>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="n">
+        <v>3749</v>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1826" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1826" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1826" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1826" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1826" t="inlineStr"/>
+      <c r="L1826" t="inlineStr"/>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="n">
+        <v>3750</v>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1827" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1827" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1827" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1827" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1827" t="inlineStr"/>
+      <c r="L1827" t="inlineStr"/>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="n">
+        <v>3751</v>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1828" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1828" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1828" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1828" t="inlineStr"/>
+      <c r="L1828" t="inlineStr"/>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="n">
+        <v>3752</v>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1829" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1829" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1829" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1829" t="inlineStr"/>
+      <c r="L1829" t="inlineStr"/>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="n">
+        <v>3753</v>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>2026-11-21</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1830" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1830" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1830" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1830" t="inlineStr"/>
+      <c r="L1830" t="inlineStr"/>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="n">
+        <v>3754</v>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>2026-11-22</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1831" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1831" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1831" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1831" t="inlineStr"/>
+      <c r="L1831" t="inlineStr"/>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="n">
+        <v>3755</v>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1832" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1832" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1832" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1832" t="inlineStr"/>
+      <c r="L1832" t="inlineStr"/>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="n">
+        <v>3756</v>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1833" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1833" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1833" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1833" t="inlineStr"/>
+      <c r="L1833" t="inlineStr"/>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="n">
+        <v>3757</v>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1834" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1834" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1834" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1834" t="inlineStr"/>
+      <c r="L1834" t="inlineStr"/>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="n">
+        <v>3758</v>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1835" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1835" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1835" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1835" t="inlineStr"/>
+      <c r="L1835" t="inlineStr"/>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="n">
+        <v>3759</v>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1836" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1836" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1836" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1836" t="inlineStr"/>
+      <c r="L1836" t="inlineStr"/>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="n">
+        <v>3760</v>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>2026-11-28</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1837" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1837" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1837" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1837" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1837" t="inlineStr"/>
+      <c r="L1837" t="inlineStr"/>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="n">
+        <v>3761</v>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>2026-11-29</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1838" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1838" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1838" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1838" t="inlineStr"/>
+      <c r="L1838" t="inlineStr"/>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="n">
+        <v>3762</v>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1839" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1839" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1839" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1839" t="inlineStr"/>
+      <c r="L1839" t="inlineStr"/>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="n">
+        <v>3763</v>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1840" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1840" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1840" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1840" t="inlineStr"/>
+      <c r="L1840" t="inlineStr"/>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="n">
+        <v>3764</v>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>2026-12-02</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1841" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1841" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1841" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1841" t="inlineStr"/>
+      <c r="L1841" t="inlineStr"/>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="n">
+        <v>3765</v>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1842" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1842" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1842" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1842" t="inlineStr"/>
+      <c r="L1842" t="inlineStr"/>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="n">
+        <v>3766</v>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1843" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1843" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1843" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1843" t="inlineStr"/>
+      <c r="L1843" t="inlineStr"/>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="n">
+        <v>3767</v>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1844" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1844" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1844" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1844" t="inlineStr"/>
+      <c r="L1844" t="inlineStr"/>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="n">
+        <v>3768</v>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>2026-12-06</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1845" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1845" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1845" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1845" t="inlineStr"/>
+      <c r="L1845" t="inlineStr"/>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="n">
+        <v>3769</v>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1846" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1846" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1846" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1846" t="inlineStr"/>
+      <c r="L1846" t="inlineStr"/>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="n">
+        <v>3770</v>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>2026-12-08</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1847" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1847" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1847" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1847" t="inlineStr"/>
+      <c r="L1847" t="inlineStr"/>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="n">
+        <v>3771</v>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1848" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1848" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1848" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1848" t="inlineStr"/>
+      <c r="L1848" t="inlineStr"/>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="n">
+        <v>3772</v>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1849" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1849" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1849" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1849" t="inlineStr"/>
+      <c r="L1849" t="inlineStr"/>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="n">
+        <v>3773</v>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1850" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1850" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1850" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1850" t="inlineStr"/>
+      <c r="L1850" t="inlineStr"/>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="n">
+        <v>3774</v>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>2026-12-12</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1851" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1851" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1851" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1851" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1851" t="inlineStr"/>
+      <c r="L1851" t="inlineStr"/>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="n">
+        <v>3775</v>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1852" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1852" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1852" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1852" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1852" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1852" t="inlineStr"/>
+      <c r="L1852" t="inlineStr"/>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="n">
+        <v>3776</v>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1853" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1853" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1853" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1853" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1853" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1853" t="inlineStr"/>
+      <c r="L1853" t="inlineStr"/>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="n">
+        <v>3777</v>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1854" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1854" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1854" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1854" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1854" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1854" t="inlineStr"/>
+      <c r="L1854" t="inlineStr"/>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="n">
+        <v>3778</v>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1855" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1855" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1855" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1855" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1855" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1855" t="inlineStr"/>
+      <c r="L1855" t="inlineStr"/>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="n">
+        <v>3779</v>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1856" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1856" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1856" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1856" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1856" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1856" t="inlineStr"/>
+      <c r="L1856" t="inlineStr"/>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="n">
+        <v>3780</v>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1857" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1857" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1857" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1857" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1857" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1857" t="inlineStr"/>
+      <c r="L1857" t="inlineStr"/>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="n">
+        <v>3781</v>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1858" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1858" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1858" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1858" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1858" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1858" t="inlineStr"/>
+      <c r="L1858" t="inlineStr"/>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="n">
+        <v>3782</v>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>2026-12-20</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1859" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1859" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1859" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1859" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1859" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1859" t="inlineStr"/>
+      <c r="L1859" t="inlineStr"/>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="n">
+        <v>3783</v>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>2026-12-21</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1860" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1860" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1860" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1860" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1860" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1860" t="inlineStr"/>
+      <c r="L1860" t="inlineStr"/>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="n">
+        <v>3784</v>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1861" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1861" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1861" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1861" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1861" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1861" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1861" t="inlineStr"/>
+      <c r="L1861" t="inlineStr"/>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="n">
+        <v>3785</v>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1862" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1862" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1862" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1862" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1862" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1862" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1862" t="inlineStr"/>
+      <c r="L1862" t="inlineStr"/>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="n">
+        <v>3786</v>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>2026-12-24</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1863" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1863" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1863" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1863" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1863" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1863" t="inlineStr"/>
+      <c r="L1863" t="inlineStr"/>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="n">
+        <v>3787</v>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1864" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1864" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1864" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1864" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1864" t="inlineStr"/>
+      <c r="L1864" t="inlineStr"/>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="n">
+        <v>3788</v>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1865" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1865" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1865" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1865" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1865" t="inlineStr"/>
+      <c r="L1865" t="inlineStr"/>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="n">
+        <v>3789</v>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>2026-12-27</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1866" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1866" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1866" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1866" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1866" t="inlineStr"/>
+      <c r="L1866" t="inlineStr"/>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="n">
+        <v>3790</v>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>2026-12-28</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1867" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1867" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1867" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1867" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1867" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1867" t="inlineStr"/>
+      <c r="L1867" t="inlineStr"/>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="n">
+        <v>3791</v>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1868" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1868" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1868" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1868" t="inlineStr"/>
+      <c r="L1868" t="inlineStr"/>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="n">
+        <v>3792</v>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1869" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1869" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1869" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1869" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1869" t="inlineStr"/>
+      <c r="L1869" t="inlineStr"/>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="n">
+        <v>3793</v>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1870" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1870" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1870" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1870" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1870" t="inlineStr"/>
+      <c r="L1870" t="inlineStr"/>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="n">
+        <v>3794</v>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1871" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1871" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1871" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1871" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1871" t="inlineStr"/>
+      <c r="L1871" t="inlineStr"/>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="n">
+        <v>3795</v>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1872" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1872" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1872" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1872" t="inlineStr"/>
+      <c r="L1872" t="inlineStr"/>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="n">
+        <v>3796</v>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1873" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1873" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1873" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1873" t="inlineStr"/>
+      <c r="L1873" t="inlineStr"/>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="n">
+        <v>3797</v>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>2027-01-04</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1874" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1874" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1874" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1874" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1874" t="inlineStr"/>
+      <c r="L1874" t="inlineStr"/>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="n">
+        <v>3798</v>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>2027-01-05</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1875" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1875" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1875" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1875" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1875" t="inlineStr"/>
+      <c r="L1875" t="inlineStr"/>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="n">
+        <v>3799</v>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1876" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1876" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1876" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1876" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1876" t="inlineStr"/>
+      <c r="L1876" t="inlineStr"/>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1877" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1877" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1877" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1877" t="inlineStr"/>
+      <c r="L1877" t="inlineStr"/>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="n">
+        <v>3801</v>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1878" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1878" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1878" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1878" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1878" t="inlineStr"/>
+      <c r="L1878" t="inlineStr"/>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="n">
+        <v>3802</v>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1879" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1879" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1879" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1879" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1879" t="inlineStr"/>
+      <c r="L1879" t="inlineStr"/>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="n">
+        <v>3803</v>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>2027-01-10</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1880" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1880" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1880" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1880" t="inlineStr"/>
+      <c r="L1880" t="inlineStr"/>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="n">
+        <v>3804</v>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>2027-01-11</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1881" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1881" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1881" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1881" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1881" t="inlineStr"/>
+      <c r="L1881" t="inlineStr"/>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="n">
+        <v>3805</v>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>2027-01-12</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1882" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1882" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1882" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1882" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1882" t="inlineStr"/>
+      <c r="L1882" t="inlineStr"/>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="n">
+        <v>3806</v>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1883" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1883" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1883" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1883" t="inlineStr"/>
+      <c r="L1883" t="inlineStr"/>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="n">
+        <v>3807</v>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1884" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1884" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1884" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1884" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1884" t="inlineStr"/>
+      <c r="L1884" t="inlineStr"/>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="n">
+        <v>3808</v>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1885" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1885" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1885" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1885" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1885" t="inlineStr"/>
+      <c r="L1885" t="inlineStr"/>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="n">
+        <v>3809</v>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>2027-01-16</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1886" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1886" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1886" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1886" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1886" t="inlineStr"/>
+      <c r="L1886" t="inlineStr"/>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="n">
+        <v>3810</v>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1887" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1887" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1887" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1887" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1887" t="inlineStr"/>
+      <c r="L1887" t="inlineStr"/>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="n">
+        <v>3811</v>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>2027-01-18</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1888" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1888" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1888" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1888" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1888" t="inlineStr"/>
+      <c r="L1888" t="inlineStr"/>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="n">
+        <v>3812</v>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>2027-01-19</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1889" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1889" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1889" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1889" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1889" t="inlineStr"/>
+      <c r="L1889" t="inlineStr"/>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="n">
+        <v>3813</v>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>2027-01-20</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1890" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1890" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1890" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1890" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1890" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1890" t="inlineStr"/>
+      <c r="L1890" t="inlineStr"/>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="n">
+        <v>3814</v>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1891" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1891" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1891" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1891" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1891" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1891" t="inlineStr"/>
+      <c r="L1891" t="inlineStr"/>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="n">
+        <v>3815</v>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1892" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1892" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1892" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1892" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1892" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1892" t="inlineStr"/>
+      <c r="L1892" t="inlineStr"/>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="n">
+        <v>3816</v>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1893" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1893" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1893" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1893" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1893" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1893" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1893" t="inlineStr"/>
+      <c r="L1893" t="inlineStr"/>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="n">
+        <v>3817</v>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>2027-01-24</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1894" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1894" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1894" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1894" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1894" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1894" t="inlineStr"/>
+      <c r="L1894" t="inlineStr"/>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="n">
+        <v>3818</v>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1895" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1895" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1895" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1895" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1895" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1895" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1895" t="inlineStr"/>
+      <c r="L1895" t="inlineStr"/>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="n">
+        <v>3819</v>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1896" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1896" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1896" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1896" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1896" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1896" t="inlineStr"/>
+      <c r="L1896" t="inlineStr"/>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="n">
+        <v>3820</v>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>2027-01-27</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1897" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1897" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1897" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1897" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1897" t="inlineStr"/>
+      <c r="L1897" t="inlineStr"/>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="n">
+        <v>3821</v>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>2027-01-28</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1898" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1898" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1898" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1898" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1898" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1898" t="inlineStr"/>
+      <c r="L1898" t="inlineStr"/>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="n">
+        <v>3822</v>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>2027-01-29</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1899" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1899" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1899" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1899" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1899" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1899" t="inlineStr"/>
+      <c r="L1899" t="inlineStr"/>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="n">
+        <v>3823</v>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>2027-01-30</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1900" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1900" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1900" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1900" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1900" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1900" t="inlineStr"/>
+      <c r="L1900" t="inlineStr"/>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="n">
+        <v>3824</v>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1901" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1901" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1901" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1901" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1901" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1901" t="inlineStr"/>
+      <c r="L1901" t="inlineStr"/>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="n">
+        <v>3825</v>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>2027-02-01</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1902" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1902" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1902" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1902" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1902" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1902" t="inlineStr"/>
+      <c r="L1902" t="inlineStr"/>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="n">
+        <v>3826</v>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>2027-02-02</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1903" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1903" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1903" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1903" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1903" t="inlineStr"/>
+      <c r="L1903" t="inlineStr"/>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="n">
+        <v>3827</v>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>2027-02-03</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1904" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1904" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1904" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1904" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1904" t="inlineStr"/>
+      <c r="L1904" t="inlineStr"/>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="n">
+        <v>3828</v>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>2027-02-04</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1905" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1905" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1905" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1905" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1905" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1905" t="inlineStr"/>
+      <c r="L1905" t="inlineStr"/>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="n">
+        <v>3829</v>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>2027-02-05</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1906" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1906" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1906" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1906" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1906" t="inlineStr"/>
+      <c r="L1906" t="inlineStr"/>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="n">
+        <v>3830</v>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>2027-02-06</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1907" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1907" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1907" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1907" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1907" t="inlineStr"/>
+      <c r="L1907" t="inlineStr"/>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="n">
+        <v>3831</v>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>2027-02-07</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1908" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1908" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1908" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1908" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1908" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1908" t="inlineStr"/>
+      <c r="L1908" t="inlineStr"/>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="n">
+        <v>3832</v>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>2027-02-08</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1909" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1909" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1909" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1909" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1909" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1909" t="inlineStr"/>
+      <c r="L1909" t="inlineStr"/>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="n">
+        <v>3833</v>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>2027-02-09</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1910" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1910" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1910" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1910" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1910" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1910" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1910" t="inlineStr"/>
+      <c r="L1910" t="inlineStr"/>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="n">
+        <v>3834</v>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>2027-02-10</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1911" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1911" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1911" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1911" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1911" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1911" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1911" t="inlineStr"/>
+      <c r="L1911" t="inlineStr"/>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="n">
+        <v>3835</v>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>2027-02-11</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1912" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1912" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1912" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1912" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1912" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1912" t="inlineStr"/>
+      <c r="L1912" t="inlineStr"/>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="n">
+        <v>3836</v>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>2027-02-12</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1913" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1913" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1913" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1913" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1913" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1913" t="inlineStr"/>
+      <c r="L1913" t="inlineStr"/>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="n">
+        <v>3837</v>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>2027-02-13</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1914" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1914" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1914" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1914" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1914" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1914" t="inlineStr"/>
+      <c r="L1914" t="inlineStr"/>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="n">
+        <v>3838</v>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>2027-02-14</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1915" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1915" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1915" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1915" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1915" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1915" t="inlineStr"/>
+      <c r="L1915" t="inlineStr"/>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="n">
+        <v>3839</v>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>2027-02-15</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1916" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1916" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1916" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1916" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1916" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1916" t="inlineStr"/>
+      <c r="L1916" t="inlineStr"/>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="n">
+        <v>3840</v>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>2027-02-16</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1917" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1917" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1917" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1917" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1917" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1917" t="inlineStr"/>
+      <c r="L1917" t="inlineStr"/>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="n">
+        <v>3841</v>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>2027-02-17</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1918" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1918" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1918" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1918" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1918" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1918" t="inlineStr"/>
+      <c r="L1918" t="inlineStr"/>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="n">
+        <v>3842</v>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>2027-02-18</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1919" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1919" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1919" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1919" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1919" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1919" t="inlineStr"/>
+      <c r="L1919" t="inlineStr"/>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="n">
+        <v>3843</v>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1920" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1920" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1920" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1920" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1920" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1920" t="inlineStr"/>
+      <c r="L1920" t="inlineStr"/>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="n">
+        <v>3844</v>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>2027-02-20</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1921" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1921" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1921" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1921" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1921" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1921" t="inlineStr"/>
+      <c r="L1921" t="inlineStr"/>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="n">
+        <v>3845</v>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>2027-02-21</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1922" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1922" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1922" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1922" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1922" t="inlineStr"/>
+      <c r="L1922" t="inlineStr"/>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="n">
+        <v>3846</v>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>2027-02-22</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1923" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1923" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1923" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1923" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1923" t="inlineStr"/>
+      <c r="L1923" t="inlineStr"/>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="n">
+        <v>3847</v>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1924" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1924" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1924" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1924" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1924" t="inlineStr"/>
+      <c r="L1924" t="inlineStr"/>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="n">
+        <v>3848</v>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>2027-02-24</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1925" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1925" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1925" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1925" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1925" t="inlineStr"/>
+      <c r="L1925" t="inlineStr"/>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="n">
+        <v>3849</v>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>2027-02-25</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1926" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1926" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1926" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1926" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1926" t="inlineStr"/>
+      <c r="L1926" t="inlineStr"/>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="n">
+        <v>3850</v>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>2027-02-26</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1927" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1927" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1927" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1927" t="inlineStr"/>
+      <c r="L1927" t="inlineStr"/>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="n">
+        <v>3851</v>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>2027-02-27</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1928" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1928" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1928" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1928" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1928" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1928" t="inlineStr"/>
+      <c r="L1928" t="inlineStr"/>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="n">
+        <v>3852</v>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1929" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1929" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1929" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1929" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1929" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1929" t="inlineStr"/>
+      <c r="L1929" t="inlineStr"/>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="n">
+        <v>3853</v>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1930" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1930" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1930" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1930" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1930" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1930" t="inlineStr"/>
+      <c r="L1930" t="inlineStr"/>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="n">
+        <v>3854</v>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>2027-03-02</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1931" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1931" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1931" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1931" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1931" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1931" t="inlineStr"/>
+      <c r="L1931" t="inlineStr"/>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="n">
+        <v>3855</v>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>2027-03-03</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1932" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1932" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1932" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1932" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1932" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1932" t="inlineStr"/>
+      <c r="L1932" t="inlineStr"/>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="n">
+        <v>3856</v>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>2027-03-04</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1933" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1933" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1933" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1933" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1933" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1933" t="inlineStr"/>
+      <c r="L1933" t="inlineStr"/>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="n">
+        <v>3857</v>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>2027-03-05</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1934" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1934" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1934" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1934" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1934" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1934" t="inlineStr"/>
+      <c r="L1934" t="inlineStr"/>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="n">
+        <v>3858</v>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>2027-03-06</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1935" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1935" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1935" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1935" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1935" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1935" t="inlineStr"/>
+      <c r="L1935" t="inlineStr"/>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="n">
+        <v>3859</v>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>2027-03-07</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1936" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1936" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1936" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1936" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1936" t="inlineStr"/>
+      <c r="L1936" t="inlineStr"/>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="n">
+        <v>3860</v>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>2027-03-08</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1937" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1937" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1937" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1937" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1937" t="inlineStr"/>
+      <c r="L1937" t="inlineStr"/>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="n">
+        <v>3861</v>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>Natália</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>2027-03-09</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>Leitura</t>
+        </is>
+      </c>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>Vocabulary</t>
+        </is>
+      </c>
+      <c r="G1938" t="inlineStr">
+        <is>
+          <t>Personalizado</t>
+        </is>
+      </c>
+      <c r="H1938" t="n">
+        <v>15</v>
+      </c>
+      <c r="I1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1938" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1938" t="inlineStr"/>
+      <c r="L1938" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -81450,13 +81450,17 @@
         <v>15</v>
       </c>
       <c r="I1758" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1758" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1758" t="inlineStr"/>
-      <c r="L1758" t="inlineStr"/>
+      <c r="L1758" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:12</t>
+        </is>
+      </c>
     </row>
     <row r="1759">
       <c r="A1759" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1938"/>
+  <dimension ref="A1:L1937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81368,7 +81368,7 @@
     </row>
     <row r="1757">
       <c r="A1757" t="n">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="B1757" t="inlineStr">
         <is>
@@ -81377,7 +81377,7 @@
       </c>
       <c r="C1757" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D1757" t="inlineStr">
@@ -81387,7 +81387,7 @@
       </c>
       <c r="E1757" t="inlineStr">
         <is>
-          <t>Leitura de Livro</t>
+          <t>Leitura</t>
         </is>
       </c>
       <c r="F1757" t="inlineStr">
@@ -81404,17 +81404,21 @@
         <v>15</v>
       </c>
       <c r="I1757" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J1757" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1757" t="inlineStr"/>
-      <c r="L1757" t="inlineStr"/>
+      <c r="L1757" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:12</t>
+        </is>
+      </c>
     </row>
     <row r="1758">
       <c r="A1758" t="n">
-        <v>3681</v>
+        <v>3682</v>
       </c>
       <c r="B1758" t="inlineStr">
         <is>
@@ -81423,7 +81427,7 @@
       </c>
       <c r="C1758" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D1758" t="inlineStr">
@@ -81450,21 +81454,17 @@
         <v>15</v>
       </c>
       <c r="I1758" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J1758" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1758" t="inlineStr"/>
-      <c r="L1758" t="inlineStr">
-        <is>
-          <t>2026-09-11 11:12</t>
-        </is>
-      </c>
+      <c r="L1758" t="inlineStr"/>
     </row>
     <row r="1759">
       <c r="A1759" t="n">
-        <v>3682</v>
+        <v>3683</v>
       </c>
       <c r="B1759" t="inlineStr">
         <is>
@@ -81473,7 +81473,7 @@
       </c>
       <c r="C1759" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D1759" t="inlineStr">
@@ -81510,7 +81510,7 @@
     </row>
     <row r="1760">
       <c r="A1760" t="n">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="B1760" t="inlineStr">
         <is>
@@ -81519,7 +81519,7 @@
       </c>
       <c r="C1760" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D1760" t="inlineStr">
@@ -81556,7 +81556,7 @@
     </row>
     <row r="1761">
       <c r="A1761" t="n">
-        <v>3684</v>
+        <v>3685</v>
       </c>
       <c r="B1761" t="inlineStr">
         <is>
@@ -81565,7 +81565,7 @@
       </c>
       <c r="C1761" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D1761" t="inlineStr">
@@ -81602,7 +81602,7 @@
     </row>
     <row r="1762">
       <c r="A1762" t="n">
-        <v>3685</v>
+        <v>3686</v>
       </c>
       <c r="B1762" t="inlineStr">
         <is>
@@ -81611,7 +81611,7 @@
       </c>
       <c r="C1762" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D1762" t="inlineStr">
@@ -81648,7 +81648,7 @@
     </row>
     <row r="1763">
       <c r="A1763" t="n">
-        <v>3686</v>
+        <v>3687</v>
       </c>
       <c r="B1763" t="inlineStr">
         <is>
@@ -81657,7 +81657,7 @@
       </c>
       <c r="C1763" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D1763" t="inlineStr">
@@ -81694,7 +81694,7 @@
     </row>
     <row r="1764">
       <c r="A1764" t="n">
-        <v>3687</v>
+        <v>3688</v>
       </c>
       <c r="B1764" t="inlineStr">
         <is>
@@ -81703,7 +81703,7 @@
       </c>
       <c r="C1764" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D1764" t="inlineStr">
@@ -81740,7 +81740,7 @@
     </row>
     <row r="1765">
       <c r="A1765" t="n">
-        <v>3688</v>
+        <v>3689</v>
       </c>
       <c r="B1765" t="inlineStr">
         <is>
@@ -81749,7 +81749,7 @@
       </c>
       <c r="C1765" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D1765" t="inlineStr">
@@ -81786,7 +81786,7 @@
     </row>
     <row r="1766">
       <c r="A1766" t="n">
-        <v>3689</v>
+        <v>3690</v>
       </c>
       <c r="B1766" t="inlineStr">
         <is>
@@ -81795,7 +81795,7 @@
       </c>
       <c r="C1766" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D1766" t="inlineStr">
@@ -81832,7 +81832,7 @@
     </row>
     <row r="1767">
       <c r="A1767" t="n">
-        <v>3690</v>
+        <v>3691</v>
       </c>
       <c r="B1767" t="inlineStr">
         <is>
@@ -81841,7 +81841,7 @@
       </c>
       <c r="C1767" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D1767" t="inlineStr">
@@ -81878,7 +81878,7 @@
     </row>
     <row r="1768">
       <c r="A1768" t="n">
-        <v>3691</v>
+        <v>3692</v>
       </c>
       <c r="B1768" t="inlineStr">
         <is>
@@ -81887,7 +81887,7 @@
       </c>
       <c r="C1768" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D1768" t="inlineStr">
@@ -81924,7 +81924,7 @@
     </row>
     <row r="1769">
       <c r="A1769" t="n">
-        <v>3692</v>
+        <v>3693</v>
       </c>
       <c r="B1769" t="inlineStr">
         <is>
@@ -81933,7 +81933,7 @@
       </c>
       <c r="C1769" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D1769" t="inlineStr">
@@ -81970,7 +81970,7 @@
     </row>
     <row r="1770">
       <c r="A1770" t="n">
-        <v>3693</v>
+        <v>3694</v>
       </c>
       <c r="B1770" t="inlineStr">
         <is>
@@ -81979,7 +81979,7 @@
       </c>
       <c r="C1770" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D1770" t="inlineStr">
@@ -82016,7 +82016,7 @@
     </row>
     <row r="1771">
       <c r="A1771" t="n">
-        <v>3694</v>
+        <v>3695</v>
       </c>
       <c r="B1771" t="inlineStr">
         <is>
@@ -82025,7 +82025,7 @@
       </c>
       <c r="C1771" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D1771" t="inlineStr">
@@ -82062,7 +82062,7 @@
     </row>
     <row r="1772">
       <c r="A1772" t="n">
-        <v>3695</v>
+        <v>3696</v>
       </c>
       <c r="B1772" t="inlineStr">
         <is>
@@ -82071,7 +82071,7 @@
       </c>
       <c r="C1772" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D1772" t="inlineStr">
@@ -82108,7 +82108,7 @@
     </row>
     <row r="1773">
       <c r="A1773" t="n">
-        <v>3696</v>
+        <v>3697</v>
       </c>
       <c r="B1773" t="inlineStr">
         <is>
@@ -82117,7 +82117,7 @@
       </c>
       <c r="C1773" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D1773" t="inlineStr">
@@ -82154,7 +82154,7 @@
     </row>
     <row r="1774">
       <c r="A1774" t="n">
-        <v>3697</v>
+        <v>3698</v>
       </c>
       <c r="B1774" t="inlineStr">
         <is>
@@ -82163,7 +82163,7 @@
       </c>
       <c r="C1774" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D1774" t="inlineStr">
@@ -82200,7 +82200,7 @@
     </row>
     <row r="1775">
       <c r="A1775" t="n">
-        <v>3698</v>
+        <v>3699</v>
       </c>
       <c r="B1775" t="inlineStr">
         <is>
@@ -82209,7 +82209,7 @@
       </c>
       <c r="C1775" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D1775" t="inlineStr">
@@ -82246,7 +82246,7 @@
     </row>
     <row r="1776">
       <c r="A1776" t="n">
-        <v>3699</v>
+        <v>3700</v>
       </c>
       <c r="B1776" t="inlineStr">
         <is>
@@ -82255,7 +82255,7 @@
       </c>
       <c r="C1776" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D1776" t="inlineStr">
@@ -82292,7 +82292,7 @@
     </row>
     <row r="1777">
       <c r="A1777" t="n">
-        <v>3700</v>
+        <v>3701</v>
       </c>
       <c r="B1777" t="inlineStr">
         <is>
@@ -82301,7 +82301,7 @@
       </c>
       <c r="C1777" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D1777" t="inlineStr">
@@ -82338,7 +82338,7 @@
     </row>
     <row r="1778">
       <c r="A1778" t="n">
-        <v>3701</v>
+        <v>3702</v>
       </c>
       <c r="B1778" t="inlineStr">
         <is>
@@ -82347,7 +82347,7 @@
       </c>
       <c r="C1778" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D1778" t="inlineStr">
@@ -82384,7 +82384,7 @@
     </row>
     <row r="1779">
       <c r="A1779" t="n">
-        <v>3702</v>
+        <v>3703</v>
       </c>
       <c r="B1779" t="inlineStr">
         <is>
@@ -82393,7 +82393,7 @@
       </c>
       <c r="C1779" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D1779" t="inlineStr">
@@ -82430,7 +82430,7 @@
     </row>
     <row r="1780">
       <c r="A1780" t="n">
-        <v>3703</v>
+        <v>3704</v>
       </c>
       <c r="B1780" t="inlineStr">
         <is>
@@ -82439,7 +82439,7 @@
       </c>
       <c r="C1780" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D1780" t="inlineStr">
@@ -82476,7 +82476,7 @@
     </row>
     <row r="1781">
       <c r="A1781" t="n">
-        <v>3704</v>
+        <v>3705</v>
       </c>
       <c r="B1781" t="inlineStr">
         <is>
@@ -82485,7 +82485,7 @@
       </c>
       <c r="C1781" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D1781" t="inlineStr">
@@ -82522,7 +82522,7 @@
     </row>
     <row r="1782">
       <c r="A1782" t="n">
-        <v>3705</v>
+        <v>3706</v>
       </c>
       <c r="B1782" t="inlineStr">
         <is>
@@ -82531,7 +82531,7 @@
       </c>
       <c r="C1782" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D1782" t="inlineStr">
@@ -82568,7 +82568,7 @@
     </row>
     <row r="1783">
       <c r="A1783" t="n">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="B1783" t="inlineStr">
         <is>
@@ -82577,7 +82577,7 @@
       </c>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D1783" t="inlineStr">
@@ -82614,7 +82614,7 @@
     </row>
     <row r="1784">
       <c r="A1784" t="n">
-        <v>3707</v>
+        <v>3708</v>
       </c>
       <c r="B1784" t="inlineStr">
         <is>
@@ -82623,7 +82623,7 @@
       </c>
       <c r="C1784" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D1784" t="inlineStr">
@@ -82660,7 +82660,7 @@
     </row>
     <row r="1785">
       <c r="A1785" t="n">
-        <v>3708</v>
+        <v>3709</v>
       </c>
       <c r="B1785" t="inlineStr">
         <is>
@@ -82669,7 +82669,7 @@
       </c>
       <c r="C1785" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D1785" t="inlineStr">
@@ -82706,7 +82706,7 @@
     </row>
     <row r="1786">
       <c r="A1786" t="n">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="B1786" t="inlineStr">
         <is>
@@ -82715,7 +82715,7 @@
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D1786" t="inlineStr">
@@ -82752,7 +82752,7 @@
     </row>
     <row r="1787">
       <c r="A1787" t="n">
-        <v>3710</v>
+        <v>3711</v>
       </c>
       <c r="B1787" t="inlineStr">
         <is>
@@ -82761,7 +82761,7 @@
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D1787" t="inlineStr">
@@ -82798,7 +82798,7 @@
     </row>
     <row r="1788">
       <c r="A1788" t="n">
-        <v>3711</v>
+        <v>3712</v>
       </c>
       <c r="B1788" t="inlineStr">
         <is>
@@ -82807,7 +82807,7 @@
       </c>
       <c r="C1788" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D1788" t="inlineStr">
@@ -82844,7 +82844,7 @@
     </row>
     <row r="1789">
       <c r="A1789" t="n">
-        <v>3712</v>
+        <v>3713</v>
       </c>
       <c r="B1789" t="inlineStr">
         <is>
@@ -82853,7 +82853,7 @@
       </c>
       <c r="C1789" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D1789" t="inlineStr">
@@ -82890,7 +82890,7 @@
     </row>
     <row r="1790">
       <c r="A1790" t="n">
-        <v>3713</v>
+        <v>3714</v>
       </c>
       <c r="B1790" t="inlineStr">
         <is>
@@ -82899,7 +82899,7 @@
       </c>
       <c r="C1790" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D1790" t="inlineStr">
@@ -82936,7 +82936,7 @@
     </row>
     <row r="1791">
       <c r="A1791" t="n">
-        <v>3714</v>
+        <v>3715</v>
       </c>
       <c r="B1791" t="inlineStr">
         <is>
@@ -82945,7 +82945,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D1791" t="inlineStr">
@@ -82982,7 +82982,7 @@
     </row>
     <row r="1792">
       <c r="A1792" t="n">
-        <v>3715</v>
+        <v>3716</v>
       </c>
       <c r="B1792" t="inlineStr">
         <is>
@@ -82991,7 +82991,7 @@
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D1792" t="inlineStr">
@@ -83028,7 +83028,7 @@
     </row>
     <row r="1793">
       <c r="A1793" t="n">
-        <v>3716</v>
+        <v>3717</v>
       </c>
       <c r="B1793" t="inlineStr">
         <is>
@@ -83037,7 +83037,7 @@
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D1793" t="inlineStr">
@@ -83074,7 +83074,7 @@
     </row>
     <row r="1794">
       <c r="A1794" t="n">
-        <v>3717</v>
+        <v>3718</v>
       </c>
       <c r="B1794" t="inlineStr">
         <is>
@@ -83083,7 +83083,7 @@
       </c>
       <c r="C1794" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D1794" t="inlineStr">
@@ -83120,7 +83120,7 @@
     </row>
     <row r="1795">
       <c r="A1795" t="n">
-        <v>3718</v>
+        <v>3719</v>
       </c>
       <c r="B1795" t="inlineStr">
         <is>
@@ -83129,7 +83129,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D1795" t="inlineStr">
@@ -83166,7 +83166,7 @@
     </row>
     <row r="1796">
       <c r="A1796" t="n">
-        <v>3719</v>
+        <v>3720</v>
       </c>
       <c r="B1796" t="inlineStr">
         <is>
@@ -83175,7 +83175,7 @@
       </c>
       <c r="C1796" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1796" t="inlineStr">
@@ -83212,7 +83212,7 @@
     </row>
     <row r="1797">
       <c r="A1797" t="n">
-        <v>3720</v>
+        <v>3721</v>
       </c>
       <c r="B1797" t="inlineStr">
         <is>
@@ -83221,7 +83221,7 @@
       </c>
       <c r="C1797" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D1797" t="inlineStr">
@@ -83258,7 +83258,7 @@
     </row>
     <row r="1798">
       <c r="A1798" t="n">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="B1798" t="inlineStr">
         <is>
@@ -83267,7 +83267,7 @@
       </c>
       <c r="C1798" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D1798" t="inlineStr">
@@ -83304,7 +83304,7 @@
     </row>
     <row r="1799">
       <c r="A1799" t="n">
-        <v>3722</v>
+        <v>3723</v>
       </c>
       <c r="B1799" t="inlineStr">
         <is>
@@ -83313,7 +83313,7 @@
       </c>
       <c r="C1799" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D1799" t="inlineStr">
@@ -83350,7 +83350,7 @@
     </row>
     <row r="1800">
       <c r="A1800" t="n">
-        <v>3723</v>
+        <v>3724</v>
       </c>
       <c r="B1800" t="inlineStr">
         <is>
@@ -83359,7 +83359,7 @@
       </c>
       <c r="C1800" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D1800" t="inlineStr">
@@ -83396,7 +83396,7 @@
     </row>
     <row r="1801">
       <c r="A1801" t="n">
-        <v>3724</v>
+        <v>3725</v>
       </c>
       <c r="B1801" t="inlineStr">
         <is>
@@ -83405,7 +83405,7 @@
       </c>
       <c r="C1801" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D1801" t="inlineStr">
@@ -83442,7 +83442,7 @@
     </row>
     <row r="1802">
       <c r="A1802" t="n">
-        <v>3725</v>
+        <v>3726</v>
       </c>
       <c r="B1802" t="inlineStr">
         <is>
@@ -83451,7 +83451,7 @@
       </c>
       <c r="C1802" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D1802" t="inlineStr">
@@ -83488,7 +83488,7 @@
     </row>
     <row r="1803">
       <c r="A1803" t="n">
-        <v>3726</v>
+        <v>3727</v>
       </c>
       <c r="B1803" t="inlineStr">
         <is>
@@ -83497,7 +83497,7 @@
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D1803" t="inlineStr">
@@ -83534,7 +83534,7 @@
     </row>
     <row r="1804">
       <c r="A1804" t="n">
-        <v>3727</v>
+        <v>3728</v>
       </c>
       <c r="B1804" t="inlineStr">
         <is>
@@ -83543,7 +83543,7 @@
       </c>
       <c r="C1804" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D1804" t="inlineStr">
@@ -83580,7 +83580,7 @@
     </row>
     <row r="1805">
       <c r="A1805" t="n">
-        <v>3728</v>
+        <v>3729</v>
       </c>
       <c r="B1805" t="inlineStr">
         <is>
@@ -83589,7 +83589,7 @@
       </c>
       <c r="C1805" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D1805" t="inlineStr">
@@ -83626,7 +83626,7 @@
     </row>
     <row r="1806">
       <c r="A1806" t="n">
-        <v>3729</v>
+        <v>3730</v>
       </c>
       <c r="B1806" t="inlineStr">
         <is>
@@ -83635,7 +83635,7 @@
       </c>
       <c r="C1806" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D1806" t="inlineStr">
@@ -83672,7 +83672,7 @@
     </row>
     <row r="1807">
       <c r="A1807" t="n">
-        <v>3730</v>
+        <v>3731</v>
       </c>
       <c r="B1807" t="inlineStr">
         <is>
@@ -83681,7 +83681,7 @@
       </c>
       <c r="C1807" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D1807" t="inlineStr">
@@ -83718,7 +83718,7 @@
     </row>
     <row r="1808">
       <c r="A1808" t="n">
-        <v>3731</v>
+        <v>3732</v>
       </c>
       <c r="B1808" t="inlineStr">
         <is>
@@ -83727,7 +83727,7 @@
       </c>
       <c r="C1808" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D1808" t="inlineStr">
@@ -83764,7 +83764,7 @@
     </row>
     <row r="1809">
       <c r="A1809" t="n">
-        <v>3732</v>
+        <v>3733</v>
       </c>
       <c r="B1809" t="inlineStr">
         <is>
@@ -83773,7 +83773,7 @@
       </c>
       <c r="C1809" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D1809" t="inlineStr">
@@ -83810,7 +83810,7 @@
     </row>
     <row r="1810">
       <c r="A1810" t="n">
-        <v>3733</v>
+        <v>3734</v>
       </c>
       <c r="B1810" t="inlineStr">
         <is>
@@ -83819,7 +83819,7 @@
       </c>
       <c r="C1810" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="D1810" t="inlineStr">
@@ -83856,7 +83856,7 @@
     </row>
     <row r="1811">
       <c r="A1811" t="n">
-        <v>3734</v>
+        <v>3735</v>
       </c>
       <c r="B1811" t="inlineStr">
         <is>
@@ -83865,7 +83865,7 @@
       </c>
       <c r="C1811" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="D1811" t="inlineStr">
@@ -83902,7 +83902,7 @@
     </row>
     <row r="1812">
       <c r="A1812" t="n">
-        <v>3735</v>
+        <v>3736</v>
       </c>
       <c r="B1812" t="inlineStr">
         <is>
@@ -83911,7 +83911,7 @@
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D1812" t="inlineStr">
@@ -83948,7 +83948,7 @@
     </row>
     <row r="1813">
       <c r="A1813" t="n">
-        <v>3736</v>
+        <v>3737</v>
       </c>
       <c r="B1813" t="inlineStr">
         <is>
@@ -83957,7 +83957,7 @@
       </c>
       <c r="C1813" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D1813" t="inlineStr">
@@ -83994,7 +83994,7 @@
     </row>
     <row r="1814">
       <c r="A1814" t="n">
-        <v>3737</v>
+        <v>3738</v>
       </c>
       <c r="B1814" t="inlineStr">
         <is>
@@ -84003,7 +84003,7 @@
       </c>
       <c r="C1814" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D1814" t="inlineStr">
@@ -84040,7 +84040,7 @@
     </row>
     <row r="1815">
       <c r="A1815" t="n">
-        <v>3738</v>
+        <v>3739</v>
       </c>
       <c r="B1815" t="inlineStr">
         <is>
@@ -84049,7 +84049,7 @@
       </c>
       <c r="C1815" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D1815" t="inlineStr">
@@ -84086,7 +84086,7 @@
     </row>
     <row r="1816">
       <c r="A1816" t="n">
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="B1816" t="inlineStr">
         <is>
@@ -84095,7 +84095,7 @@
       </c>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">
@@ -84132,7 +84132,7 @@
     </row>
     <row r="1817">
       <c r="A1817" t="n">
-        <v>3740</v>
+        <v>3741</v>
       </c>
       <c r="B1817" t="inlineStr">
         <is>
@@ -84141,7 +84141,7 @@
       </c>
       <c r="C1817" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D1817" t="inlineStr">
@@ -84178,7 +84178,7 @@
     </row>
     <row r="1818">
       <c r="A1818" t="n">
-        <v>3741</v>
+        <v>3742</v>
       </c>
       <c r="B1818" t="inlineStr">
         <is>
@@ -84187,7 +84187,7 @@
       </c>
       <c r="C1818" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D1818" t="inlineStr">
@@ -84224,7 +84224,7 @@
     </row>
     <row r="1819">
       <c r="A1819" t="n">
-        <v>3742</v>
+        <v>3743</v>
       </c>
       <c r="B1819" t="inlineStr">
         <is>
@@ -84233,7 +84233,7 @@
       </c>
       <c r="C1819" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="D1819" t="inlineStr">
@@ -84270,7 +84270,7 @@
     </row>
     <row r="1820">
       <c r="A1820" t="n">
-        <v>3743</v>
+        <v>3744</v>
       </c>
       <c r="B1820" t="inlineStr">
         <is>
@@ -84279,7 +84279,7 @@
       </c>
       <c r="C1820" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="D1820" t="inlineStr">
@@ -84316,7 +84316,7 @@
     </row>
     <row r="1821">
       <c r="A1821" t="n">
-        <v>3744</v>
+        <v>3745</v>
       </c>
       <c r="B1821" t="inlineStr">
         <is>
@@ -84325,7 +84325,7 @@
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D1821" t="inlineStr">
@@ -84362,7 +84362,7 @@
     </row>
     <row r="1822">
       <c r="A1822" t="n">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="B1822" t="inlineStr">
         <is>
@@ -84371,7 +84371,7 @@
       </c>
       <c r="C1822" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="D1822" t="inlineStr">
@@ -84408,7 +84408,7 @@
     </row>
     <row r="1823">
       <c r="A1823" t="n">
-        <v>3746</v>
+        <v>3747</v>
       </c>
       <c r="B1823" t="inlineStr">
         <is>
@@ -84417,7 +84417,7 @@
       </c>
       <c r="C1823" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D1823" t="inlineStr">
@@ -84454,7 +84454,7 @@
     </row>
     <row r="1824">
       <c r="A1824" t="n">
-        <v>3747</v>
+        <v>3748</v>
       </c>
       <c r="B1824" t="inlineStr">
         <is>
@@ -84463,7 +84463,7 @@
       </c>
       <c r="C1824" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D1824" t="inlineStr">
@@ -84500,7 +84500,7 @@
     </row>
     <row r="1825">
       <c r="A1825" t="n">
-        <v>3748</v>
+        <v>3749</v>
       </c>
       <c r="B1825" t="inlineStr">
         <is>
@@ -84509,7 +84509,7 @@
       </c>
       <c r="C1825" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="D1825" t="inlineStr">
@@ -84546,7 +84546,7 @@
     </row>
     <row r="1826">
       <c r="A1826" t="n">
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="B1826" t="inlineStr">
         <is>
@@ -84555,7 +84555,7 @@
       </c>
       <c r="C1826" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D1826" t="inlineStr">
@@ -84592,7 +84592,7 @@
     </row>
     <row r="1827">
       <c r="A1827" t="n">
-        <v>3750</v>
+        <v>3751</v>
       </c>
       <c r="B1827" t="inlineStr">
         <is>
@@ -84601,7 +84601,7 @@
       </c>
       <c r="C1827" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="D1827" t="inlineStr">
@@ -84638,7 +84638,7 @@
     </row>
     <row r="1828">
       <c r="A1828" t="n">
-        <v>3751</v>
+        <v>3752</v>
       </c>
       <c r="B1828" t="inlineStr">
         <is>
@@ -84647,7 +84647,7 @@
       </c>
       <c r="C1828" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D1828" t="inlineStr">
@@ -84684,7 +84684,7 @@
     </row>
     <row r="1829">
       <c r="A1829" t="n">
-        <v>3752</v>
+        <v>3753</v>
       </c>
       <c r="B1829" t="inlineStr">
         <is>
@@ -84693,7 +84693,7 @@
       </c>
       <c r="C1829" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D1829" t="inlineStr">
@@ -84730,7 +84730,7 @@
     </row>
     <row r="1830">
       <c r="A1830" t="n">
-        <v>3753</v>
+        <v>3754</v>
       </c>
       <c r="B1830" t="inlineStr">
         <is>
@@ -84739,7 +84739,7 @@
       </c>
       <c r="C1830" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D1830" t="inlineStr">
@@ -84776,7 +84776,7 @@
     </row>
     <row r="1831">
       <c r="A1831" t="n">
-        <v>3754</v>
+        <v>3755</v>
       </c>
       <c r="B1831" t="inlineStr">
         <is>
@@ -84785,7 +84785,7 @@
       </c>
       <c r="C1831" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="D1831" t="inlineStr">
@@ -84822,7 +84822,7 @@
     </row>
     <row r="1832">
       <c r="A1832" t="n">
-        <v>3755</v>
+        <v>3756</v>
       </c>
       <c r="B1832" t="inlineStr">
         <is>
@@ -84831,7 +84831,7 @@
       </c>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
@@ -84868,7 +84868,7 @@
     </row>
     <row r="1833">
       <c r="A1833" t="n">
-        <v>3756</v>
+        <v>3757</v>
       </c>
       <c r="B1833" t="inlineStr">
         <is>
@@ -84877,7 +84877,7 @@
       </c>
       <c r="C1833" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="D1833" t="inlineStr">
@@ -84914,7 +84914,7 @@
     </row>
     <row r="1834">
       <c r="A1834" t="n">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="B1834" t="inlineStr">
         <is>
@@ -84923,7 +84923,7 @@
       </c>
       <c r="C1834" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="D1834" t="inlineStr">
@@ -84960,7 +84960,7 @@
     </row>
     <row r="1835">
       <c r="A1835" t="n">
-        <v>3758</v>
+        <v>3759</v>
       </c>
       <c r="B1835" t="inlineStr">
         <is>
@@ -84969,7 +84969,7 @@
       </c>
       <c r="C1835" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D1835" t="inlineStr">
@@ -85006,7 +85006,7 @@
     </row>
     <row r="1836">
       <c r="A1836" t="n">
-        <v>3759</v>
+        <v>3760</v>
       </c>
       <c r="B1836" t="inlineStr">
         <is>
@@ -85015,7 +85015,7 @@
       </c>
       <c r="C1836" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D1836" t="inlineStr">
@@ -85052,7 +85052,7 @@
     </row>
     <row r="1837">
       <c r="A1837" t="n">
-        <v>3760</v>
+        <v>3761</v>
       </c>
       <c r="B1837" t="inlineStr">
         <is>
@@ -85061,7 +85061,7 @@
       </c>
       <c r="C1837" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="D1837" t="inlineStr">
@@ -85098,7 +85098,7 @@
     </row>
     <row r="1838">
       <c r="A1838" t="n">
-        <v>3761</v>
+        <v>3762</v>
       </c>
       <c r="B1838" t="inlineStr">
         <is>
@@ -85107,7 +85107,7 @@
       </c>
       <c r="C1838" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D1838" t="inlineStr">
@@ -85144,7 +85144,7 @@
     </row>
     <row r="1839">
       <c r="A1839" t="n">
-        <v>3762</v>
+        <v>3763</v>
       </c>
       <c r="B1839" t="inlineStr">
         <is>
@@ -85153,7 +85153,7 @@
       </c>
       <c r="C1839" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="D1839" t="inlineStr">
@@ -85190,7 +85190,7 @@
     </row>
     <row r="1840">
       <c r="A1840" t="n">
-        <v>3763</v>
+        <v>3764</v>
       </c>
       <c r="B1840" t="inlineStr">
         <is>
@@ -85199,7 +85199,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
@@ -85236,7 +85236,7 @@
     </row>
     <row r="1841">
       <c r="A1841" t="n">
-        <v>3764</v>
+        <v>3765</v>
       </c>
       <c r="B1841" t="inlineStr">
         <is>
@@ -85245,7 +85245,7 @@
       </c>
       <c r="C1841" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D1841" t="inlineStr">
@@ -85282,7 +85282,7 @@
     </row>
     <row r="1842">
       <c r="A1842" t="n">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="B1842" t="inlineStr">
         <is>
@@ -85291,7 +85291,7 @@
       </c>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D1842" t="inlineStr">
@@ -85328,7 +85328,7 @@
     </row>
     <row r="1843">
       <c r="A1843" t="n">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="B1843" t="inlineStr">
         <is>
@@ -85337,7 +85337,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="D1843" t="inlineStr">
@@ -85374,7 +85374,7 @@
     </row>
     <row r="1844">
       <c r="A1844" t="n">
-        <v>3767</v>
+        <v>3768</v>
       </c>
       <c r="B1844" t="inlineStr">
         <is>
@@ -85383,7 +85383,7 @@
       </c>
       <c r="C1844" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="D1844" t="inlineStr">
@@ -85420,7 +85420,7 @@
     </row>
     <row r="1845">
       <c r="A1845" t="n">
-        <v>3768</v>
+        <v>3769</v>
       </c>
       <c r="B1845" t="inlineStr">
         <is>
@@ -85429,7 +85429,7 @@
       </c>
       <c r="C1845" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D1845" t="inlineStr">
@@ -85466,7 +85466,7 @@
     </row>
     <row r="1846">
       <c r="A1846" t="n">
-        <v>3769</v>
+        <v>3770</v>
       </c>
       <c r="B1846" t="inlineStr">
         <is>
@@ -85475,7 +85475,7 @@
       </c>
       <c r="C1846" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="D1846" t="inlineStr">
@@ -85512,7 +85512,7 @@
     </row>
     <row r="1847">
       <c r="A1847" t="n">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="B1847" t="inlineStr">
         <is>
@@ -85521,7 +85521,7 @@
       </c>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
@@ -85558,7 +85558,7 @@
     </row>
     <row r="1848">
       <c r="A1848" t="n">
-        <v>3771</v>
+        <v>3772</v>
       </c>
       <c r="B1848" t="inlineStr">
         <is>
@@ -85567,7 +85567,7 @@
       </c>
       <c r="C1848" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D1848" t="inlineStr">
@@ -85604,7 +85604,7 @@
     </row>
     <row r="1849">
       <c r="A1849" t="n">
-        <v>3772</v>
+        <v>3773</v>
       </c>
       <c r="B1849" t="inlineStr">
         <is>
@@ -85613,7 +85613,7 @@
       </c>
       <c r="C1849" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D1849" t="inlineStr">
@@ -85650,7 +85650,7 @@
     </row>
     <row r="1850">
       <c r="A1850" t="n">
-        <v>3773</v>
+        <v>3774</v>
       </c>
       <c r="B1850" t="inlineStr">
         <is>
@@ -85659,7 +85659,7 @@
       </c>
       <c r="C1850" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="D1850" t="inlineStr">
@@ -85696,7 +85696,7 @@
     </row>
     <row r="1851">
       <c r="A1851" t="n">
-        <v>3774</v>
+        <v>3775</v>
       </c>
       <c r="B1851" t="inlineStr">
         <is>
@@ -85705,7 +85705,7 @@
       </c>
       <c r="C1851" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D1851" t="inlineStr">
@@ -85742,7 +85742,7 @@
     </row>
     <row r="1852">
       <c r="A1852" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="B1852" t="inlineStr">
         <is>
@@ -85751,7 +85751,7 @@
       </c>
       <c r="C1852" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D1852" t="inlineStr">
@@ -85788,7 +85788,7 @@
     </row>
     <row r="1853">
       <c r="A1853" t="n">
-        <v>3776</v>
+        <v>3777</v>
       </c>
       <c r="B1853" t="inlineStr">
         <is>
@@ -85797,7 +85797,7 @@
       </c>
       <c r="C1853" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="D1853" t="inlineStr">
@@ -85834,7 +85834,7 @@
     </row>
     <row r="1854">
       <c r="A1854" t="n">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="B1854" t="inlineStr">
         <is>
@@ -85843,7 +85843,7 @@
       </c>
       <c r="C1854" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="D1854" t="inlineStr">
@@ -85880,7 +85880,7 @@
     </row>
     <row r="1855">
       <c r="A1855" t="n">
-        <v>3778</v>
+        <v>3779</v>
       </c>
       <c r="B1855" t="inlineStr">
         <is>
@@ -85889,7 +85889,7 @@
       </c>
       <c r="C1855" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D1855" t="inlineStr">
@@ -85926,7 +85926,7 @@
     </row>
     <row r="1856">
       <c r="A1856" t="n">
-        <v>3779</v>
+        <v>3780</v>
       </c>
       <c r="B1856" t="inlineStr">
         <is>
@@ -85935,7 +85935,7 @@
       </c>
       <c r="C1856" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
@@ -85972,7 +85972,7 @@
     </row>
     <row r="1857">
       <c r="A1857" t="n">
-        <v>3780</v>
+        <v>3781</v>
       </c>
       <c r="B1857" t="inlineStr">
         <is>
@@ -85981,7 +85981,7 @@
       </c>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -86018,7 +86018,7 @@
     </row>
     <row r="1858">
       <c r="A1858" t="n">
-        <v>3781</v>
+        <v>3782</v>
       </c>
       <c r="B1858" t="inlineStr">
         <is>
@@ -86027,7 +86027,7 @@
       </c>
       <c r="C1858" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D1858" t="inlineStr">
@@ -86064,7 +86064,7 @@
     </row>
     <row r="1859">
       <c r="A1859" t="n">
-        <v>3782</v>
+        <v>3783</v>
       </c>
       <c r="B1859" t="inlineStr">
         <is>
@@ -86073,7 +86073,7 @@
       </c>
       <c r="C1859" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D1859" t="inlineStr">
@@ -86110,7 +86110,7 @@
     </row>
     <row r="1860">
       <c r="A1860" t="n">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="B1860" t="inlineStr">
         <is>
@@ -86119,7 +86119,7 @@
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="D1860" t="inlineStr">
@@ -86156,7 +86156,7 @@
     </row>
     <row r="1861">
       <c r="A1861" t="n">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="B1861" t="inlineStr">
         <is>
@@ -86165,7 +86165,7 @@
       </c>
       <c r="C1861" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="D1861" t="inlineStr">
@@ -86202,7 +86202,7 @@
     </row>
     <row r="1862">
       <c r="A1862" t="n">
-        <v>3785</v>
+        <v>3786</v>
       </c>
       <c r="B1862" t="inlineStr">
         <is>
@@ -86211,7 +86211,7 @@
       </c>
       <c r="C1862" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="D1862" t="inlineStr">
@@ -86248,7 +86248,7 @@
     </row>
     <row r="1863">
       <c r="A1863" t="n">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="B1863" t="inlineStr">
         <is>
@@ -86257,7 +86257,7 @@
       </c>
       <c r="C1863" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="D1863" t="inlineStr">
@@ -86294,7 +86294,7 @@
     </row>
     <row r="1864">
       <c r="A1864" t="n">
-        <v>3787</v>
+        <v>3788</v>
       </c>
       <c r="B1864" t="inlineStr">
         <is>
@@ -86303,7 +86303,7 @@
       </c>
       <c r="C1864" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="D1864" t="inlineStr">
@@ -86340,7 +86340,7 @@
     </row>
     <row r="1865">
       <c r="A1865" t="n">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="B1865" t="inlineStr">
         <is>
@@ -86349,7 +86349,7 @@
       </c>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="D1865" t="inlineStr">
@@ -86386,7 +86386,7 @@
     </row>
     <row r="1866">
       <c r="A1866" t="n">
-        <v>3789</v>
+        <v>3790</v>
       </c>
       <c r="B1866" t="inlineStr">
         <is>
@@ -86395,7 +86395,7 @@
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="D1866" t="inlineStr">
@@ -86432,7 +86432,7 @@
     </row>
     <row r="1867">
       <c r="A1867" t="n">
-        <v>3790</v>
+        <v>3791</v>
       </c>
       <c r="B1867" t="inlineStr">
         <is>
@@ -86441,7 +86441,7 @@
       </c>
       <c r="C1867" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="D1867" t="inlineStr">
@@ -86478,7 +86478,7 @@
     </row>
     <row r="1868">
       <c r="A1868" t="n">
-        <v>3791</v>
+        <v>3792</v>
       </c>
       <c r="B1868" t="inlineStr">
         <is>
@@ -86487,7 +86487,7 @@
       </c>
       <c r="C1868" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="D1868" t="inlineStr">
@@ -86524,7 +86524,7 @@
     </row>
     <row r="1869">
       <c r="A1869" t="n">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="B1869" t="inlineStr">
         <is>
@@ -86533,7 +86533,7 @@
       </c>
       <c r="C1869" t="inlineStr">
         <is>
-          <t>2026-12-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="D1869" t="inlineStr">
@@ -86570,7 +86570,7 @@
     </row>
     <row r="1870">
       <c r="A1870" t="n">
-        <v>3793</v>
+        <v>3794</v>
       </c>
       <c r="B1870" t="inlineStr">
         <is>
@@ -86579,7 +86579,7 @@
       </c>
       <c r="C1870" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="D1870" t="inlineStr">
@@ -86616,7 +86616,7 @@
     </row>
     <row r="1871">
       <c r="A1871" t="n">
-        <v>3794</v>
+        <v>3795</v>
       </c>
       <c r="B1871" t="inlineStr">
         <is>
@@ -86625,7 +86625,7 @@
       </c>
       <c r="C1871" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2027-01-02</t>
         </is>
       </c>
       <c r="D1871" t="inlineStr">
@@ -86662,7 +86662,7 @@
     </row>
     <row r="1872">
       <c r="A1872" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="B1872" t="inlineStr">
         <is>
@@ -86671,7 +86671,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>2027-01-02</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
@@ -86708,7 +86708,7 @@
     </row>
     <row r="1873">
       <c r="A1873" t="n">
-        <v>3796</v>
+        <v>3797</v>
       </c>
       <c r="B1873" t="inlineStr">
         <is>
@@ -86717,7 +86717,7 @@
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2027-01-04</t>
         </is>
       </c>
       <c r="D1873" t="inlineStr">
@@ -86754,7 +86754,7 @@
     </row>
     <row r="1874">
       <c r="A1874" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="B1874" t="inlineStr">
         <is>
@@ -86763,7 +86763,7 @@
       </c>
       <c r="C1874" t="inlineStr">
         <is>
-          <t>2027-01-04</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="D1874" t="inlineStr">
@@ -86800,7 +86800,7 @@
     </row>
     <row r="1875">
       <c r="A1875" t="n">
-        <v>3798</v>
+        <v>3799</v>
       </c>
       <c r="B1875" t="inlineStr">
         <is>
@@ -86809,7 +86809,7 @@
       </c>
       <c r="C1875" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2027-01-06</t>
         </is>
       </c>
       <c r="D1875" t="inlineStr">
@@ -86846,7 +86846,7 @@
     </row>
     <row r="1876">
       <c r="A1876" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="B1876" t="inlineStr">
         <is>
@@ -86855,7 +86855,7 @@
       </c>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-01-07</t>
         </is>
       </c>
       <c r="D1876" t="inlineStr">
@@ -86892,7 +86892,7 @@
     </row>
     <row r="1877">
       <c r="A1877" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="B1877" t="inlineStr">
         <is>
@@ -86901,7 +86901,7 @@
       </c>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>2027-01-07</t>
+          <t>2027-01-08</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">
@@ -86938,7 +86938,7 @@
     </row>
     <row r="1878">
       <c r="A1878" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="B1878" t="inlineStr">
         <is>
@@ -86947,7 +86947,7 @@
       </c>
       <c r="C1878" t="inlineStr">
         <is>
-          <t>2027-01-08</t>
+          <t>2027-01-09</t>
         </is>
       </c>
       <c r="D1878" t="inlineStr">
@@ -86984,7 +86984,7 @@
     </row>
     <row r="1879">
       <c r="A1879" t="n">
-        <v>3802</v>
+        <v>3803</v>
       </c>
       <c r="B1879" t="inlineStr">
         <is>
@@ -86993,7 +86993,7 @@
       </c>
       <c r="C1879" t="inlineStr">
         <is>
-          <t>2027-01-09</t>
+          <t>2027-01-10</t>
         </is>
       </c>
       <c r="D1879" t="inlineStr">
@@ -87030,7 +87030,7 @@
     </row>
     <row r="1880">
       <c r="A1880" t="n">
-        <v>3803</v>
+        <v>3804</v>
       </c>
       <c r="B1880" t="inlineStr">
         <is>
@@ -87039,7 +87039,7 @@
       </c>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>2027-01-10</t>
+          <t>2027-01-11</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
@@ -87076,7 +87076,7 @@
     </row>
     <row r="1881">
       <c r="A1881" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="B1881" t="inlineStr">
         <is>
@@ -87085,7 +87085,7 @@
       </c>
       <c r="C1881" t="inlineStr">
         <is>
-          <t>2027-01-11</t>
+          <t>2027-01-12</t>
         </is>
       </c>
       <c r="D1881" t="inlineStr">
@@ -87122,7 +87122,7 @@
     </row>
     <row r="1882">
       <c r="A1882" t="n">
-        <v>3805</v>
+        <v>3806</v>
       </c>
       <c r="B1882" t="inlineStr">
         <is>
@@ -87131,7 +87131,7 @@
       </c>
       <c r="C1882" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="D1882" t="inlineStr">
@@ -87168,7 +87168,7 @@
     </row>
     <row r="1883">
       <c r="A1883" t="n">
-        <v>3806</v>
+        <v>3807</v>
       </c>
       <c r="B1883" t="inlineStr">
         <is>
@@ -87177,7 +87177,7 @@
       </c>
       <c r="C1883" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="D1883" t="inlineStr">
@@ -87214,7 +87214,7 @@
     </row>
     <row r="1884">
       <c r="A1884" t="n">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="B1884" t="inlineStr">
         <is>
@@ -87223,7 +87223,7 @@
       </c>
       <c r="C1884" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="D1884" t="inlineStr">
@@ -87260,7 +87260,7 @@
     </row>
     <row r="1885">
       <c r="A1885" t="n">
-        <v>3808</v>
+        <v>3809</v>
       </c>
       <c r="B1885" t="inlineStr">
         <is>
@@ -87269,7 +87269,7 @@
       </c>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="D1885" t="inlineStr">
@@ -87306,7 +87306,7 @@
     </row>
     <row r="1886">
       <c r="A1886" t="n">
-        <v>3809</v>
+        <v>3810</v>
       </c>
       <c r="B1886" t="inlineStr">
         <is>
@@ -87315,7 +87315,7 @@
       </c>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
@@ -87352,7 +87352,7 @@
     </row>
     <row r="1887">
       <c r="A1887" t="n">
-        <v>3810</v>
+        <v>3811</v>
       </c>
       <c r="B1887" t="inlineStr">
         <is>
@@ -87361,7 +87361,7 @@
       </c>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="D1887" t="inlineStr">
@@ -87398,7 +87398,7 @@
     </row>
     <row r="1888">
       <c r="A1888" t="n">
-        <v>3811</v>
+        <v>3812</v>
       </c>
       <c r="B1888" t="inlineStr">
         <is>
@@ -87407,7 +87407,7 @@
       </c>
       <c r="C1888" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
@@ -87444,7 +87444,7 @@
     </row>
     <row r="1889">
       <c r="A1889" t="n">
-        <v>3812</v>
+        <v>3813</v>
       </c>
       <c r="B1889" t="inlineStr">
         <is>
@@ -87453,7 +87453,7 @@
       </c>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D1889" t="inlineStr">
@@ -87490,7 +87490,7 @@
     </row>
     <row r="1890">
       <c r="A1890" t="n">
-        <v>3813</v>
+        <v>3814</v>
       </c>
       <c r="B1890" t="inlineStr">
         <is>
@@ -87499,7 +87499,7 @@
       </c>
       <c r="C1890" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D1890" t="inlineStr">
@@ -87536,7 +87536,7 @@
     </row>
     <row r="1891">
       <c r="A1891" t="n">
-        <v>3814</v>
+        <v>3815</v>
       </c>
       <c r="B1891" t="inlineStr">
         <is>
@@ -87545,7 +87545,7 @@
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
@@ -87582,7 +87582,7 @@
     </row>
     <row r="1892">
       <c r="A1892" t="n">
-        <v>3815</v>
+        <v>3816</v>
       </c>
       <c r="B1892" t="inlineStr">
         <is>
@@ -87591,7 +87591,7 @@
       </c>
       <c r="C1892" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="D1892" t="inlineStr">
@@ -87628,7 +87628,7 @@
     </row>
     <row r="1893">
       <c r="A1893" t="n">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="B1893" t="inlineStr">
         <is>
@@ -87637,7 +87637,7 @@
       </c>
       <c r="C1893" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="D1893" t="inlineStr">
@@ -87674,7 +87674,7 @@
     </row>
     <row r="1894">
       <c r="A1894" t="n">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="B1894" t="inlineStr">
         <is>
@@ -87683,7 +87683,7 @@
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="D1894" t="inlineStr">
@@ -87720,7 +87720,7 @@
     </row>
     <row r="1895">
       <c r="A1895" t="n">
-        <v>3818</v>
+        <v>3819</v>
       </c>
       <c r="B1895" t="inlineStr">
         <is>
@@ -87729,7 +87729,7 @@
       </c>
       <c r="C1895" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="D1895" t="inlineStr">
@@ -87766,7 +87766,7 @@
     </row>
     <row r="1896">
       <c r="A1896" t="n">
-        <v>3819</v>
+        <v>3820</v>
       </c>
       <c r="B1896" t="inlineStr">
         <is>
@@ -87775,7 +87775,7 @@
       </c>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -87812,7 +87812,7 @@
     </row>
     <row r="1897">
       <c r="A1897" t="n">
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="B1897" t="inlineStr">
         <is>
@@ -87821,7 +87821,7 @@
       </c>
       <c r="C1897" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="D1897" t="inlineStr">
@@ -87858,7 +87858,7 @@
     </row>
     <row r="1898">
       <c r="A1898" t="n">
-        <v>3821</v>
+        <v>3822</v>
       </c>
       <c r="B1898" t="inlineStr">
         <is>
@@ -87867,7 +87867,7 @@
       </c>
       <c r="C1898" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="D1898" t="inlineStr">
@@ -87904,7 +87904,7 @@
     </row>
     <row r="1899">
       <c r="A1899" t="n">
-        <v>3822</v>
+        <v>3823</v>
       </c>
       <c r="B1899" t="inlineStr">
         <is>
@@ -87913,7 +87913,7 @@
       </c>
       <c r="C1899" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="D1899" t="inlineStr">
@@ -87950,7 +87950,7 @@
     </row>
     <row r="1900">
       <c r="A1900" t="n">
-        <v>3823</v>
+        <v>3824</v>
       </c>
       <c r="B1900" t="inlineStr">
         <is>
@@ -87959,7 +87959,7 @@
       </c>
       <c r="C1900" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2027-01-31</t>
         </is>
       </c>
       <c r="D1900" t="inlineStr">
@@ -87996,7 +87996,7 @@
     </row>
     <row r="1901">
       <c r="A1901" t="n">
-        <v>3824</v>
+        <v>3825</v>
       </c>
       <c r="B1901" t="inlineStr">
         <is>
@@ -88005,7 +88005,7 @@
       </c>
       <c r="C1901" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="D1901" t="inlineStr">
@@ -88042,7 +88042,7 @@
     </row>
     <row r="1902">
       <c r="A1902" t="n">
-        <v>3825</v>
+        <v>3826</v>
       </c>
       <c r="B1902" t="inlineStr">
         <is>
@@ -88051,7 +88051,7 @@
       </c>
       <c r="C1902" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2027-02-02</t>
         </is>
       </c>
       <c r="D1902" t="inlineStr">
@@ -88088,7 +88088,7 @@
     </row>
     <row r="1903">
       <c r="A1903" t="n">
-        <v>3826</v>
+        <v>3827</v>
       </c>
       <c r="B1903" t="inlineStr">
         <is>
@@ -88097,7 +88097,7 @@
       </c>
       <c r="C1903" t="inlineStr">
         <is>
-          <t>2027-02-02</t>
+          <t>2027-02-03</t>
         </is>
       </c>
       <c r="D1903" t="inlineStr">
@@ -88134,7 +88134,7 @@
     </row>
     <row r="1904">
       <c r="A1904" t="n">
-        <v>3827</v>
+        <v>3828</v>
       </c>
       <c r="B1904" t="inlineStr">
         <is>
@@ -88143,7 +88143,7 @@
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>2027-02-03</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -88180,7 +88180,7 @@
     </row>
     <row r="1905">
       <c r="A1905" t="n">
-        <v>3828</v>
+        <v>3829</v>
       </c>
       <c r="B1905" t="inlineStr">
         <is>
@@ -88189,7 +88189,7 @@
       </c>
       <c r="C1905" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="D1905" t="inlineStr">
@@ -88226,7 +88226,7 @@
     </row>
     <row r="1906">
       <c r="A1906" t="n">
-        <v>3829</v>
+        <v>3830</v>
       </c>
       <c r="B1906" t="inlineStr">
         <is>
@@ -88235,7 +88235,7 @@
       </c>
       <c r="C1906" t="inlineStr">
         <is>
-          <t>2027-02-05</t>
+          <t>2027-02-06</t>
         </is>
       </c>
       <c r="D1906" t="inlineStr">
@@ -88272,7 +88272,7 @@
     </row>
     <row r="1907">
       <c r="A1907" t="n">
-        <v>3830</v>
+        <v>3831</v>
       </c>
       <c r="B1907" t="inlineStr">
         <is>
@@ -88281,7 +88281,7 @@
       </c>
       <c r="C1907" t="inlineStr">
         <is>
-          <t>2027-02-06</t>
+          <t>2027-02-07</t>
         </is>
       </c>
       <c r="D1907" t="inlineStr">
@@ -88318,7 +88318,7 @@
     </row>
     <row r="1908">
       <c r="A1908" t="n">
-        <v>3831</v>
+        <v>3832</v>
       </c>
       <c r="B1908" t="inlineStr">
         <is>
@@ -88327,7 +88327,7 @@
       </c>
       <c r="C1908" t="inlineStr">
         <is>
-          <t>2027-02-07</t>
+          <t>2027-02-08</t>
         </is>
       </c>
       <c r="D1908" t="inlineStr">
@@ -88364,7 +88364,7 @@
     </row>
     <row r="1909">
       <c r="A1909" t="n">
-        <v>3832</v>
+        <v>3833</v>
       </c>
       <c r="B1909" t="inlineStr">
         <is>
@@ -88373,7 +88373,7 @@
       </c>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>2027-02-08</t>
+          <t>2027-02-09</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -88410,7 +88410,7 @@
     </row>
     <row r="1910">
       <c r="A1910" t="n">
-        <v>3833</v>
+        <v>3834</v>
       </c>
       <c r="B1910" t="inlineStr">
         <is>
@@ -88419,7 +88419,7 @@
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>2027-02-09</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D1910" t="inlineStr">
@@ -88456,7 +88456,7 @@
     </row>
     <row r="1911">
       <c r="A1911" t="n">
-        <v>3834</v>
+        <v>3835</v>
       </c>
       <c r="B1911" t="inlineStr">
         <is>
@@ -88465,7 +88465,7 @@
       </c>
       <c r="C1911" t="inlineStr">
         <is>
-          <t>2027-02-10</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="D1911" t="inlineStr">
@@ -88502,7 +88502,7 @@
     </row>
     <row r="1912">
       <c r="A1912" t="n">
-        <v>3835</v>
+        <v>3836</v>
       </c>
       <c r="B1912" t="inlineStr">
         <is>
@@ -88511,7 +88511,7 @@
       </c>
       <c r="C1912" t="inlineStr">
         <is>
-          <t>2027-02-11</t>
+          <t>2027-02-12</t>
         </is>
       </c>
       <c r="D1912" t="inlineStr">
@@ -88548,7 +88548,7 @@
     </row>
     <row r="1913">
       <c r="A1913" t="n">
-        <v>3836</v>
+        <v>3837</v>
       </c>
       <c r="B1913" t="inlineStr">
         <is>
@@ -88557,7 +88557,7 @@
       </c>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-13</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
@@ -88594,7 +88594,7 @@
     </row>
     <row r="1914">
       <c r="A1914" t="n">
-        <v>3837</v>
+        <v>3838</v>
       </c>
       <c r="B1914" t="inlineStr">
         <is>
@@ -88603,7 +88603,7 @@
       </c>
       <c r="C1914" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="D1914" t="inlineStr">
@@ -88640,7 +88640,7 @@
     </row>
     <row r="1915">
       <c r="A1915" t="n">
-        <v>3838</v>
+        <v>3839</v>
       </c>
       <c r="B1915" t="inlineStr">
         <is>
@@ -88649,7 +88649,7 @@
       </c>
       <c r="C1915" t="inlineStr">
         <is>
-          <t>2027-02-14</t>
+          <t>2027-02-15</t>
         </is>
       </c>
       <c r="D1915" t="inlineStr">
@@ -88686,7 +88686,7 @@
     </row>
     <row r="1916">
       <c r="A1916" t="n">
-        <v>3839</v>
+        <v>3840</v>
       </c>
       <c r="B1916" t="inlineStr">
         <is>
@@ -88695,7 +88695,7 @@
       </c>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>2027-02-15</t>
+          <t>2027-02-16</t>
         </is>
       </c>
       <c r="D1916" t="inlineStr">
@@ -88732,7 +88732,7 @@
     </row>
     <row r="1917">
       <c r="A1917" t="n">
-        <v>3840</v>
+        <v>3841</v>
       </c>
       <c r="B1917" t="inlineStr">
         <is>
@@ -88741,7 +88741,7 @@
       </c>
       <c r="C1917" t="inlineStr">
         <is>
-          <t>2027-02-16</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="D1917" t="inlineStr">
@@ -88778,7 +88778,7 @@
     </row>
     <row r="1918">
       <c r="A1918" t="n">
-        <v>3841</v>
+        <v>3842</v>
       </c>
       <c r="B1918" t="inlineStr">
         <is>
@@ -88787,7 +88787,7 @@
       </c>
       <c r="C1918" t="inlineStr">
         <is>
-          <t>2027-02-17</t>
+          <t>2027-02-18</t>
         </is>
       </c>
       <c r="D1918" t="inlineStr">
@@ -88824,7 +88824,7 @@
     </row>
     <row r="1919">
       <c r="A1919" t="n">
-        <v>3842</v>
+        <v>3843</v>
       </c>
       <c r="B1919" t="inlineStr">
         <is>
@@ -88833,7 +88833,7 @@
       </c>
       <c r="C1919" t="inlineStr">
         <is>
-          <t>2027-02-18</t>
+          <t>2027-02-19</t>
         </is>
       </c>
       <c r="D1919" t="inlineStr">
@@ -88870,7 +88870,7 @@
     </row>
     <row r="1920">
       <c r="A1920" t="n">
-        <v>3843</v>
+        <v>3844</v>
       </c>
       <c r="B1920" t="inlineStr">
         <is>
@@ -88879,7 +88879,7 @@
       </c>
       <c r="C1920" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="D1920" t="inlineStr">
@@ -88916,7 +88916,7 @@
     </row>
     <row r="1921">
       <c r="A1921" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="B1921" t="inlineStr">
         <is>
@@ -88925,7 +88925,7 @@
       </c>
       <c r="C1921" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-02-21</t>
         </is>
       </c>
       <c r="D1921" t="inlineStr">
@@ -88962,7 +88962,7 @@
     </row>
     <row r="1922">
       <c r="A1922" t="n">
-        <v>3845</v>
+        <v>3846</v>
       </c>
       <c r="B1922" t="inlineStr">
         <is>
@@ -88971,7 +88971,7 @@
       </c>
       <c r="C1922" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="D1922" t="inlineStr">
@@ -89008,7 +89008,7 @@
     </row>
     <row r="1923">
       <c r="A1923" t="n">
-        <v>3846</v>
+        <v>3847</v>
       </c>
       <c r="B1923" t="inlineStr">
         <is>
@@ -89017,7 +89017,7 @@
       </c>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-23</t>
         </is>
       </c>
       <c r="D1923" t="inlineStr">
@@ -89054,7 +89054,7 @@
     </row>
     <row r="1924">
       <c r="A1924" t="n">
-        <v>3847</v>
+        <v>3848</v>
       </c>
       <c r="B1924" t="inlineStr">
         <is>
@@ -89063,7 +89063,7 @@
       </c>
       <c r="C1924" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="D1924" t="inlineStr">
@@ -89100,7 +89100,7 @@
     </row>
     <row r="1925">
       <c r="A1925" t="n">
-        <v>3848</v>
+        <v>3849</v>
       </c>
       <c r="B1925" t="inlineStr">
         <is>
@@ -89109,7 +89109,7 @@
       </c>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>2027-02-24</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="D1925" t="inlineStr">
@@ -89146,7 +89146,7 @@
     </row>
     <row r="1926">
       <c r="A1926" t="n">
-        <v>3849</v>
+        <v>3850</v>
       </c>
       <c r="B1926" t="inlineStr">
         <is>
@@ -89155,7 +89155,7 @@
       </c>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="D1926" t="inlineStr">
@@ -89192,7 +89192,7 @@
     </row>
     <row r="1927">
       <c r="A1927" t="n">
-        <v>3850</v>
+        <v>3851</v>
       </c>
       <c r="B1927" t="inlineStr">
         <is>
@@ -89201,7 +89201,7 @@
       </c>
       <c r="C1927" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="D1927" t="inlineStr">
@@ -89238,7 +89238,7 @@
     </row>
     <row r="1928">
       <c r="A1928" t="n">
-        <v>3851</v>
+        <v>3852</v>
       </c>
       <c r="B1928" t="inlineStr">
         <is>
@@ -89247,7 +89247,7 @@
       </c>
       <c r="C1928" t="inlineStr">
         <is>
-          <t>2027-02-27</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="D1928" t="inlineStr">
@@ -89284,7 +89284,7 @@
     </row>
     <row r="1929">
       <c r="A1929" t="n">
-        <v>3852</v>
+        <v>3853</v>
       </c>
       <c r="B1929" t="inlineStr">
         <is>
@@ -89293,7 +89293,7 @@
       </c>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="D1929" t="inlineStr">
@@ -89330,7 +89330,7 @@
     </row>
     <row r="1930">
       <c r="A1930" t="n">
-        <v>3853</v>
+        <v>3854</v>
       </c>
       <c r="B1930" t="inlineStr">
         <is>
@@ -89339,7 +89339,7 @@
       </c>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>2027-03-01</t>
+          <t>2027-03-02</t>
         </is>
       </c>
       <c r="D1930" t="inlineStr">
@@ -89376,7 +89376,7 @@
     </row>
     <row r="1931">
       <c r="A1931" t="n">
-        <v>3854</v>
+        <v>3855</v>
       </c>
       <c r="B1931" t="inlineStr">
         <is>
@@ -89385,7 +89385,7 @@
       </c>
       <c r="C1931" t="inlineStr">
         <is>
-          <t>2027-03-02</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="D1931" t="inlineStr">
@@ -89422,7 +89422,7 @@
     </row>
     <row r="1932">
       <c r="A1932" t="n">
-        <v>3855</v>
+        <v>3856</v>
       </c>
       <c r="B1932" t="inlineStr">
         <is>
@@ -89431,7 +89431,7 @@
       </c>
       <c r="C1932" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
+          <t>2027-03-04</t>
         </is>
       </c>
       <c r="D1932" t="inlineStr">
@@ -89468,7 +89468,7 @@
     </row>
     <row r="1933">
       <c r="A1933" t="n">
-        <v>3856</v>
+        <v>3857</v>
       </c>
       <c r="B1933" t="inlineStr">
         <is>
@@ -89477,7 +89477,7 @@
       </c>
       <c r="C1933" t="inlineStr">
         <is>
-          <t>2027-03-04</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="D1933" t="inlineStr">
@@ -89514,7 +89514,7 @@
     </row>
     <row r="1934">
       <c r="A1934" t="n">
-        <v>3857</v>
+        <v>3858</v>
       </c>
       <c r="B1934" t="inlineStr">
         <is>
@@ -89523,7 +89523,7 @@
       </c>
       <c r="C1934" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-03-06</t>
         </is>
       </c>
       <c r="D1934" t="inlineStr">
@@ -89560,7 +89560,7 @@
     </row>
     <row r="1935">
       <c r="A1935" t="n">
-        <v>3858</v>
+        <v>3859</v>
       </c>
       <c r="B1935" t="inlineStr">
         <is>
@@ -89569,7 +89569,7 @@
       </c>
       <c r="C1935" t="inlineStr">
         <is>
-          <t>2027-03-06</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="D1935" t="inlineStr">
@@ -89606,7 +89606,7 @@
     </row>
     <row r="1936">
       <c r="A1936" t="n">
-        <v>3859</v>
+        <v>3860</v>
       </c>
       <c r="B1936" t="inlineStr">
         <is>
@@ -89615,7 +89615,7 @@
       </c>
       <c r="C1936" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="D1936" t="inlineStr">
@@ -89652,7 +89652,7 @@
     </row>
     <row r="1937">
       <c r="A1937" t="n">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="B1937" t="inlineStr">
         <is>
@@ -89661,7 +89661,7 @@
       </c>
       <c r="C1937" t="inlineStr">
         <is>
-          <t>2027-03-08</t>
+          <t>2027-03-09</t>
         </is>
       </c>
       <c r="D1937" t="inlineStr">
@@ -89695,52 +89695,6 @@
       </c>
       <c r="K1937" t="inlineStr"/>
       <c r="L1937" t="inlineStr"/>
-    </row>
-    <row r="1938">
-      <c r="A1938" t="n">
-        <v>3861</v>
-      </c>
-      <c r="B1938" t="inlineStr">
-        <is>
-          <t>Natália</t>
-        </is>
-      </c>
-      <c r="C1938" t="inlineStr">
-        <is>
-          <t>2027-03-09</t>
-        </is>
-      </c>
-      <c r="D1938" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="E1938" t="inlineStr">
-        <is>
-          <t>Leitura</t>
-        </is>
-      </c>
-      <c r="F1938" t="inlineStr">
-        <is>
-          <t>Vocabulary</t>
-        </is>
-      </c>
-      <c r="G1938" t="inlineStr">
-        <is>
-          <t>Personalizado</t>
-        </is>
-      </c>
-      <c r="H1938" t="n">
-        <v>15</v>
-      </c>
-      <c r="I1938" t="n">
-        <v>0</v>
-      </c>
-      <c r="J1938" t="b">
-        <v>0</v>
-      </c>
-      <c r="K1938" t="inlineStr"/>
-      <c r="L1938" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1714,13 +1714,17 @@
         <v>20</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1814,13 +1814,17 @@
         <v>20</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:23</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Atividades" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Usuarios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Materiais" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1914,13 +1913,17 @@
         <v>30</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-09-11 16:14</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -89917,186 +89920,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Usuario</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Titulo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Descricao</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>NomeArquivo</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>CaminhoArquivo</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TamanhoKB</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>DataCriacao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Darlei Delfino</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Exercícios - Present Simple and Present Continuous</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Série de exercícios para treinar</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.thea.study/s/1246841602/18e468b90</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-09-06 03:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Darlei Delfino</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Vocabulary - Daily Routine</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.thea.study/s/1246892220/1d070842d</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-09-06 04:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Darlei Delfino</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Jogo de Gramática</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Crie seu perfil e aceite o desafio.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://englishgrammarjourney.streamlit.app/</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-09-07 02:12</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -1992,7 +1992,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>English Live - Conversação em grupo</t>
+          <t>English Live - Conversa com Professor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>

--- a/data/estudo_ingles_dados.xlsx
+++ b/data/estudo_ingles_dados.xlsx
@@ -2009,13 +2009,17 @@
         <v>45</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-09-11 18:44</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
